--- a/excel/Weekends_予算と報奨金案_粗利2150万円.xlsx
+++ b/excel/Weekends_予算と報奨金案_粗利2150万円.xlsx
@@ -12,7 +12,8 @@
     <sheet name="達成度別" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="粗利率別" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="月別目標と営業利益" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="報奨金（例B）" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="月別（スマレジ版）" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="報奨金（例B）" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -395,6 +396,120 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>月別の営業利益（スマレジ版・100%達成時）</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'月別（スマレジ版）'!G4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'月別（スマレジ版）'!$A$5:$A$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'月別（スマレジ版）'!$G$5:$G$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'月別（スマレジ版）'!H4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'月別（スマレジ版）'!$H$5:$H$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -423,6 +538,33 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -2372,6 +2514,710 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>月別の目標と営業利益　スマレジ版（全月で100%達成した場合）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>月の目標は、店長がスマレジに登録した店舗予算（年6,000万円・税抜）の月比率で配分。前年構成比版との差も表示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>スマレジ予算（参考）</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>月比率</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>目標売上</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>粗利目標100%</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>粗利目標105%</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>営業利益（100%時）</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>累計</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>構成比版との差（粗利目標）</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>実績粗利</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>段階</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>報奨金</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="C5" s="10">
+        <f>B5/SUM($B$5:$B$16)</f>
+        <v/>
+      </c>
+      <c r="D5" s="9">
+        <f>ROUND(入力!$B$19*C5,-3)</f>
+        <v/>
+      </c>
+      <c r="E5" s="9">
+        <f>ROUND(入力!$B$5*C5,-3)</f>
+        <v/>
+      </c>
+      <c r="F5" s="9">
+        <f>ROUND(E5*入力!$B$16,-3)</f>
+        <v/>
+      </c>
+      <c r="G5" s="9">
+        <f>E5-D5*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="H5" s="9">
+        <f>SUM($G$5:G5)</f>
+        <v/>
+      </c>
+      <c r="I5" s="9">
+        <f>E5-'月別目標と営業利益'!E5</f>
+        <v/>
+      </c>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="15">
+        <f>IF(J5="","",IF(J5&gt;=F5,2,IF(J5&gt;=E5,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L5" s="9">
+        <f>IF(OR(K5="",K5=0),0,IF(K5=2,入力!$B$15,入力!$B$14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="C6" s="10">
+        <f>B6/SUM($B$5:$B$16)</f>
+        <v/>
+      </c>
+      <c r="D6" s="9">
+        <f>ROUND(入力!$B$19*C6,-3)</f>
+        <v/>
+      </c>
+      <c r="E6" s="9">
+        <f>ROUND(入力!$B$5*C6,-3)</f>
+        <v/>
+      </c>
+      <c r="F6" s="9">
+        <f>ROUND(E6*入力!$B$16,-3)</f>
+        <v/>
+      </c>
+      <c r="G6" s="9">
+        <f>E6-D6*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="H6" s="9">
+        <f>SUM($G$5:G6)</f>
+        <v/>
+      </c>
+      <c r="I6" s="9">
+        <f>E6-'月別目標と営業利益'!E6</f>
+        <v/>
+      </c>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="15">
+        <f>IF(J6="","",IF(J6&gt;=F6,2,IF(J6&gt;=E6,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L6" s="9">
+        <f>IF(OR(K6="",K6=0),0,IF(K6=2,入力!$B$15,入力!$B$14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>10月</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="C7" s="10">
+        <f>B7/SUM($B$5:$B$16)</f>
+        <v/>
+      </c>
+      <c r="D7" s="9">
+        <f>ROUND(入力!$B$19*C7,-3)</f>
+        <v/>
+      </c>
+      <c r="E7" s="9">
+        <f>ROUND(入力!$B$5*C7,-3)</f>
+        <v/>
+      </c>
+      <c r="F7" s="9">
+        <f>ROUND(E7*入力!$B$16,-3)</f>
+        <v/>
+      </c>
+      <c r="G7" s="9">
+        <f>E7-D7*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="H7" s="9">
+        <f>SUM($G$5:G7)</f>
+        <v/>
+      </c>
+      <c r="I7" s="9">
+        <f>E7-'月別目標と営業利益'!E7</f>
+        <v/>
+      </c>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="15">
+        <f>IF(J7="","",IF(J7&gt;=F7,2,IF(J7&gt;=E7,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L7" s="9">
+        <f>IF(OR(K7="",K7=0),0,IF(K7=2,入力!$B$15,入力!$B$14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="C8" s="10">
+        <f>B8/SUM($B$5:$B$16)</f>
+        <v/>
+      </c>
+      <c r="D8" s="9">
+        <f>ROUND(入力!$B$19*C8,-3)</f>
+        <v/>
+      </c>
+      <c r="E8" s="9">
+        <f>ROUND(入力!$B$5*C8,-3)</f>
+        <v/>
+      </c>
+      <c r="F8" s="9">
+        <f>ROUND(E8*入力!$B$16,-3)</f>
+        <v/>
+      </c>
+      <c r="G8" s="9">
+        <f>E8-D8*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="H8" s="9">
+        <f>SUM($G$5:G8)</f>
+        <v/>
+      </c>
+      <c r="I8" s="9">
+        <f>E8-'月別目標と営業利益'!E8</f>
+        <v/>
+      </c>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="15">
+        <f>IF(J8="","",IF(J8&gt;=F8,2,IF(J8&gt;=E8,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L8" s="9">
+        <f>IF(OR(K8="",K8=0),0,IF(K8=2,入力!$B$15,入力!$B$14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>12月</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="C9" s="10">
+        <f>B9/SUM($B$5:$B$16)</f>
+        <v/>
+      </c>
+      <c r="D9" s="9">
+        <f>ROUND(入力!$B$19*C9,-3)</f>
+        <v/>
+      </c>
+      <c r="E9" s="9">
+        <f>ROUND(入力!$B$5*C9,-3)</f>
+        <v/>
+      </c>
+      <c r="F9" s="9">
+        <f>ROUND(E9*入力!$B$16,-3)</f>
+        <v/>
+      </c>
+      <c r="G9" s="9">
+        <f>E9-D9*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="H9" s="9">
+        <f>SUM($G$5:G9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="9">
+        <f>E9-'月別目標と営業利益'!E9</f>
+        <v/>
+      </c>
+      <c r="J9" s="4" t="n"/>
+      <c r="K9" s="15">
+        <f>IF(J9="","",IF(J9&gt;=F9,2,IF(J9&gt;=E9,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L9" s="9">
+        <f>IF(OR(K9="",K9=0),0,IF(K9=2,入力!$B$15,入力!$B$14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>1月</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="C10" s="10">
+        <f>B10/SUM($B$5:$B$16)</f>
+        <v/>
+      </c>
+      <c r="D10" s="9">
+        <f>ROUND(入力!$B$19*C10,-3)</f>
+        <v/>
+      </c>
+      <c r="E10" s="9">
+        <f>ROUND(入力!$B$5*C10,-3)</f>
+        <v/>
+      </c>
+      <c r="F10" s="9">
+        <f>ROUND(E10*入力!$B$16,-3)</f>
+        <v/>
+      </c>
+      <c r="G10" s="9">
+        <f>E10-D10*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="H10" s="9">
+        <f>SUM($G$5:G10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="9">
+        <f>E10-'月別目標と営業利益'!E10</f>
+        <v/>
+      </c>
+      <c r="J10" s="4" t="n"/>
+      <c r="K10" s="15">
+        <f>IF(J10="","",IF(J10&gt;=F10,2,IF(J10&gt;=E10,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L10" s="9">
+        <f>IF(OR(K10="",K10=0),0,IF(K10=2,入力!$B$15,入力!$B$14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2月</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="C11" s="10">
+        <f>B11/SUM($B$5:$B$16)</f>
+        <v/>
+      </c>
+      <c r="D11" s="9">
+        <f>ROUND(入力!$B$19*C11,-3)</f>
+        <v/>
+      </c>
+      <c r="E11" s="9">
+        <f>ROUND(入力!$B$5*C11,-3)</f>
+        <v/>
+      </c>
+      <c r="F11" s="9">
+        <f>ROUND(E11*入力!$B$16,-3)</f>
+        <v/>
+      </c>
+      <c r="G11" s="9">
+        <f>E11-D11*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="H11" s="9">
+        <f>SUM($G$5:G11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="9">
+        <f>E11-'月別目標と営業利益'!E11</f>
+        <v/>
+      </c>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="15">
+        <f>IF(J11="","",IF(J11&gt;=F11,2,IF(J11&gt;=E11,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L11" s="9">
+        <f>IF(OR(K11="",K11=0),0,IF(K11=2,入力!$B$15,入力!$B$14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="C12" s="10">
+        <f>B12/SUM($B$5:$B$16)</f>
+        <v/>
+      </c>
+      <c r="D12" s="9">
+        <f>ROUND(入力!$B$19*C12,-3)</f>
+        <v/>
+      </c>
+      <c r="E12" s="9">
+        <f>ROUND(入力!$B$5*C12,-3)</f>
+        <v/>
+      </c>
+      <c r="F12" s="9">
+        <f>ROUND(E12*入力!$B$16,-3)</f>
+        <v/>
+      </c>
+      <c r="G12" s="9">
+        <f>E12-D12*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="H12" s="9">
+        <f>SUM($G$5:G12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="9">
+        <f>E12-'月別目標と営業利益'!E12</f>
+        <v/>
+      </c>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="15">
+        <f>IF(J12="","",IF(J12&gt;=F12,2,IF(J12&gt;=E12,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L12" s="9">
+        <f>IF(OR(K12="",K12=0),0,IF(K12=2,入力!$B$15,入力!$B$14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="C13" s="10">
+        <f>B13/SUM($B$5:$B$16)</f>
+        <v/>
+      </c>
+      <c r="D13" s="9">
+        <f>ROUND(入力!$B$19*C13,-3)</f>
+        <v/>
+      </c>
+      <c r="E13" s="9">
+        <f>ROUND(入力!$B$5*C13,-3)</f>
+        <v/>
+      </c>
+      <c r="F13" s="9">
+        <f>ROUND(E13*入力!$B$16,-3)</f>
+        <v/>
+      </c>
+      <c r="G13" s="9">
+        <f>E13-D13*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="H13" s="9">
+        <f>SUM($G$5:G13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="9">
+        <f>E13-'月別目標と営業利益'!E13</f>
+        <v/>
+      </c>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="15">
+        <f>IF(J13="","",IF(J13&gt;=F13,2,IF(J13&gt;=E13,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L13" s="9">
+        <f>IF(OR(K13="",K13=0),0,IF(K13=2,入力!$B$15,入力!$B$14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="C14" s="10">
+        <f>B14/SUM($B$5:$B$16)</f>
+        <v/>
+      </c>
+      <c r="D14" s="9">
+        <f>ROUND(入力!$B$19*C14,-3)</f>
+        <v/>
+      </c>
+      <c r="E14" s="9">
+        <f>ROUND(入力!$B$5*C14,-3)</f>
+        <v/>
+      </c>
+      <c r="F14" s="9">
+        <f>ROUND(E14*入力!$B$16,-3)</f>
+        <v/>
+      </c>
+      <c r="G14" s="9">
+        <f>E14-D14*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="H14" s="9">
+        <f>SUM($G$5:G14)</f>
+        <v/>
+      </c>
+      <c r="I14" s="9">
+        <f>E14-'月別目標と営業利益'!E14</f>
+        <v/>
+      </c>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="15">
+        <f>IF(J14="","",IF(J14&gt;=F14,2,IF(J14&gt;=E14,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L14" s="9">
+        <f>IF(OR(K14="",K14=0),0,IF(K14=2,入力!$B$15,入力!$B$14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="C15" s="10">
+        <f>B15/SUM($B$5:$B$16)</f>
+        <v/>
+      </c>
+      <c r="D15" s="9">
+        <f>ROUND(入力!$B$19*C15,-3)</f>
+        <v/>
+      </c>
+      <c r="E15" s="9">
+        <f>ROUND(入力!$B$5*C15,-3)</f>
+        <v/>
+      </c>
+      <c r="F15" s="9">
+        <f>ROUND(E15*入力!$B$16,-3)</f>
+        <v/>
+      </c>
+      <c r="G15" s="9">
+        <f>E15-D15*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="H15" s="9">
+        <f>SUM($G$5:G15)</f>
+        <v/>
+      </c>
+      <c r="I15" s="9">
+        <f>E15-'月別目標と営業利益'!E15</f>
+        <v/>
+      </c>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="15">
+        <f>IF(J15="","",IF(J15&gt;=F15,2,IF(J15&gt;=E15,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L15" s="9">
+        <f>IF(OR(K15="",K15=0),0,IF(K15=2,入力!$B$15,入力!$B$14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>7月</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="C16" s="10">
+        <f>B16/SUM($B$5:$B$16)</f>
+        <v/>
+      </c>
+      <c r="D16" s="9">
+        <f>ROUND(入力!$B$19*C16,-3)</f>
+        <v/>
+      </c>
+      <c r="E16" s="9">
+        <f>ROUND(入力!$B$5*C16,-3)</f>
+        <v/>
+      </c>
+      <c r="F16" s="9">
+        <f>ROUND(E16*入力!$B$16,-3)</f>
+        <v/>
+      </c>
+      <c r="G16" s="9">
+        <f>E16-D16*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="H16" s="9">
+        <f>SUM($G$5:G16)</f>
+        <v/>
+      </c>
+      <c r="I16" s="9">
+        <f>E16-'月別目標と営業利益'!E16</f>
+        <v/>
+      </c>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="15">
+        <f>IF(J16="","",IF(J16&gt;=F16,2,IF(J16&gt;=E16,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L16" s="9">
+        <f>IF(OR(K16="",K16=0),0,IF(K16=2,入力!$B$15,入力!$B$14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>年計</t>
+        </is>
+      </c>
+      <c r="B17" s="14">
+        <f>SUM(B5:B16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="14">
+        <f>SUM(D5:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="14">
+        <f>SUM(E5:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="14">
+        <f>SUM(F5:F16)</f>
+        <v/>
+      </c>
+      <c r="G17" s="14">
+        <f>SUM(G5:G16)</f>
+        <v/>
+      </c>
+      <c r="J17" s="14">
+        <f>SUM(J5:J16)</f>
+        <v/>
+      </c>
+      <c r="L17" s="14">
+        <f>SUM(L5:L16)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/excel/Weekends_予算と報奨金案_粗利2150万円.xlsx
+++ b/excel/Weekends_予算と報奨金案_粗利2150万円.xlsx
@@ -294,7 +294,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>月別の営業利益（100%達成時）</a:t>
+              <a:t>月別　営業利益（100%達成時）</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -309,7 +309,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'月別目標と営業利益'!G4</f>
+              <f>'月別目標と営業利益'!H5</f>
             </strRef>
           </tx>
           <spPr>
@@ -319,12 +319,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'月別目標と営業利益'!$A$5:$A$16</f>
+              <f>'月別目標と営業利益'!$A$6:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'月別目標と営業利益'!$G$5:$G$16</f>
+              <f>'月別目標と営業利益'!$H$6:$H$17</f>
             </numRef>
           </val>
         </ser>
@@ -339,7 +339,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'月別目標と営業利益'!H4</f>
+              <f>'月別目標と営業利益'!I5</f>
             </strRef>
           </tx>
           <spPr>
@@ -357,7 +357,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'月別目標と営業利益'!$H$5:$H$16</f>
+              <f>'月別目標と営業利益'!$I$6:$I$17</f>
             </numRef>
           </val>
         </ser>
@@ -408,7 +408,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>月別の営業利益（スマレジ版・100%達成時）</a:t>
+              <a:t>月別（スマレジ版）　営業利益（100%達成時）</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -423,7 +423,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'月別（スマレジ版）'!G4</f>
+              <f>'月別（スマレジ版）'!H5</f>
             </strRef>
           </tx>
           <spPr>
@@ -433,12 +433,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'月別（スマレジ版）'!$A$5:$A$16</f>
+              <f>'月別（スマレジ版）'!$A$6:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'月別（スマレジ版）'!$G$5:$G$16</f>
+              <f>'月別（スマレジ版）'!$H$6:$H$17</f>
             </numRef>
           </val>
         </ser>
@@ -453,7 +453,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'月別（スマレジ版）'!H4</f>
+              <f>'月別（スマレジ版）'!I5</f>
             </strRef>
           </tx>
           <spPr>
@@ -471,7 +471,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'月別（スマレジ版）'!$H$5:$H$16</f>
+              <f>'月別（スマレジ版）'!$I$6:$I$17</f>
             </numRef>
           </val>
         </ser>
@@ -543,7 +543,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="2880000"/>
@@ -570,7 +570,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="2880000"/>
@@ -1864,642 +1864,714 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>月別の目標と営業利益（全月で100%達成した場合）</t>
+          <t>月別の目標と営業利益　構成比版（全月で100%達成した場合）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>月の目標は前年（2025/8〜2026/7）の売上構成比で配分。固定費は12等分。黄色に実績粗利（スマレジ・税抜）を入れると段階と報奨金が出る。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+          <t>月の目標は前年（2025/8〜2026/7）の売上構成比で配分。固定費は12等分。黄色の実績粗利（スマレジ・税抜）を入れると段階と報奨金が出る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>黄色の「粗利目標100%」は5万円単位に丸めた目標（年計2,150万円に合わせて調整済み）。105%は5万円単位。目標売上は粗利目標÷粗利率を1万円単位で表示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>前年売上（参考）</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>構成比</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>目標売上</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>比率</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>目標売上（参考）</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>粗利目標（丸め前）</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>粗利目標100%</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>粗利目標105%</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>営業利益（100%時）</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>累計</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>実績粗利</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>報奨金</t>
         </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>8月</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>3040292</v>
-      </c>
-      <c r="C5" s="10">
-        <f>B5/SUM($B$5:$B$16)</f>
-        <v/>
-      </c>
-      <c r="D5" s="9">
-        <f>ROUND(入力!$B$19*C5,-3)</f>
-        <v/>
-      </c>
-      <c r="E5" s="9">
-        <f>ROUND(入力!$B$5*C5,-3)</f>
-        <v/>
-      </c>
-      <c r="F5" s="9">
-        <f>ROUND(E5*入力!$B$16,-3)</f>
-        <v/>
-      </c>
-      <c r="G5" s="9">
-        <f>E5-D5*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v/>
-      </c>
-      <c r="H5" s="9">
-        <f>SUM($G$5:G5)</f>
-        <v/>
-      </c>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="15">
-        <f>IF(I5="","",IF(I5&gt;=F5,2,IF(I5&gt;=E5,1,0)))</f>
-        <v/>
-      </c>
-      <c r="K5" s="9">
-        <f>IF(OR(J5="",J5=0),0,IF(J5=2,入力!$B$15,入力!$B$14))</f>
-        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>9月</t>
+          <t>8月</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>3638478</v>
+        <v>3040292</v>
       </c>
       <c r="C6" s="10">
-        <f>B6/SUM($B$5:$B$16)</f>
+        <f>B6/SUM($B$6:$B$17)</f>
         <v/>
       </c>
       <c r="D6" s="9">
-        <f>ROUND(入力!$B$19*C6,-3)</f>
+        <f>ROUND(F6/入力!$B$6,-4)</f>
         <v/>
       </c>
       <c r="E6" s="9">
         <f>ROUND(入力!$B$5*C6,-3)</f>
         <v/>
       </c>
-      <c r="F6" s="9">
-        <f>ROUND(E6*入力!$B$16,-3)</f>
-        <v/>
+      <c r="F6" s="4" t="n">
+        <v>1200000</v>
       </c>
       <c r="G6" s="9">
-        <f>E6-D6*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <f>ROUND(F6*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
       <c r="H6" s="9">
-        <f>SUM($G$5:G6)</f>
-        <v/>
-      </c>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="15">
-        <f>IF(I6="","",IF(I6&gt;=F6,2,IF(I6&gt;=E6,1,0)))</f>
-        <v/>
-      </c>
-      <c r="K6" s="9">
-        <f>IF(OR(J6="",J6=0),0,IF(J6=2,入力!$B$15,入力!$B$14))</f>
+        <f>F6-D6*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I6" s="9">
+        <f>SUM($H$6:H6)</f>
+        <v/>
+      </c>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="15">
+        <f>IF(J6="","",IF(J6&gt;=G6,2,IF(J6&gt;=F6,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L6" s="9">
+        <f>IF(OR(K6="",K6=0),0,IF(K6=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10月</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>4934704</v>
+        <v>3638478</v>
       </c>
       <c r="C7" s="10">
-        <f>B7/SUM($B$5:$B$16)</f>
+        <f>B7/SUM($B$6:$B$17)</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>ROUND(入力!$B$19*C7,-3)</f>
+        <f>ROUND(F7/入力!$B$6,-4)</f>
         <v/>
       </c>
       <c r="E7" s="9">
         <f>ROUND(入力!$B$5*C7,-3)</f>
         <v/>
       </c>
-      <c r="F7" s="9">
-        <f>ROUND(E7*入力!$B$16,-3)</f>
-        <v/>
+      <c r="F7" s="4" t="n">
+        <v>1450000</v>
       </c>
       <c r="G7" s="9">
-        <f>E7-D7*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <f>ROUND(F7*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
       <c r="H7" s="9">
-        <f>SUM($G$5:G7)</f>
-        <v/>
-      </c>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="15">
-        <f>IF(I7="","",IF(I7&gt;=F7,2,IF(I7&gt;=E7,1,0)))</f>
-        <v/>
-      </c>
-      <c r="K7" s="9">
-        <f>IF(OR(J7="",J7=0),0,IF(J7=2,入力!$B$15,入力!$B$14))</f>
+        <f>F7-D7*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I7" s="9">
+        <f>SUM($H$6:H7)</f>
+        <v/>
+      </c>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="15">
+        <f>IF(J7="","",IF(J7&gt;=G7,2,IF(J7&gt;=F7,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L7" s="9">
+        <f>IF(OR(K7="",K7=0),0,IF(K7=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>11月</t>
+          <t>10月</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>5149749</v>
+        <v>4934704</v>
       </c>
       <c r="C8" s="10">
-        <f>B8/SUM($B$5:$B$16)</f>
+        <f>B8/SUM($B$6:$B$17)</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>ROUND(入力!$B$19*C8,-3)</f>
+        <f>ROUND(F8/入力!$B$6,-4)</f>
         <v/>
       </c>
       <c r="E8" s="9">
         <f>ROUND(入力!$B$5*C8,-3)</f>
         <v/>
       </c>
-      <c r="F8" s="9">
-        <f>ROUND(E8*入力!$B$16,-3)</f>
-        <v/>
+      <c r="F8" s="4" t="n">
+        <v>2000000</v>
       </c>
       <c r="G8" s="9">
-        <f>E8-D8*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <f>ROUND(F8*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
       <c r="H8" s="9">
-        <f>SUM($G$5:G8)</f>
-        <v/>
-      </c>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="15">
-        <f>IF(I8="","",IF(I8&gt;=F8,2,IF(I8&gt;=E8,1,0)))</f>
-        <v/>
-      </c>
-      <c r="K8" s="9">
-        <f>IF(OR(J8="",J8=0),0,IF(J8=2,入力!$B$15,入力!$B$14))</f>
+        <f>F8-D8*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I8" s="9">
+        <f>SUM($H$6:H8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="15">
+        <f>IF(J8="","",IF(J8&gt;=G8,2,IF(J8&gt;=F8,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L8" s="9">
+        <f>IF(OR(K8="",K8=0),0,IF(K8=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12月</t>
+          <t>11月</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>6820952</v>
+        <v>5149749</v>
       </c>
       <c r="C9" s="10">
-        <f>B9/SUM($B$5:$B$16)</f>
+        <f>B9/SUM($B$6:$B$17)</f>
         <v/>
       </c>
       <c r="D9" s="9">
-        <f>ROUND(入力!$B$19*C9,-3)</f>
+        <f>ROUND(F9/入力!$B$6,-4)</f>
         <v/>
       </c>
       <c r="E9" s="9">
         <f>ROUND(入力!$B$5*C9,-3)</f>
         <v/>
       </c>
-      <c r="F9" s="9">
-        <f>ROUND(E9*入力!$B$16,-3)</f>
-        <v/>
+      <c r="F9" s="4" t="n">
+        <v>2050000</v>
       </c>
       <c r="G9" s="9">
-        <f>E9-D9*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <f>ROUND(F9*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
       <c r="H9" s="9">
-        <f>SUM($G$5:G9)</f>
-        <v/>
-      </c>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="15">
-        <f>IF(I9="","",IF(I9&gt;=F9,2,IF(I9&gt;=E9,1,0)))</f>
-        <v/>
-      </c>
-      <c r="K9" s="9">
-        <f>IF(OR(J9="",J9=0),0,IF(J9=2,入力!$B$15,入力!$B$14))</f>
+        <f>F9-D9*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I9" s="9">
+        <f>SUM($H$6:H9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="4" t="n"/>
+      <c r="K9" s="15">
+        <f>IF(J9="","",IF(J9&gt;=G9,2,IF(J9&gt;=F9,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L9" s="9">
+        <f>IF(OR(K9="",K9=0),0,IF(K9=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1月</t>
+          <t>12月</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>4850701</v>
+        <v>6820952</v>
       </c>
       <c r="C10" s="10">
-        <f>B10/SUM($B$5:$B$16)</f>
+        <f>B10/SUM($B$6:$B$17)</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>ROUND(入力!$B$19*C10,-3)</f>
+        <f>ROUND(F10/入力!$B$6,-4)</f>
         <v/>
       </c>
       <c r="E10" s="9">
         <f>ROUND(入力!$B$5*C10,-3)</f>
         <v/>
       </c>
-      <c r="F10" s="9">
-        <f>ROUND(E10*入力!$B$16,-3)</f>
-        <v/>
+      <c r="F10" s="4" t="n">
+        <v>2750000</v>
       </c>
       <c r="G10" s="9">
-        <f>E10-D10*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <f>ROUND(F10*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
       <c r="H10" s="9">
-        <f>SUM($G$5:G10)</f>
-        <v/>
-      </c>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="15">
-        <f>IF(I10="","",IF(I10&gt;=F10,2,IF(I10&gt;=E10,1,0)))</f>
-        <v/>
-      </c>
-      <c r="K10" s="9">
-        <f>IF(OR(J10="",J10=0),0,IF(J10=2,入力!$B$15,入力!$B$14))</f>
+        <f>F10-D10*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I10" s="9">
+        <f>SUM($H$6:H10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="4" t="n"/>
+      <c r="K10" s="15">
+        <f>IF(J10="","",IF(J10&gt;=G10,2,IF(J10&gt;=F10,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L10" s="9">
+        <f>IF(OR(K10="",K10=0),0,IF(K10=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2月</t>
+          <t>1月</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>2795656</v>
+        <v>4850701</v>
       </c>
       <c r="C11" s="10">
-        <f>B11/SUM($B$5:$B$16)</f>
+        <f>B11/SUM($B$6:$B$17)</f>
         <v/>
       </c>
       <c r="D11" s="9">
-        <f>ROUND(入力!$B$19*C11,-3)</f>
+        <f>ROUND(F11/入力!$B$6,-4)</f>
         <v/>
       </c>
       <c r="E11" s="9">
         <f>ROUND(入力!$B$5*C11,-3)</f>
         <v/>
       </c>
-      <c r="F11" s="9">
-        <f>ROUND(E11*入力!$B$16,-3)</f>
-        <v/>
+      <c r="F11" s="4" t="n">
+        <v>1950000</v>
       </c>
       <c r="G11" s="9">
-        <f>E11-D11*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <f>ROUND(F11*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
       <c r="H11" s="9">
-        <f>SUM($G$5:G11)</f>
-        <v/>
-      </c>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="15">
-        <f>IF(I11="","",IF(I11&gt;=F11,2,IF(I11&gt;=E11,1,0)))</f>
-        <v/>
-      </c>
-      <c r="K11" s="9">
-        <f>IF(OR(J11="",J11=0),0,IF(J11=2,入力!$B$15,入力!$B$14))</f>
+        <f>F11-D11*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I11" s="9">
+        <f>SUM($H$6:H11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="15">
+        <f>IF(J11="","",IF(J11&gt;=G11,2,IF(J11&gt;=F11,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L11" s="9">
+        <f>IF(OR(K11="",K11=0),0,IF(K11=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>3月</t>
+          <t>2月</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>4419804</v>
+        <v>2795656</v>
       </c>
       <c r="C12" s="10">
-        <f>B12/SUM($B$5:$B$16)</f>
+        <f>B12/SUM($B$6:$B$17)</f>
         <v/>
       </c>
       <c r="D12" s="9">
-        <f>ROUND(入力!$B$19*C12,-3)</f>
+        <f>ROUND(F12/入力!$B$6,-4)</f>
         <v/>
       </c>
       <c r="E12" s="9">
         <f>ROUND(入力!$B$5*C12,-3)</f>
         <v/>
       </c>
-      <c r="F12" s="9">
-        <f>ROUND(E12*入力!$B$16,-3)</f>
-        <v/>
+      <c r="F12" s="4" t="n">
+        <v>1100000</v>
       </c>
       <c r="G12" s="9">
-        <f>E12-D12*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <f>ROUND(F12*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
       <c r="H12" s="9">
-        <f>SUM($G$5:G12)</f>
-        <v/>
-      </c>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="15">
-        <f>IF(I12="","",IF(I12&gt;=F12,2,IF(I12&gt;=E12,1,0)))</f>
-        <v/>
-      </c>
-      <c r="K12" s="9">
-        <f>IF(OR(J12="",J12=0),0,IF(J12=2,入力!$B$15,入力!$B$14))</f>
+        <f>F12-D12*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I12" s="9">
+        <f>SUM($H$6:H12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="15">
+        <f>IF(J12="","",IF(J12&gt;=G12,2,IF(J12&gt;=F12,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L12" s="9">
+        <f>IF(OR(K12="",K12=0),0,IF(K12=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>4月</t>
+          <t>3月</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>3581469</v>
+        <v>4419804</v>
       </c>
       <c r="C13" s="10">
-        <f>B13/SUM($B$5:$B$16)</f>
+        <f>B13/SUM($B$6:$B$17)</f>
         <v/>
       </c>
       <c r="D13" s="9">
-        <f>ROUND(入力!$B$19*C13,-3)</f>
+        <f>ROUND(F13/入力!$B$6,-4)</f>
         <v/>
       </c>
       <c r="E13" s="9">
         <f>ROUND(入力!$B$5*C13,-3)</f>
         <v/>
       </c>
-      <c r="F13" s="9">
-        <f>ROUND(E13*入力!$B$16,-3)</f>
-        <v/>
+      <c r="F13" s="4" t="n">
+        <v>1750000</v>
       </c>
       <c r="G13" s="9">
-        <f>E13-D13*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <f>ROUND(F13*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
       <c r="H13" s="9">
-        <f>SUM($G$5:G13)</f>
-        <v/>
-      </c>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="15">
-        <f>IF(I13="","",IF(I13&gt;=F13,2,IF(I13&gt;=E13,1,0)))</f>
-        <v/>
-      </c>
-      <c r="K13" s="9">
-        <f>IF(OR(J13="",J13=0),0,IF(J13=2,入力!$B$15,入力!$B$14))</f>
+        <f>F13-D13*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I13" s="9">
+        <f>SUM($H$6:H13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="15">
+        <f>IF(J13="","",IF(J13&gt;=G13,2,IF(J13&gt;=F13,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L13" s="9">
+        <f>IF(OR(K13="",K13=0),0,IF(K13=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>5月</t>
+          <t>4月</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>4799124</v>
+        <v>3581469</v>
       </c>
       <c r="C14" s="10">
-        <f>B14/SUM($B$5:$B$16)</f>
+        <f>B14/SUM($B$6:$B$17)</f>
         <v/>
       </c>
       <c r="D14" s="9">
-        <f>ROUND(入力!$B$19*C14,-3)</f>
+        <f>ROUND(F14/入力!$B$6,-4)</f>
         <v/>
       </c>
       <c r="E14" s="9">
         <f>ROUND(入力!$B$5*C14,-3)</f>
         <v/>
       </c>
-      <c r="F14" s="9">
-        <f>ROUND(E14*入力!$B$16,-3)</f>
-        <v/>
+      <c r="F14" s="4" t="n">
+        <v>1450000</v>
       </c>
       <c r="G14" s="9">
-        <f>E14-D14*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <f>ROUND(F14*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
       <c r="H14" s="9">
-        <f>SUM($G$5:G14)</f>
-        <v/>
-      </c>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="15">
-        <f>IF(I14="","",IF(I14&gt;=F14,2,IF(I14&gt;=E14,1,0)))</f>
-        <v/>
-      </c>
-      <c r="K14" s="9">
-        <f>IF(OR(J14="",J14=0),0,IF(J14=2,入力!$B$15,入力!$B$14))</f>
+        <f>F14-D14*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I14" s="9">
+        <f>SUM($H$6:H14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="15">
+        <f>IF(J14="","",IF(J14&gt;=G14,2,IF(J14&gt;=F14,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L14" s="9">
+        <f>IF(OR(K14="",K14=0),0,IF(K14=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>6月</t>
+          <t>5月</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>4888307</v>
+        <v>4799124</v>
       </c>
       <c r="C15" s="10">
-        <f>B15/SUM($B$5:$B$16)</f>
+        <f>B15/SUM($B$6:$B$17)</f>
         <v/>
       </c>
       <c r="D15" s="9">
-        <f>ROUND(入力!$B$19*C15,-3)</f>
+        <f>ROUND(F15/入力!$B$6,-4)</f>
         <v/>
       </c>
       <c r="E15" s="9">
         <f>ROUND(入力!$B$5*C15,-3)</f>
         <v/>
       </c>
-      <c r="F15" s="9">
-        <f>ROUND(E15*入力!$B$16,-3)</f>
-        <v/>
+      <c r="F15" s="4" t="n">
+        <v>1950000</v>
       </c>
       <c r="G15" s="9">
-        <f>E15-D15*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <f>ROUND(F15*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
       <c r="H15" s="9">
-        <f>SUM($G$5:G15)</f>
-        <v/>
-      </c>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="15">
-        <f>IF(I15="","",IF(I15&gt;=F15,2,IF(I15&gt;=E15,1,0)))</f>
-        <v/>
-      </c>
-      <c r="K15" s="9">
-        <f>IF(OR(J15="",J15=0),0,IF(J15=2,入力!$B$15,入力!$B$14))</f>
+        <f>F15-D15*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I15" s="9">
+        <f>SUM($H$6:H15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="15">
+        <f>IF(J15="","",IF(J15&gt;=G15,2,IF(J15&gt;=F15,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L15" s="9">
+        <f>IF(OR(K15="",K15=0),0,IF(K15=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>7月</t>
+          <t>6月</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>4741065</v>
+        <v>4888307</v>
       </c>
       <c r="C16" s="10">
-        <f>B16/SUM($B$5:$B$16)</f>
+        <f>B16/SUM($B$6:$B$17)</f>
         <v/>
       </c>
       <c r="D16" s="9">
-        <f>ROUND(入力!$B$19*C16,-3)</f>
+        <f>ROUND(F16/入力!$B$6,-4)</f>
         <v/>
       </c>
       <c r="E16" s="9">
         <f>ROUND(入力!$B$5*C16,-3)</f>
         <v/>
       </c>
-      <c r="F16" s="9">
-        <f>ROUND(E16*入力!$B$16,-3)</f>
-        <v/>
+      <c r="F16" s="4" t="n">
+        <v>1950000</v>
       </c>
       <c r="G16" s="9">
-        <f>E16-D16*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <f>ROUND(F16*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
       <c r="H16" s="9">
-        <f>SUM($G$5:G16)</f>
-        <v/>
-      </c>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="15">
-        <f>IF(I16="","",IF(I16&gt;=F16,2,IF(I16&gt;=E16,1,0)))</f>
-        <v/>
-      </c>
-      <c r="K16" s="9">
-        <f>IF(OR(J16="",J16=0),0,IF(J16=2,入力!$B$15,入力!$B$14))</f>
+        <f>F16-D16*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I16" s="9">
+        <f>SUM($H$6:H16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="15">
+        <f>IF(J16="","",IF(J16&gt;=G16,2,IF(J16&gt;=F16,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L16" s="9">
+        <f>IF(OR(K16="",K16=0),0,IF(K16=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>7月</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>4741065</v>
+      </c>
+      <c r="C17" s="10">
+        <f>B17/SUM($B$6:$B$17)</f>
+        <v/>
+      </c>
+      <c r="D17" s="9">
+        <f>ROUND(F17/入力!$B$6,-4)</f>
+        <v/>
+      </c>
+      <c r="E17" s="9">
+        <f>ROUND(入力!$B$5*C17,-3)</f>
+        <v/>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="G17" s="9">
+        <f>ROUND(F17*入力!$B$16/50000,0)*50000</f>
+        <v/>
+      </c>
+      <c r="H17" s="9">
+        <f>F17-D17*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I17" s="9">
+        <f>SUM($H$6:H17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="15">
+        <f>IF(J17="","",IF(J17&gt;=G17,2,IF(J17&gt;=F17,1,0)))</f>
+        <v/>
+      </c>
+      <c r="L17" s="9">
+        <f>IF(OR(K17="",K17=0),0,IF(K17=2,入力!$B$15,入力!$B$14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>年計</t>
         </is>
       </c>
-      <c r="B17" s="14">
-        <f>SUM(B5:B16)</f>
-        <v/>
-      </c>
-      <c r="D17" s="14">
-        <f>SUM(D5:D16)</f>
-        <v/>
-      </c>
-      <c r="E17" s="14">
-        <f>SUM(E5:E16)</f>
-        <v/>
-      </c>
-      <c r="F17" s="14">
-        <f>SUM(F5:F16)</f>
-        <v/>
-      </c>
-      <c r="G17" s="14">
-        <f>SUM(G5:G16)</f>
-        <v/>
-      </c>
-      <c r="I17" s="14">
-        <f>SUM(I5:I16)</f>
-        <v/>
-      </c>
-      <c r="K17" s="14">
-        <f>SUM(K5:K16)</f>
-        <v/>
+      <c r="B18" s="14">
+        <f>SUM(B6:B17)</f>
+        <v/>
+      </c>
+      <c r="D18" s="14">
+        <f>SUM(D6:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="14">
+        <f>SUM(E6:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="14">
+        <f>SUM(F6:F17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="14">
+        <f>SUM(G6:G17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="14">
+        <f>SUM(H6:H17)</f>
+        <v/>
+      </c>
+      <c r="J18" s="14">
+        <f>SUM(J6:J17)</f>
+        <v/>
+      </c>
+      <c r="L18" s="14">
+        <f>SUM(L6:L17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>年間目標との差</t>
+        </is>
+      </c>
+      <c r="F19" s="9">
+        <f>F18-入力!B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>（丸めた目標を直したら、F19が0円になるように調整してください）</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2514,21 +2586,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2541,669 +2614,739 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>月の目標は、店長がスマレジに登録した店舗予算（年6,000万円・税抜）の月比率で配分。前年構成比版との差も表示。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+          <t>月の目標は、店長がスマレジに登録した店舗予算（年6,000万円・税抜）の月比率で配分。同じ予算額の月は同じ目標にそろえた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>黄色の「粗利目標100%」は5万円単位に丸めた目標（年計2,150万円に合わせて調整済み）。105%は5万円単位。目標売上は粗利目標÷粗利率を1万円単位で表示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>スマレジ予算（参考）</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>月比率</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>目標売上</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>比率</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>目標売上（参考）</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>粗利目標（丸め前）</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>粗利目標100%</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>粗利目標105%</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>営業利益（100%時）</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>累計</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>構成比版との差（粗利目標）</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>実績粗利</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>報奨金</t>
         </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>8月</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="C5" s="10">
-        <f>B5/SUM($B$5:$B$16)</f>
-        <v/>
-      </c>
-      <c r="D5" s="9">
-        <f>ROUND(入力!$B$19*C5,-3)</f>
-        <v/>
-      </c>
-      <c r="E5" s="9">
-        <f>ROUND(入力!$B$5*C5,-3)</f>
-        <v/>
-      </c>
-      <c r="F5" s="9">
-        <f>ROUND(E5*入力!$B$16,-3)</f>
-        <v/>
-      </c>
-      <c r="G5" s="9">
-        <f>E5-D5*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v/>
-      </c>
-      <c r="H5" s="9">
-        <f>SUM($G$5:G5)</f>
-        <v/>
-      </c>
-      <c r="I5" s="9">
-        <f>E5-'月別目標と営業利益'!E5</f>
-        <v/>
-      </c>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="15">
-        <f>IF(J5="","",IF(J5&gt;=F5,2,IF(J5&gt;=E5,1,0)))</f>
-        <v/>
-      </c>
-      <c r="L5" s="9">
-        <f>IF(OR(K5="",K5=0),0,IF(K5=2,入力!$B$15,入力!$B$14))</f>
-        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>9月</t>
+          <t>8月</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>4500000</v>
+        <v>3500000</v>
       </c>
       <c r="C6" s="10">
-        <f>B6/SUM($B$5:$B$16)</f>
+        <f>B6/SUM($B$6:$B$17)</f>
         <v/>
       </c>
       <c r="D6" s="9">
-        <f>ROUND(入力!$B$19*C6,-3)</f>
+        <f>ROUND(F6/入力!$B$6,-4)</f>
         <v/>
       </c>
       <c r="E6" s="9">
         <f>ROUND(入力!$B$5*C6,-3)</f>
         <v/>
       </c>
-      <c r="F6" s="9">
-        <f>ROUND(E6*入力!$B$16,-3)</f>
-        <v/>
+      <c r="F6" s="4" t="n">
+        <v>1250000</v>
       </c>
       <c r="G6" s="9">
-        <f>E6-D6*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <f>ROUND(F6*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
       <c r="H6" s="9">
-        <f>SUM($G$5:G6)</f>
+        <f>F6-D6*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
       <c r="I6" s="9">
-        <f>E6-'月別目標と営業利益'!E6</f>
-        <v/>
-      </c>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="15">
-        <f>IF(J6="","",IF(J6&gt;=F6,2,IF(J6&gt;=E6,1,0)))</f>
-        <v/>
-      </c>
-      <c r="L6" s="9">
-        <f>IF(OR(K6="",K6=0),0,IF(K6=2,入力!$B$15,入力!$B$14))</f>
+        <f>SUM($H$6:H6)</f>
+        <v/>
+      </c>
+      <c r="J6" s="9">
+        <f>F6-'月別目標と営業利益'!F6</f>
+        <v/>
+      </c>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="15">
+        <f>IF(K6="","",IF(K6&gt;=G6,2,IF(K6&gt;=F6,1,0)))</f>
+        <v/>
+      </c>
+      <c r="M6" s="9">
+        <f>IF(OR(L6="",L6=0),0,IF(L6=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10月</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>5500000</v>
+        <v>4500000</v>
       </c>
       <c r="C7" s="10">
-        <f>B7/SUM($B$5:$B$16)</f>
+        <f>B7/SUM($B$6:$B$17)</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>ROUND(入力!$B$19*C7,-3)</f>
+        <f>ROUND(F7/入力!$B$6,-4)</f>
         <v/>
       </c>
       <c r="E7" s="9">
         <f>ROUND(入力!$B$5*C7,-3)</f>
         <v/>
       </c>
-      <c r="F7" s="9">
-        <f>ROUND(E7*入力!$B$16,-3)</f>
-        <v/>
+      <c r="F7" s="4" t="n">
+        <v>1600000</v>
       </c>
       <c r="G7" s="9">
-        <f>E7-D7*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <f>ROUND(F7*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
       <c r="H7" s="9">
-        <f>SUM($G$5:G7)</f>
+        <f>F7-D7*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
       <c r="I7" s="9">
-        <f>E7-'月別目標と営業利益'!E7</f>
-        <v/>
-      </c>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="15">
-        <f>IF(J7="","",IF(J7&gt;=F7,2,IF(J7&gt;=E7,1,0)))</f>
-        <v/>
-      </c>
-      <c r="L7" s="9">
-        <f>IF(OR(K7="",K7=0),0,IF(K7=2,入力!$B$15,入力!$B$14))</f>
+        <f>SUM($H$6:H7)</f>
+        <v/>
+      </c>
+      <c r="J7" s="9">
+        <f>F7-'月別目標と営業利益'!F7</f>
+        <v/>
+      </c>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="15">
+        <f>IF(K7="","",IF(K7&gt;=G7,2,IF(K7&gt;=F7,1,0)))</f>
+        <v/>
+      </c>
+      <c r="M7" s="9">
+        <f>IF(OR(L7="",L7=0),0,IF(L7=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>11月</t>
+          <t>10月</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
         <v>5500000</v>
       </c>
       <c r="C8" s="10">
-        <f>B8/SUM($B$5:$B$16)</f>
+        <f>B8/SUM($B$6:$B$17)</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>ROUND(入力!$B$19*C8,-3)</f>
+        <f>ROUND(F8/入力!$B$6,-4)</f>
         <v/>
       </c>
       <c r="E8" s="9">
         <f>ROUND(入力!$B$5*C8,-3)</f>
         <v/>
       </c>
-      <c r="F8" s="9">
-        <f>ROUND(E8*入力!$B$16,-3)</f>
-        <v/>
+      <c r="F8" s="4" t="n">
+        <v>2000000</v>
       </c>
       <c r="G8" s="9">
-        <f>E8-D8*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <f>ROUND(F8*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
       <c r="H8" s="9">
-        <f>SUM($G$5:G8)</f>
+        <f>F8-D8*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
       <c r="I8" s="9">
-        <f>E8-'月別目標と営業利益'!E8</f>
-        <v/>
-      </c>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="15">
-        <f>IF(J8="","",IF(J8&gt;=F8,2,IF(J8&gt;=E8,1,0)))</f>
-        <v/>
-      </c>
-      <c r="L8" s="9">
-        <f>IF(OR(K8="",K8=0),0,IF(K8=2,入力!$B$15,入力!$B$14))</f>
+        <f>SUM($H$6:H8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="9">
+        <f>F8-'月別目標と営業利益'!F8</f>
+        <v/>
+      </c>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="15">
+        <f>IF(K8="","",IF(K8&gt;=G8,2,IF(K8&gt;=F8,1,0)))</f>
+        <v/>
+      </c>
+      <c r="M8" s="9">
+        <f>IF(OR(L8="",L8=0),0,IF(L8=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12月</t>
+          <t>11月</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>7000000</v>
+        <v>5500000</v>
       </c>
       <c r="C9" s="10">
-        <f>B9/SUM($B$5:$B$16)</f>
+        <f>B9/SUM($B$6:$B$17)</f>
         <v/>
       </c>
       <c r="D9" s="9">
-        <f>ROUND(入力!$B$19*C9,-3)</f>
+        <f>ROUND(F9/入力!$B$6,-4)</f>
         <v/>
       </c>
       <c r="E9" s="9">
         <f>ROUND(入力!$B$5*C9,-3)</f>
         <v/>
       </c>
-      <c r="F9" s="9">
-        <f>ROUND(E9*入力!$B$16,-3)</f>
-        <v/>
+      <c r="F9" s="4" t="n">
+        <v>2000000</v>
       </c>
       <c r="G9" s="9">
-        <f>E9-D9*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <f>ROUND(F9*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
       <c r="H9" s="9">
-        <f>SUM($G$5:G9)</f>
+        <f>F9-D9*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
       <c r="I9" s="9">
-        <f>E9-'月別目標と営業利益'!E9</f>
-        <v/>
-      </c>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="15">
-        <f>IF(J9="","",IF(J9&gt;=F9,2,IF(J9&gt;=E9,1,0)))</f>
-        <v/>
-      </c>
-      <c r="L9" s="9">
-        <f>IF(OR(K9="",K9=0),0,IF(K9=2,入力!$B$15,入力!$B$14))</f>
+        <f>SUM($H$6:H9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="9">
+        <f>F9-'月別目標と営業利益'!F9</f>
+        <v/>
+      </c>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="15">
+        <f>IF(K9="","",IF(K9&gt;=G9,2,IF(K9&gt;=F9,1,0)))</f>
+        <v/>
+      </c>
+      <c r="M9" s="9">
+        <f>IF(OR(L9="",L9=0),0,IF(L9=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1月</t>
+          <t>12月</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>6000000</v>
+        <v>7000000</v>
       </c>
       <c r="C10" s="10">
-        <f>B10/SUM($B$5:$B$16)</f>
+        <f>B10/SUM($B$6:$B$17)</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>ROUND(入力!$B$19*C10,-3)</f>
+        <f>ROUND(F10/入力!$B$6,-4)</f>
         <v/>
       </c>
       <c r="E10" s="9">
         <f>ROUND(入力!$B$5*C10,-3)</f>
         <v/>
       </c>
-      <c r="F10" s="9">
-        <f>ROUND(E10*入力!$B$16,-3)</f>
-        <v/>
+      <c r="F10" s="4" t="n">
+        <v>2500000</v>
       </c>
       <c r="G10" s="9">
-        <f>E10-D10*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <f>ROUND(F10*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
       <c r="H10" s="9">
-        <f>SUM($G$5:G10)</f>
+        <f>F10-D10*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
       <c r="I10" s="9">
-        <f>E10-'月別目標と営業利益'!E10</f>
-        <v/>
-      </c>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="15">
-        <f>IF(J10="","",IF(J10&gt;=F10,2,IF(J10&gt;=E10,1,0)))</f>
-        <v/>
-      </c>
-      <c r="L10" s="9">
-        <f>IF(OR(K10="",K10=0),0,IF(K10=2,入力!$B$15,入力!$B$14))</f>
+        <f>SUM($H$6:H10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="9">
+        <f>F10-'月別目標と営業利益'!F10</f>
+        <v/>
+      </c>
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="15">
+        <f>IF(K10="","",IF(K10&gt;=G10,2,IF(K10&gt;=F10,1,0)))</f>
+        <v/>
+      </c>
+      <c r="M10" s="9">
+        <f>IF(OR(L10="",L10=0),0,IF(L10=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2月</t>
+          <t>1月</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>3500000</v>
+        <v>6000000</v>
       </c>
       <c r="C11" s="10">
-        <f>B11/SUM($B$5:$B$16)</f>
+        <f>B11/SUM($B$6:$B$17)</f>
         <v/>
       </c>
       <c r="D11" s="9">
-        <f>ROUND(入力!$B$19*C11,-3)</f>
+        <f>ROUND(F11/入力!$B$6,-4)</f>
         <v/>
       </c>
       <c r="E11" s="9">
         <f>ROUND(入力!$B$5*C11,-3)</f>
         <v/>
       </c>
-      <c r="F11" s="9">
-        <f>ROUND(E11*入力!$B$16,-3)</f>
-        <v/>
+      <c r="F11" s="4" t="n">
+        <v>2100000</v>
       </c>
       <c r="G11" s="9">
-        <f>E11-D11*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <f>ROUND(F11*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
       <c r="H11" s="9">
-        <f>SUM($G$5:G11)</f>
+        <f>F11-D11*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
       <c r="I11" s="9">
-        <f>E11-'月別目標と営業利益'!E11</f>
-        <v/>
-      </c>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="15">
-        <f>IF(J11="","",IF(J11&gt;=F11,2,IF(J11&gt;=E11,1,0)))</f>
-        <v/>
-      </c>
-      <c r="L11" s="9">
-        <f>IF(OR(K11="",K11=0),0,IF(K11=2,入力!$B$15,入力!$B$14))</f>
+        <f>SUM($H$6:H11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="9">
+        <f>F11-'月別目標と営業利益'!F11</f>
+        <v/>
+      </c>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="15">
+        <f>IF(K11="","",IF(K11&gt;=G11,2,IF(K11&gt;=F11,1,0)))</f>
+        <v/>
+      </c>
+      <c r="M11" s="9">
+        <f>IF(OR(L11="",L11=0),0,IF(L11=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>3月</t>
+          <t>2月</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>5500000</v>
+        <v>3500000</v>
       </c>
       <c r="C12" s="10">
-        <f>B12/SUM($B$5:$B$16)</f>
+        <f>B12/SUM($B$6:$B$17)</f>
         <v/>
       </c>
       <c r="D12" s="9">
-        <f>ROUND(入力!$B$19*C12,-3)</f>
+        <f>ROUND(F12/入力!$B$6,-4)</f>
         <v/>
       </c>
       <c r="E12" s="9">
         <f>ROUND(入力!$B$5*C12,-3)</f>
         <v/>
       </c>
-      <c r="F12" s="9">
-        <f>ROUND(E12*入力!$B$16,-3)</f>
-        <v/>
+      <c r="F12" s="4" t="n">
+        <v>1250000</v>
       </c>
       <c r="G12" s="9">
-        <f>E12-D12*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <f>ROUND(F12*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
       <c r="H12" s="9">
-        <f>SUM($G$5:G12)</f>
+        <f>F12-D12*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
       <c r="I12" s="9">
-        <f>E12-'月別目標と営業利益'!E12</f>
-        <v/>
-      </c>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="15">
-        <f>IF(J12="","",IF(J12&gt;=F12,2,IF(J12&gt;=E12,1,0)))</f>
-        <v/>
-      </c>
-      <c r="L12" s="9">
-        <f>IF(OR(K12="",K12=0),0,IF(K12=2,入力!$B$15,入力!$B$14))</f>
+        <f>SUM($H$6:H12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="9">
+        <f>F12-'月別目標と営業利益'!F12</f>
+        <v/>
+      </c>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="15">
+        <f>IF(K12="","",IF(K12&gt;=G12,2,IF(K12&gt;=F12,1,0)))</f>
+        <v/>
+      </c>
+      <c r="M12" s="9">
+        <f>IF(OR(L12="",L12=0),0,IF(L12=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>4月</t>
+          <t>3月</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>4500000</v>
+        <v>5500000</v>
       </c>
       <c r="C13" s="10">
-        <f>B13/SUM($B$5:$B$16)</f>
+        <f>B13/SUM($B$6:$B$17)</f>
         <v/>
       </c>
       <c r="D13" s="9">
-        <f>ROUND(入力!$B$19*C13,-3)</f>
+        <f>ROUND(F13/入力!$B$6,-4)</f>
         <v/>
       </c>
       <c r="E13" s="9">
         <f>ROUND(入力!$B$5*C13,-3)</f>
         <v/>
       </c>
-      <c r="F13" s="9">
-        <f>ROUND(E13*入力!$B$16,-3)</f>
-        <v/>
+      <c r="F13" s="4" t="n">
+        <v>2000000</v>
       </c>
       <c r="G13" s="9">
-        <f>E13-D13*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <f>ROUND(F13*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
       <c r="H13" s="9">
-        <f>SUM($G$5:G13)</f>
+        <f>F13-D13*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
       <c r="I13" s="9">
-        <f>E13-'月別目標と営業利益'!E13</f>
-        <v/>
-      </c>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="15">
-        <f>IF(J13="","",IF(J13&gt;=F13,2,IF(J13&gt;=E13,1,0)))</f>
-        <v/>
-      </c>
-      <c r="L13" s="9">
-        <f>IF(OR(K13="",K13=0),0,IF(K13=2,入力!$B$15,入力!$B$14))</f>
+        <f>SUM($H$6:H13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="9">
+        <f>F13-'月別目標と営業利益'!F13</f>
+        <v/>
+      </c>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="15">
+        <f>IF(K13="","",IF(K13&gt;=G13,2,IF(K13&gt;=F13,1,0)))</f>
+        <v/>
+      </c>
+      <c r="M13" s="9">
+        <f>IF(OR(L13="",L13=0),0,IF(L13=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>5月</t>
+          <t>4月</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
         <v>4500000</v>
       </c>
       <c r="C14" s="10">
-        <f>B14/SUM($B$5:$B$16)</f>
+        <f>B14/SUM($B$6:$B$17)</f>
         <v/>
       </c>
       <c r="D14" s="9">
-        <f>ROUND(入力!$B$19*C14,-3)</f>
+        <f>ROUND(F14/入力!$B$6,-4)</f>
         <v/>
       </c>
       <c r="E14" s="9">
         <f>ROUND(入力!$B$5*C14,-3)</f>
         <v/>
       </c>
-      <c r="F14" s="9">
-        <f>ROUND(E14*入力!$B$16,-3)</f>
-        <v/>
+      <c r="F14" s="4" t="n">
+        <v>1600000</v>
       </c>
       <c r="G14" s="9">
-        <f>E14-D14*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <f>ROUND(F14*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
       <c r="H14" s="9">
-        <f>SUM($G$5:G14)</f>
+        <f>F14-D14*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
       <c r="I14" s="9">
-        <f>E14-'月別目標と営業利益'!E14</f>
-        <v/>
-      </c>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="15">
-        <f>IF(J14="","",IF(J14&gt;=F14,2,IF(J14&gt;=E14,1,0)))</f>
-        <v/>
-      </c>
-      <c r="L14" s="9">
-        <f>IF(OR(K14="",K14=0),0,IF(K14=2,入力!$B$15,入力!$B$14))</f>
+        <f>SUM($H$6:H14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="9">
+        <f>F14-'月別目標と営業利益'!F14</f>
+        <v/>
+      </c>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="15">
+        <f>IF(K14="","",IF(K14&gt;=G14,2,IF(K14&gt;=F14,1,0)))</f>
+        <v/>
+      </c>
+      <c r="M14" s="9">
+        <f>IF(OR(L14="",L14=0),0,IF(L14=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>6月</t>
+          <t>5月</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>5500000</v>
+        <v>4500000</v>
       </c>
       <c r="C15" s="10">
-        <f>B15/SUM($B$5:$B$16)</f>
+        <f>B15/SUM($B$6:$B$17)</f>
         <v/>
       </c>
       <c r="D15" s="9">
-        <f>ROUND(入力!$B$19*C15,-3)</f>
+        <f>ROUND(F15/入力!$B$6,-4)</f>
         <v/>
       </c>
       <c r="E15" s="9">
         <f>ROUND(入力!$B$5*C15,-3)</f>
         <v/>
       </c>
-      <c r="F15" s="9">
-        <f>ROUND(E15*入力!$B$16,-3)</f>
-        <v/>
+      <c r="F15" s="4" t="n">
+        <v>1600000</v>
       </c>
       <c r="G15" s="9">
-        <f>E15-D15*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <f>ROUND(F15*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
       <c r="H15" s="9">
-        <f>SUM($G$5:G15)</f>
+        <f>F15-D15*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
       <c r="I15" s="9">
-        <f>E15-'月別目標と営業利益'!E15</f>
-        <v/>
-      </c>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="15">
-        <f>IF(J15="","",IF(J15&gt;=F15,2,IF(J15&gt;=E15,1,0)))</f>
-        <v/>
-      </c>
-      <c r="L15" s="9">
-        <f>IF(OR(K15="",K15=0),0,IF(K15=2,入力!$B$15,入力!$B$14))</f>
+        <f>SUM($H$6:H15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="9">
+        <f>F15-'月別目標と営業利益'!F15</f>
+        <v/>
+      </c>
+      <c r="K15" s="4" t="n"/>
+      <c r="L15" s="15">
+        <f>IF(K15="","",IF(K15&gt;=G15,2,IF(K15&gt;=F15,1,0)))</f>
+        <v/>
+      </c>
+      <c r="M15" s="9">
+        <f>IF(OR(L15="",L15=0),0,IF(L15=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>7月</t>
+          <t>6月</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>4500000</v>
+        <v>5500000</v>
       </c>
       <c r="C16" s="10">
-        <f>B16/SUM($B$5:$B$16)</f>
+        <f>B16/SUM($B$6:$B$17)</f>
         <v/>
       </c>
       <c r="D16" s="9">
-        <f>ROUND(入力!$B$19*C16,-3)</f>
+        <f>ROUND(F16/入力!$B$6,-4)</f>
         <v/>
       </c>
       <c r="E16" s="9">
         <f>ROUND(入力!$B$5*C16,-3)</f>
         <v/>
       </c>
-      <c r="F16" s="9">
-        <f>ROUND(E16*入力!$B$16,-3)</f>
-        <v/>
+      <c r="F16" s="4" t="n">
+        <v>2000000</v>
       </c>
       <c r="G16" s="9">
-        <f>E16-D16*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <f>ROUND(F16*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
       <c r="H16" s="9">
-        <f>SUM($G$5:G16)</f>
+        <f>F16-D16*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
       <c r="I16" s="9">
-        <f>E16-'月別目標と営業利益'!E16</f>
-        <v/>
-      </c>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="15">
-        <f>IF(J16="","",IF(J16&gt;=F16,2,IF(J16&gt;=E16,1,0)))</f>
-        <v/>
-      </c>
-      <c r="L16" s="9">
-        <f>IF(OR(K16="",K16=0),0,IF(K16=2,入力!$B$15,入力!$B$14))</f>
+        <f>SUM($H$6:H16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="9">
+        <f>F16-'月別目標と営業利益'!F16</f>
+        <v/>
+      </c>
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="15">
+        <f>IF(K16="","",IF(K16&gt;=G16,2,IF(K16&gt;=F16,1,0)))</f>
+        <v/>
+      </c>
+      <c r="M16" s="9">
+        <f>IF(OR(L16="",L16=0),0,IF(L16=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>7月</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="C17" s="10">
+        <f>B17/SUM($B$6:$B$17)</f>
+        <v/>
+      </c>
+      <c r="D17" s="9">
+        <f>ROUND(F17/入力!$B$6,-4)</f>
+        <v/>
+      </c>
+      <c r="E17" s="9">
+        <f>ROUND(入力!$B$5*C17,-3)</f>
+        <v/>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="G17" s="9">
+        <f>ROUND(F17*入力!$B$16/50000,0)*50000</f>
+        <v/>
+      </c>
+      <c r="H17" s="9">
+        <f>F17-D17*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I17" s="9">
+        <f>SUM($H$6:H17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="9">
+        <f>F17-'月別目標と営業利益'!F17</f>
+        <v/>
+      </c>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="15">
+        <f>IF(K17="","",IF(K17&gt;=G17,2,IF(K17&gt;=F17,1,0)))</f>
+        <v/>
+      </c>
+      <c r="M17" s="9">
+        <f>IF(OR(L17="",L17=0),0,IF(L17=2,入力!$B$15,入力!$B$14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>年計</t>
         </is>
       </c>
-      <c r="B17" s="14">
-        <f>SUM(B5:B16)</f>
-        <v/>
-      </c>
-      <c r="D17" s="14">
-        <f>SUM(D5:D16)</f>
-        <v/>
-      </c>
-      <c r="E17" s="14">
-        <f>SUM(E5:E16)</f>
-        <v/>
-      </c>
-      <c r="F17" s="14">
-        <f>SUM(F5:F16)</f>
-        <v/>
-      </c>
-      <c r="G17" s="14">
-        <f>SUM(G5:G16)</f>
-        <v/>
-      </c>
-      <c r="J17" s="14">
-        <f>SUM(J5:J16)</f>
-        <v/>
-      </c>
-      <c r="L17" s="14">
-        <f>SUM(L5:L16)</f>
-        <v/>
+      <c r="B18" s="14">
+        <f>SUM(B6:B17)</f>
+        <v/>
+      </c>
+      <c r="D18" s="14">
+        <f>SUM(D6:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="14">
+        <f>SUM(E6:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="14">
+        <f>SUM(F6:F17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="14">
+        <f>SUM(G6:G17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="14">
+        <f>SUM(H6:H17)</f>
+        <v/>
+      </c>
+      <c r="K18" s="14">
+        <f>SUM(K6:K17)</f>
+        <v/>
+      </c>
+      <c r="M18" s="14">
+        <f>SUM(M6:M17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>年間目標との差</t>
+        </is>
+      </c>
+      <c r="F19" s="9">
+        <f>F18-入力!B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>（丸めた目標を直したら、F19が0円になるように調整してください）</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/excel/Weekends_予算と報奨金案_粗利2150万円.xlsx
+++ b/excel/Weekends_予算と報奨金案_粗利2150万円.xlsx
@@ -7,13 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="入力" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="年間損益" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="達成度別" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="粗利率別" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="月別目標と営業利益" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="月別（スマレジ版）" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="報奨金（例B）" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="目標設定" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="入力" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="年間損益" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="達成度別" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="粗利率別" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="月別目標と営業利益" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="月別（スマレジ版）" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="報奨金（例B）" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -91,27 +92,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -880,6 +882,723 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Weekends 2027年度 月別目標（粗利2,150万円・税抜）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>金額はすべて税抜。判定はスマレジの粗利（税抜）で毎月行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>目標の配分</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>1＝スマレジ版（店長が登録した予算の月比率・おすすめ）　2＝構成比版（前年の売上構成比）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>日数</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>粗利目標（100%）</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>粗利目標（105%）</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>売上の目安（粗利率35%）</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1日あたり粗利目標</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>1日あたり売上の目安</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>報奨金 第1段階（店舗計）</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>報奨金 第2段階（店舗計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="C6" s="7">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!F6,'月別目標と営業利益'!F6)</f>
+        <v/>
+      </c>
+      <c r="D6" s="8">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!G6,'月別目標と営業利益'!G6)</f>
+        <v/>
+      </c>
+      <c r="E6" s="8">
+        <f>ROUND(C6/入力!$B$6,-4)</f>
+        <v/>
+      </c>
+      <c r="F6" s="8">
+        <f>ROUND(C6/B6,-3)</f>
+        <v/>
+      </c>
+      <c r="G6" s="8">
+        <f>ROUND(E6/B6,-3)</f>
+        <v/>
+      </c>
+      <c r="H6" s="8">
+        <f>入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I6" s="8">
+        <f>入力!$B$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="C7" s="7">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!F7,'月別目標と営業利益'!F7)</f>
+        <v/>
+      </c>
+      <c r="D7" s="8">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!G7,'月別目標と営業利益'!G7)</f>
+        <v/>
+      </c>
+      <c r="E7" s="8">
+        <f>ROUND(C7/入力!$B$6,-4)</f>
+        <v/>
+      </c>
+      <c r="F7" s="8">
+        <f>ROUND(C7/B7,-3)</f>
+        <v/>
+      </c>
+      <c r="G7" s="8">
+        <f>ROUND(E7/B7,-3)</f>
+        <v/>
+      </c>
+      <c r="H7" s="8">
+        <f>入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I7" s="8">
+        <f>入力!$B$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>10月</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="C8" s="7">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!F8,'月別目標と営業利益'!F8)</f>
+        <v/>
+      </c>
+      <c r="D8" s="8">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!G8,'月別目標と営業利益'!G8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="8">
+        <f>ROUND(C8/入力!$B$6,-4)</f>
+        <v/>
+      </c>
+      <c r="F8" s="8">
+        <f>ROUND(C8/B8,-3)</f>
+        <v/>
+      </c>
+      <c r="G8" s="8">
+        <f>ROUND(E8/B8,-3)</f>
+        <v/>
+      </c>
+      <c r="H8" s="8">
+        <f>入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I8" s="8">
+        <f>入力!$B$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="C9" s="7">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!F9,'月別目標と営業利益'!F9)</f>
+        <v/>
+      </c>
+      <c r="D9" s="8">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!G9,'月別目標と営業利益'!G9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="8">
+        <f>ROUND(C9/入力!$B$6,-4)</f>
+        <v/>
+      </c>
+      <c r="F9" s="8">
+        <f>ROUND(C9/B9,-3)</f>
+        <v/>
+      </c>
+      <c r="G9" s="8">
+        <f>ROUND(E9/B9,-3)</f>
+        <v/>
+      </c>
+      <c r="H9" s="8">
+        <f>入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I9" s="8">
+        <f>入力!$B$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>12月</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="C10" s="7">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!F10,'月別目標と営業利益'!F10)</f>
+        <v/>
+      </c>
+      <c r="D10" s="8">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!G10,'月別目標と営業利益'!G10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="8">
+        <f>ROUND(C10/入力!$B$6,-4)</f>
+        <v/>
+      </c>
+      <c r="F10" s="8">
+        <f>ROUND(C10/B10,-3)</f>
+        <v/>
+      </c>
+      <c r="G10" s="8">
+        <f>ROUND(E10/B10,-3)</f>
+        <v/>
+      </c>
+      <c r="H10" s="8">
+        <f>入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I10" s="8">
+        <f>入力!$B$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>1月</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="C11" s="7">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!F11,'月別目標と営業利益'!F11)</f>
+        <v/>
+      </c>
+      <c r="D11" s="8">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!G11,'月別目標と営業利益'!G11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="8">
+        <f>ROUND(C11/入力!$B$6,-4)</f>
+        <v/>
+      </c>
+      <c r="F11" s="8">
+        <f>ROUND(C11/B11,-3)</f>
+        <v/>
+      </c>
+      <c r="G11" s="8">
+        <f>ROUND(E11/B11,-3)</f>
+        <v/>
+      </c>
+      <c r="H11" s="8">
+        <f>入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I11" s="8">
+        <f>入力!$B$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2月</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="C12" s="7">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!F12,'月別目標と営業利益'!F12)</f>
+        <v/>
+      </c>
+      <c r="D12" s="8">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!G12,'月別目標と営業利益'!G12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="8">
+        <f>ROUND(C12/入力!$B$6,-4)</f>
+        <v/>
+      </c>
+      <c r="F12" s="8">
+        <f>ROUND(C12/B12,-3)</f>
+        <v/>
+      </c>
+      <c r="G12" s="8">
+        <f>ROUND(E12/B12,-3)</f>
+        <v/>
+      </c>
+      <c r="H12" s="8">
+        <f>入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I12" s="8">
+        <f>入力!$B$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="C13" s="7">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!F13,'月別目標と営業利益'!F13)</f>
+        <v/>
+      </c>
+      <c r="D13" s="8">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!G13,'月別目標と営業利益'!G13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="8">
+        <f>ROUND(C13/入力!$B$6,-4)</f>
+        <v/>
+      </c>
+      <c r="F13" s="8">
+        <f>ROUND(C13/B13,-3)</f>
+        <v/>
+      </c>
+      <c r="G13" s="8">
+        <f>ROUND(E13/B13,-3)</f>
+        <v/>
+      </c>
+      <c r="H13" s="8">
+        <f>入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I13" s="8">
+        <f>入力!$B$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="C14" s="7">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!F14,'月別目標と営業利益'!F14)</f>
+        <v/>
+      </c>
+      <c r="D14" s="8">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!G14,'月別目標と営業利益'!G14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="8">
+        <f>ROUND(C14/入力!$B$6,-4)</f>
+        <v/>
+      </c>
+      <c r="F14" s="8">
+        <f>ROUND(C14/B14,-3)</f>
+        <v/>
+      </c>
+      <c r="G14" s="8">
+        <f>ROUND(E14/B14,-3)</f>
+        <v/>
+      </c>
+      <c r="H14" s="8">
+        <f>入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I14" s="8">
+        <f>入力!$B$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="C15" s="7">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!F15,'月別目標と営業利益'!F15)</f>
+        <v/>
+      </c>
+      <c r="D15" s="8">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!G15,'月別目標と営業利益'!G15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="8">
+        <f>ROUND(C15/入力!$B$6,-4)</f>
+        <v/>
+      </c>
+      <c r="F15" s="8">
+        <f>ROUND(C15/B15,-3)</f>
+        <v/>
+      </c>
+      <c r="G15" s="8">
+        <f>ROUND(E15/B15,-3)</f>
+        <v/>
+      </c>
+      <c r="H15" s="8">
+        <f>入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I15" s="8">
+        <f>入力!$B$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="C16" s="7">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!F16,'月別目標と営業利益'!F16)</f>
+        <v/>
+      </c>
+      <c r="D16" s="8">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!G16,'月別目標と営業利益'!G16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="8">
+        <f>ROUND(C16/入力!$B$6,-4)</f>
+        <v/>
+      </c>
+      <c r="F16" s="8">
+        <f>ROUND(C16/B16,-3)</f>
+        <v/>
+      </c>
+      <c r="G16" s="8">
+        <f>ROUND(E16/B16,-3)</f>
+        <v/>
+      </c>
+      <c r="H16" s="8">
+        <f>入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I16" s="8">
+        <f>入力!$B$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>7月</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="C17" s="7">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!F17,'月別目標と営業利益'!F17)</f>
+        <v/>
+      </c>
+      <c r="D17" s="8">
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!G17,'月別目標と営業利益'!G17)</f>
+        <v/>
+      </c>
+      <c r="E17" s="8">
+        <f>ROUND(C17/入力!$B$6,-4)</f>
+        <v/>
+      </c>
+      <c r="F17" s="8">
+        <f>ROUND(C17/B17,-3)</f>
+        <v/>
+      </c>
+      <c r="G17" s="8">
+        <f>ROUND(E17/B17,-3)</f>
+        <v/>
+      </c>
+      <c r="H17" s="8">
+        <f>入力!$B$14</f>
+        <v/>
+      </c>
+      <c r="I17" s="8">
+        <f>入力!$B$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>年計</t>
+        </is>
+      </c>
+      <c r="B18" s="9">
+        <f>SUM(B6:B17)</f>
+        <v/>
+      </c>
+      <c r="C18" s="10">
+        <f>SUM(C6:C17)</f>
+        <v/>
+      </c>
+      <c r="D18" s="10">
+        <f>SUM(D6:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="10">
+        <f>SUM(E6:E17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="10">
+        <f>SUM(H6:H17)</f>
+        <v/>
+      </c>
+      <c r="I18" s="10">
+        <f>SUM(I6:I17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>年間目標との差</t>
+        </is>
+      </c>
+      <c r="C19" s="8">
+        <f>C18-入力!B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>1人あたりの報奨金（月額）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>人数</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>第1段階（100%以上）</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>第2段階（105%以上）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2">
+        <f>'報奨金（例B）'!A5</f>
+        <v/>
+      </c>
+      <c r="B23" s="11">
+        <f>'報奨金（例B）'!B5</f>
+        <v/>
+      </c>
+      <c r="C23" s="8">
+        <f>'報奨金（例B）'!D5</f>
+        <v/>
+      </c>
+      <c r="D23" s="8">
+        <f>'報奨金（例B）'!E5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2">
+        <f>'報奨金（例B）'!A6</f>
+        <v/>
+      </c>
+      <c r="B24" s="11">
+        <f>'報奨金（例B）'!B6</f>
+        <v/>
+      </c>
+      <c r="C24" s="8">
+        <f>'報奨金（例B）'!D6</f>
+        <v/>
+      </c>
+      <c r="D24" s="8">
+        <f>'報奨金（例B）'!E6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2">
+        <f>'報奨金（例B）'!A7</f>
+        <v/>
+      </c>
+      <c r="B25" s="11">
+        <f>'報奨金（例B）'!B7</f>
+        <v/>
+      </c>
+      <c r="C25" s="8">
+        <f>'報奨金（例B）'!D7</f>
+        <v/>
+      </c>
+      <c r="D25" s="8">
+        <f>'報奨金（例B）'!E7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>ルール</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>・その月の粗利（スマレジ・税抜）が「粗利目標（100%）」以上で第1段階、「粗利目標（105%）」以上で第2段階。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>・判定は粗利額だけ。値引きで売上を作っても報奨金は出ない。処分品は粗利の計算から除く。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>・判定は毎月、支払いは夏冬の賞与にまとめる案（社会保険・扶養への影響は社労士に確認）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>・日数は暦日。定休日を除いた営業日数にしたい場合は青字の日数を書き換える。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -903,17 +1622,17 @@
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>値</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>出所・備考</t>
         </is>
@@ -925,7 +1644,7 @@
           <t>年間の目標粗利</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="12" t="n">
         <v>21500000</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -940,7 +1659,7 @@
           <t>目標粗利率</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="13" t="n">
         <v>0.35</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -955,7 +1674,7 @@
           <t>人件費（月）</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="12" t="n">
         <v>800000</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -970,7 +1689,7 @@
           <t>テナント経費の固定分（月）</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="14" t="n">
         <v>209792</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -985,7 +1704,7 @@
           <t>テナント経費の売上連動率</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="15" t="n">
         <v>0.0692</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1000,7 +1719,7 @@
           <t>その他の店舗経費（年）</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="14" t="n">
         <v>3493268</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1015,7 +1734,7 @@
           <t>共通部の実費（年）</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="14" t="n">
         <v>943852</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1030,7 +1749,7 @@
           <t>本部費（月）</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="14" t="n">
         <v>158000</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1045,7 +1764,7 @@
           <t>営業外費用（年）</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="14" t="n">
         <v>300000</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1060,7 +1779,7 @@
           <t>報奨金 第1段階（店舗計・月）</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="12" t="n">
         <v>30000</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1075,7 +1794,7 @@
           <t>報奨金 第2段階（店舗計・月）</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="12" t="n">
         <v>50000</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1090,13 +1809,13 @@
           <t>第2段階のライン</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="13" t="n">
         <v>1.05</v>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>計算値</t>
         </is>
@@ -1108,7 +1827,7 @@
           <t>年間の目標売上</t>
         </is>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="8">
         <f>ROUND(B5/B6,0)</f>
         <v/>
       </c>
@@ -1124,7 +1843,7 @@
           <t>年間の固定費</t>
         </is>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="8">
         <f>B7*12+B8*12+B10+B11</f>
         <v/>
       </c>
@@ -1140,7 +1859,7 @@
           <t>限界利益率</t>
         </is>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="16">
         <f>B6-B9</f>
         <v/>
       </c>
@@ -1156,7 +1875,7 @@
           <t>損益分岐の売上（報奨金前）</t>
         </is>
       </c>
-      <c r="B22" s="9">
+      <c r="B22" s="8">
         <f>B20/B21</f>
         <v/>
       </c>
@@ -1167,7 +1886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1190,22 +1909,22 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>100%達成</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>105%達成</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>内訳・計算</t>
         </is>
@@ -1217,10 +1936,10 @@
           <t>達成度</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="16">
         <f>入力!B16</f>
         <v/>
       </c>
@@ -1232,11 +1951,11 @@
           <t>売上</t>
         </is>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="8">
         <f>入力!$B$19*B4</f>
         <v/>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <f>入力!$B$19*C4</f>
         <v/>
       </c>
@@ -1252,11 +1971,11 @@
           <t>粗利</t>
         </is>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="8">
         <f>入力!$B$5*B4</f>
         <v/>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <f>入力!$B$5*C4</f>
         <v/>
       </c>
@@ -1268,11 +1987,11 @@
           <t>人件費</t>
         </is>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="8">
         <f>入力!$B$7*12</f>
         <v/>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="8">
         <f>入力!$B$7*12</f>
         <v/>
       </c>
@@ -1288,11 +2007,11 @@
           <t>報奨金</t>
         </is>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="8">
         <f>入力!$B$14*12</f>
         <v/>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <f>入力!$B$15*12</f>
         <v/>
       </c>
@@ -1308,11 +2027,11 @@
           <t>テナント経費</t>
         </is>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="8">
         <f>入力!$B$8*12+B5*入力!$B$9</f>
         <v/>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <f>入力!$B$8*12+C5*入力!$B$9</f>
         <v/>
       </c>
@@ -1328,11 +2047,11 @@
           <t>その他の店舗経費</t>
         </is>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="8">
         <f>入力!$B$10</f>
         <v/>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="8">
         <f>入力!$B$10</f>
         <v/>
       </c>
@@ -1344,11 +2063,11 @@
           <t>共通部の実費</t>
         </is>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="8">
         <f>入力!$B$11</f>
         <v/>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="8">
         <f>入力!$B$11</f>
         <v/>
       </c>
@@ -1360,27 +2079,27 @@
           <t>販管費 計</t>
         </is>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="8">
         <f>SUM(B7:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="8">
         <f>SUM(C7:C11)</f>
         <v/>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>営業利益</t>
         </is>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="7">
         <f>B6-B12</f>
         <v/>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="7">
         <f>C6-C12</f>
         <v/>
       </c>
@@ -1392,27 +2111,27 @@
           <t>営業外費用</t>
         </is>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="8">
         <f>入力!$B$13</f>
         <v/>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="8">
         <f>入力!$B$13</f>
         <v/>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>経常利益</t>
         </is>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="7">
         <f>B13-B14</f>
         <v/>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="7">
         <f>C13-C14</f>
         <v/>
       </c>
@@ -1424,11 +2143,11 @@
           <t>参考：本部費込みの営業利益</t>
         </is>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="8">
         <f>B13+B11-入力!$B$12*12</f>
         <v/>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="8">
         <f>C13+C11-入力!$B$12*12</f>
         <v/>
       </c>
@@ -1443,7 +2162,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1468,183 +2187,183 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>達成度</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>売上</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>粗利</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>報奨金（年）</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>営業利益</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>経常利益</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="n">
+      <c r="A4" s="18" t="n">
         <v>0.9</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <f>入力!$B$19*A4</f>
         <v/>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <f>入力!$B$5*A4</f>
         <v/>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="8">
         <f>IF(A4&gt;=入力!$B$16,入力!$B$15,IF(A4&gt;=1,入力!$B$14,0))*12</f>
         <v/>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="10">
         <f>C4-B4*入力!$B$9-入力!$B$20-D4</f>
         <v/>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="8">
         <f>E4-入力!$B$13</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="n">
+      <c r="A5" s="18" t="n">
         <v>0.95</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="8">
         <f>入力!$B$19*A5</f>
         <v/>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <f>入力!$B$5*A5</f>
         <v/>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <f>IF(A5&gt;=入力!$B$16,入力!$B$15,IF(A5&gt;=1,入力!$B$14,0))*12</f>
         <v/>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="10">
         <f>C5-B5*入力!$B$9-入力!$B$20-D5</f>
         <v/>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <f>E5-入力!$B$13</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="n">
+      <c r="A6" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="8">
         <f>入力!$B$19*A6</f>
         <v/>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <f>入力!$B$5*A6</f>
         <v/>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <f>IF(A6&gt;=入力!$B$16,入力!$B$15,IF(A6&gt;=1,入力!$B$14,0))*12</f>
         <v/>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="10">
         <f>C6-B6*入力!$B$9-入力!$B$20-D6</f>
         <v/>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="8">
         <f>E6-入力!$B$13</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n">
+      <c r="A7" s="18" t="n">
         <v>1.03</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="8">
         <f>入力!$B$19*A7</f>
         <v/>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="8">
         <f>入力!$B$5*A7</f>
         <v/>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <f>IF(A7&gt;=入力!$B$16,入力!$B$15,IF(A7&gt;=1,入力!$B$14,0))*12</f>
         <v/>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="10">
         <f>C7-B7*入力!$B$9-入力!$B$20-D7</f>
         <v/>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="8">
         <f>E7-入力!$B$13</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n">
+      <c r="A8" s="18" t="n">
         <v>1.05</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="8">
         <f>入力!$B$19*A8</f>
         <v/>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <f>入力!$B$5*A8</f>
         <v/>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <f>IF(A8&gt;=入力!$B$16,入力!$B$15,IF(A8&gt;=1,入力!$B$14,0))*12</f>
         <v/>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="10">
         <f>C8-B8*入力!$B$9-入力!$B$20-D8</f>
         <v/>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="8">
         <f>E8-入力!$B$13</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n">
+      <c r="A9" s="18" t="n">
         <v>1.1</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="8">
         <f>入力!$B$19*A9</f>
         <v/>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <f>入力!$B$5*A9</f>
         <v/>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <f>IF(A9&gt;=入力!$B$16,入力!$B$15,IF(A9&gt;=1,入力!$B$14,0))*12</f>
         <v/>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="10">
         <f>C9-B9*入力!$B$9-入力!$B$20-D9</f>
         <v/>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="8">
         <f>E9-入力!$B$13</f>
         <v/>
       </c>
@@ -1655,7 +2374,7 @@
           <t>予算を1%超えるごとの営業利益の増加</t>
         </is>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="8">
         <f>入力!B19*0.01*入力!B21</f>
         <v/>
       </c>
@@ -1666,7 +2385,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1690,154 +2409,154 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>粗利率</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>粗利</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>報奨金（年）</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>営業利益</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>経常利益</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="n">
+      <c r="A4" s="18" t="n">
         <v>0.31</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <f>入力!$B$19*A4</f>
         <v/>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <f>IF(B4&gt;=入力!$B$5*入力!$B$16-1,入力!$B$15,IF(B4&gt;=入力!$B$5-1,入力!$B$14,0))*12</f>
         <v/>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="10">
         <f>B4-入力!$B$19*入力!$B$9-入力!$B$20-C4</f>
         <v/>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="8">
         <f>D4-入力!$B$13</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="n">
+      <c r="A5" s="18" t="n">
         <v>0.33</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="8">
         <f>入力!$B$19*A5</f>
         <v/>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <f>IF(B5&gt;=入力!$B$5*入力!$B$16-1,入力!$B$15,IF(B5&gt;=入力!$B$5-1,入力!$B$14,0))*12</f>
         <v/>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="10">
         <f>B5-入力!$B$19*入力!$B$9-入力!$B$20-C5</f>
         <v/>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <f>D5-入力!$B$13</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="n">
+      <c r="A6" s="18" t="n">
         <v>0.34</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="8">
         <f>入力!$B$19*A6</f>
         <v/>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <f>IF(B6&gt;=入力!$B$5*入力!$B$16-1,入力!$B$15,IF(B6&gt;=入力!$B$5-1,入力!$B$14,0))*12</f>
         <v/>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="10">
         <f>B6-入力!$B$19*入力!$B$9-入力!$B$20-C6</f>
         <v/>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="8">
         <f>D6-入力!$B$13</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n">
+      <c r="A7" s="18" t="n">
         <v>0.35</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="8">
         <f>入力!$B$19*A7</f>
         <v/>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="8">
         <f>IF(B7&gt;=入力!$B$5*入力!$B$16-1,入力!$B$15,IF(B7&gt;=入力!$B$5-1,入力!$B$14,0))*12</f>
         <v/>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="10">
         <f>B7-入力!$B$19*入力!$B$9-入力!$B$20-C7</f>
         <v/>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="8">
         <f>D7-入力!$B$13</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n">
+      <c r="A8" s="18" t="n">
         <v>0.36</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="8">
         <f>入力!$B$19*A8</f>
         <v/>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <f>IF(B8&gt;=入力!$B$5*入力!$B$16-1,入力!$B$15,IF(B8&gt;=入力!$B$5-1,入力!$B$14,0))*12</f>
         <v/>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="10">
         <f>B8-入力!$B$19*入力!$B$9-入力!$B$20-C8</f>
         <v/>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="8">
         <f>D8-入力!$B$13</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n">
+      <c r="A9" s="18" t="n">
         <v>0.37</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="8">
         <f>入力!$B$19*A9</f>
         <v/>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <f>IF(B9&gt;=入力!$B$5*入力!$B$16-1,入力!$B$15,IF(B9&gt;=入力!$B$5-1,入力!$B$14,0))*12</f>
         <v/>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="10">
         <f>B9-入力!$B$19*入力!$B$9-入力!$B$20-C9</f>
         <v/>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="8">
         <f>D9-入力!$B$13</f>
         <v/>
       </c>
@@ -1848,7 +2567,7 @@
           <t>粗利率1ポイントあたりの営業利益の変化</t>
         </is>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <f>入力!B19*0.01</f>
         <v/>
       </c>
@@ -1858,7 +2577,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1904,62 +2623,62 @@
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>前年売上（参考）</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>比率</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>目標売上（参考）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>粗利目標（丸め前）</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>粗利目標100%</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>粗利目標105%</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>営業利益（100%時）</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>累計</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>実績粗利</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>報奨金</t>
         </is>
@@ -1971,42 +2690,42 @@
           <t>8月</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="14" t="n">
         <v>3040292</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="16">
         <f>B6/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <f>ROUND(F6/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="8">
         <f>ROUND(入力!$B$5*C6,-3)</f>
         <v/>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="12" t="n">
         <v>1200000</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="8">
         <f>ROUND(F6*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="8">
         <f>F6-D6*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="8">
         <f>SUM($H$6:H6)</f>
         <v/>
       </c>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="15">
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="11">
         <f>IF(J6="","",IF(J6&gt;=G6,2,IF(J6&gt;=F6,1,0)))</f>
         <v/>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="8">
         <f>IF(OR(K6="",K6=0),0,IF(K6=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
@@ -2017,42 +2736,42 @@
           <t>9月</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="14" t="n">
         <v>3638478</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="16">
         <f>B7/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <f>ROUND(F7/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="8">
         <f>ROUND(入力!$B$5*C7,-3)</f>
         <v/>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="12" t="n">
         <v>1450000</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="8">
         <f>ROUND(F7*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="8">
         <f>F7-D7*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="8">
         <f>SUM($H$6:H7)</f>
         <v/>
       </c>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="15">
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="11">
         <f>IF(J7="","",IF(J7&gt;=G7,2,IF(J7&gt;=F7,1,0)))</f>
         <v/>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="8">
         <f>IF(OR(K7="",K7=0),0,IF(K7=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
@@ -2063,42 +2782,42 @@
           <t>10月</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="14" t="n">
         <v>4934704</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="16">
         <f>B8/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <f>ROUND(F8/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="8">
         <f>ROUND(入力!$B$5*C8,-3)</f>
         <v/>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="12" t="n">
         <v>2000000</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="8">
         <f>ROUND(F8*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="8">
         <f>F8-D8*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="8">
         <f>SUM($H$6:H8)</f>
         <v/>
       </c>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="15">
+      <c r="J8" s="12" t="n"/>
+      <c r="K8" s="11">
         <f>IF(J8="","",IF(J8&gt;=G8,2,IF(J8&gt;=F8,1,0)))</f>
         <v/>
       </c>
-      <c r="L8" s="9">
+      <c r="L8" s="8">
         <f>IF(OR(K8="",K8=0),0,IF(K8=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
@@ -2109,42 +2828,42 @@
           <t>11月</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="14" t="n">
         <v>5149749</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="16">
         <f>B9/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <f>ROUND(F9/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="8">
         <f>ROUND(入力!$B$5*C9,-3)</f>
         <v/>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="12" t="n">
         <v>2050000</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="8">
         <f>ROUND(F9*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <f>F9-D9*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="8">
         <f>SUM($H$6:H9)</f>
         <v/>
       </c>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="15">
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="11">
         <f>IF(J9="","",IF(J9&gt;=G9,2,IF(J9&gt;=F9,1,0)))</f>
         <v/>
       </c>
-      <c r="L9" s="9">
+      <c r="L9" s="8">
         <f>IF(OR(K9="",K9=0),0,IF(K9=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
@@ -2155,42 +2874,42 @@
           <t>12月</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="14" t="n">
         <v>6820952</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="16">
         <f>B10/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <f>ROUND(F10/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="8">
         <f>ROUND(入力!$B$5*C10,-3)</f>
         <v/>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="12" t="n">
         <v>2750000</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="8">
         <f>ROUND(F10*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="8">
         <f>F10-D10*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="8">
         <f>SUM($H$6:H10)</f>
         <v/>
       </c>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="15">
+      <c r="J10" s="12" t="n"/>
+      <c r="K10" s="11">
         <f>IF(J10="","",IF(J10&gt;=G10,2,IF(J10&gt;=F10,1,0)))</f>
         <v/>
       </c>
-      <c r="L10" s="9">
+      <c r="L10" s="8">
         <f>IF(OR(K10="",K10=0),0,IF(K10=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
@@ -2201,42 +2920,42 @@
           <t>1月</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="14" t="n">
         <v>4850701</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="16">
         <f>B11/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <f>ROUND(F11/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="8">
         <f>ROUND(入力!$B$5*C11,-3)</f>
         <v/>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="12" t="n">
         <v>1950000</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="8">
         <f>ROUND(F11*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="8">
         <f>F11-D11*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="8">
         <f>SUM($H$6:H11)</f>
         <v/>
       </c>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="15">
+      <c r="J11" s="12" t="n"/>
+      <c r="K11" s="11">
         <f>IF(J11="","",IF(J11&gt;=G11,2,IF(J11&gt;=F11,1,0)))</f>
         <v/>
       </c>
-      <c r="L11" s="9">
+      <c r="L11" s="8">
         <f>IF(OR(K11="",K11=0),0,IF(K11=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
@@ -2247,42 +2966,42 @@
           <t>2月</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="14" t="n">
         <v>2795656</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="16">
         <f>B12/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="8">
         <f>ROUND(F12/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="8">
         <f>ROUND(入力!$B$5*C12,-3)</f>
         <v/>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="12" t="n">
         <v>1100000</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="8">
         <f>ROUND(F12*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="8">
         <f>F12-D12*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="8">
         <f>SUM($H$6:H12)</f>
         <v/>
       </c>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="15">
+      <c r="J12" s="12" t="n"/>
+      <c r="K12" s="11">
         <f>IF(J12="","",IF(J12&gt;=G12,2,IF(J12&gt;=F12,1,0)))</f>
         <v/>
       </c>
-      <c r="L12" s="9">
+      <c r="L12" s="8">
         <f>IF(OR(K12="",K12=0),0,IF(K12=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
@@ -2293,42 +3012,42 @@
           <t>3月</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="14" t="n">
         <v>4419804</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="16">
         <f>B13/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="8">
         <f>ROUND(F13/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="8">
         <f>ROUND(入力!$B$5*C13,-3)</f>
         <v/>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="12" t="n">
         <v>1750000</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="8">
         <f>ROUND(F13*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="8">
         <f>F13-D13*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="8">
         <f>SUM($H$6:H13)</f>
         <v/>
       </c>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="15">
+      <c r="J13" s="12" t="n"/>
+      <c r="K13" s="11">
         <f>IF(J13="","",IF(J13&gt;=G13,2,IF(J13&gt;=F13,1,0)))</f>
         <v/>
       </c>
-      <c r="L13" s="9">
+      <c r="L13" s="8">
         <f>IF(OR(K13="",K13=0),0,IF(K13=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
@@ -2339,42 +3058,42 @@
           <t>4月</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="14" t="n">
         <v>3581469</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="16">
         <f>B14/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="8">
         <f>ROUND(F14/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="8">
         <f>ROUND(入力!$B$5*C14,-3)</f>
         <v/>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="12" t="n">
         <v>1450000</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="8">
         <f>ROUND(F14*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="8">
         <f>F14-D14*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="8">
         <f>SUM($H$6:H14)</f>
         <v/>
       </c>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="15">
+      <c r="J14" s="12" t="n"/>
+      <c r="K14" s="11">
         <f>IF(J14="","",IF(J14&gt;=G14,2,IF(J14&gt;=F14,1,0)))</f>
         <v/>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="8">
         <f>IF(OR(K14="",K14=0),0,IF(K14=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
@@ -2385,42 +3104,42 @@
           <t>5月</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="14" t="n">
         <v>4799124</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="16">
         <f>B15/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="8">
         <f>ROUND(F15/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="8">
         <f>ROUND(入力!$B$5*C15,-3)</f>
         <v/>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="12" t="n">
         <v>1950000</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="8">
         <f>ROUND(F15*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="8">
         <f>F15-D15*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="8">
         <f>SUM($H$6:H15)</f>
         <v/>
       </c>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="15">
+      <c r="J15" s="12" t="n"/>
+      <c r="K15" s="11">
         <f>IF(J15="","",IF(J15&gt;=G15,2,IF(J15&gt;=F15,1,0)))</f>
         <v/>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="8">
         <f>IF(OR(K15="",K15=0),0,IF(K15=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
@@ -2431,42 +3150,42 @@
           <t>6月</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="14" t="n">
         <v>4888307</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="16">
         <f>B16/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="8">
         <f>ROUND(F16/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="8">
         <f>ROUND(入力!$B$5*C16,-3)</f>
         <v/>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="12" t="n">
         <v>1950000</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="8">
         <f>ROUND(F16*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="8">
         <f>F16-D16*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="8">
         <f>SUM($H$6:H16)</f>
         <v/>
       </c>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="15">
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="11">
         <f>IF(J16="","",IF(J16&gt;=G16,2,IF(J16&gt;=F16,1,0)))</f>
         <v/>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="8">
         <f>IF(OR(K16="",K16=0),0,IF(K16=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
@@ -2477,81 +3196,81 @@
           <t>7月</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="14" t="n">
         <v>4741065</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="16">
         <f>B17/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="8">
         <f>ROUND(F17/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="8">
         <f>ROUND(入力!$B$5*C17,-3)</f>
         <v/>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="12" t="n">
         <v>1900000</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="8">
         <f>ROUND(F17*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="8">
         <f>F17-D17*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="8">
         <f>SUM($H$6:H17)</f>
         <v/>
       </c>
-      <c r="J17" s="4" t="n"/>
-      <c r="K17" s="15">
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="11">
         <f>IF(J17="","",IF(J17&gt;=G17,2,IF(J17&gt;=F17,1,0)))</f>
         <v/>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="8">
         <f>IF(OR(K17="",K17=0),0,IF(K17=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>年計</t>
         </is>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="10">
         <f>SUM(B6:B17)</f>
         <v/>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="10">
         <f>SUM(D6:D17)</f>
         <v/>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="10">
         <f>SUM(E6:E17)</f>
         <v/>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="10">
         <f>SUM(F6:F17)</f>
         <v/>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="10">
         <f>SUM(G6:G17)</f>
         <v/>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="10">
         <f>SUM(H6:H17)</f>
         <v/>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="10">
         <f>SUM(J6:J17)</f>
         <v/>
       </c>
-      <c r="L18" s="14">
+      <c r="L18" s="10">
         <f>SUM(L6:L17)</f>
         <v/>
       </c>
@@ -2562,7 +3281,7 @@
           <t>年間目標との差</t>
         </is>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="8">
         <f>F18-入力!B5</f>
         <v/>
       </c>
@@ -2580,7 +3299,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2626,67 +3345,67 @@
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>スマレジ予算（参考）</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>比率</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>目標売上（参考）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>粗利目標（丸め前）</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>粗利目標100%</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>粗利目標105%</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>営業利益（100%時）</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>累計</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>構成比版との差（粗利目標）</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>実績粗利</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>段階</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>報奨金</t>
         </is>
@@ -2698,46 +3417,46 @@
           <t>8月</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="14" t="n">
         <v>3500000</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="16">
         <f>B6/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <f>ROUND(F6/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="8">
         <f>ROUND(入力!$B$5*C6,-3)</f>
         <v/>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="12" t="n">
         <v>1250000</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="8">
         <f>ROUND(F6*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="8">
         <f>F6-D6*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="8">
         <f>SUM($H$6:H6)</f>
         <v/>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="8">
         <f>F6-'月別目標と営業利益'!F6</f>
         <v/>
       </c>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="15">
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="11">
         <f>IF(K6="","",IF(K6&gt;=G6,2,IF(K6&gt;=F6,1,0)))</f>
         <v/>
       </c>
-      <c r="M6" s="9">
+      <c r="M6" s="8">
         <f>IF(OR(L6="",L6=0),0,IF(L6=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
@@ -2748,46 +3467,46 @@
           <t>9月</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="14" t="n">
         <v>4500000</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="16">
         <f>B7/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <f>ROUND(F7/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="8">
         <f>ROUND(入力!$B$5*C7,-3)</f>
         <v/>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="12" t="n">
         <v>1600000</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="8">
         <f>ROUND(F7*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="8">
         <f>F7-D7*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="8">
         <f>SUM($H$6:H7)</f>
         <v/>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="8">
         <f>F7-'月別目標と営業利益'!F7</f>
         <v/>
       </c>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="15">
+      <c r="K7" s="12" t="n"/>
+      <c r="L7" s="11">
         <f>IF(K7="","",IF(K7&gt;=G7,2,IF(K7&gt;=F7,1,0)))</f>
         <v/>
       </c>
-      <c r="M7" s="9">
+      <c r="M7" s="8">
         <f>IF(OR(L7="",L7=0),0,IF(L7=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
@@ -2798,46 +3517,46 @@
           <t>10月</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="14" t="n">
         <v>5500000</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="16">
         <f>B8/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <f>ROUND(F8/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="8">
         <f>ROUND(入力!$B$5*C8,-3)</f>
         <v/>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="12" t="n">
         <v>2000000</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="8">
         <f>ROUND(F8*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="8">
         <f>F8-D8*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="8">
         <f>SUM($H$6:H8)</f>
         <v/>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="8">
         <f>F8-'月別目標と営業利益'!F8</f>
         <v/>
       </c>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="15">
+      <c r="K8" s="12" t="n"/>
+      <c r="L8" s="11">
         <f>IF(K8="","",IF(K8&gt;=G8,2,IF(K8&gt;=F8,1,0)))</f>
         <v/>
       </c>
-      <c r="M8" s="9">
+      <c r="M8" s="8">
         <f>IF(OR(L8="",L8=0),0,IF(L8=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
@@ -2848,46 +3567,46 @@
           <t>11月</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="14" t="n">
         <v>5500000</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="16">
         <f>B9/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <f>ROUND(F9/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="8">
         <f>ROUND(入力!$B$5*C9,-3)</f>
         <v/>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="12" t="n">
         <v>2000000</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="8">
         <f>ROUND(F9*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <f>F9-D9*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="8">
         <f>SUM($H$6:H9)</f>
         <v/>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="8">
         <f>F9-'月別目標と営業利益'!F9</f>
         <v/>
       </c>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="15">
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="11">
         <f>IF(K9="","",IF(K9&gt;=G9,2,IF(K9&gt;=F9,1,0)))</f>
         <v/>
       </c>
-      <c r="M9" s="9">
+      <c r="M9" s="8">
         <f>IF(OR(L9="",L9=0),0,IF(L9=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
@@ -2898,46 +3617,46 @@
           <t>12月</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="14" t="n">
         <v>7000000</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="16">
         <f>B10/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <f>ROUND(F10/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="8">
         <f>ROUND(入力!$B$5*C10,-3)</f>
         <v/>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="12" t="n">
         <v>2500000</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="8">
         <f>ROUND(F10*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="8">
         <f>F10-D10*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="8">
         <f>SUM($H$6:H10)</f>
         <v/>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="8">
         <f>F10-'月別目標と営業利益'!F10</f>
         <v/>
       </c>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="15">
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="11">
         <f>IF(K10="","",IF(K10&gt;=G10,2,IF(K10&gt;=F10,1,0)))</f>
         <v/>
       </c>
-      <c r="M10" s="9">
+      <c r="M10" s="8">
         <f>IF(OR(L10="",L10=0),0,IF(L10=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
@@ -2948,46 +3667,46 @@
           <t>1月</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="14" t="n">
         <v>6000000</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="16">
         <f>B11/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <f>ROUND(F11/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="8">
         <f>ROUND(入力!$B$5*C11,-3)</f>
         <v/>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="12" t="n">
         <v>2100000</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="8">
         <f>ROUND(F11*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="8">
         <f>F11-D11*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="8">
         <f>SUM($H$6:H11)</f>
         <v/>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="8">
         <f>F11-'月別目標と営業利益'!F11</f>
         <v/>
       </c>
-      <c r="K11" s="4" t="n"/>
-      <c r="L11" s="15">
+      <c r="K11" s="12" t="n"/>
+      <c r="L11" s="11">
         <f>IF(K11="","",IF(K11&gt;=G11,2,IF(K11&gt;=F11,1,0)))</f>
         <v/>
       </c>
-      <c r="M11" s="9">
+      <c r="M11" s="8">
         <f>IF(OR(L11="",L11=0),0,IF(L11=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
@@ -2998,46 +3717,46 @@
           <t>2月</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="14" t="n">
         <v>3500000</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="16">
         <f>B12/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="8">
         <f>ROUND(F12/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="8">
         <f>ROUND(入力!$B$5*C12,-3)</f>
         <v/>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="12" t="n">
         <v>1250000</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="8">
         <f>ROUND(F12*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="8">
         <f>F12-D12*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="8">
         <f>SUM($H$6:H12)</f>
         <v/>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="8">
         <f>F12-'月別目標と営業利益'!F12</f>
         <v/>
       </c>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="15">
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="11">
         <f>IF(K12="","",IF(K12&gt;=G12,2,IF(K12&gt;=F12,1,0)))</f>
         <v/>
       </c>
-      <c r="M12" s="9">
+      <c r="M12" s="8">
         <f>IF(OR(L12="",L12=0),0,IF(L12=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
@@ -3048,46 +3767,46 @@
           <t>3月</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="14" t="n">
         <v>5500000</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="16">
         <f>B13/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="8">
         <f>ROUND(F13/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="8">
         <f>ROUND(入力!$B$5*C13,-3)</f>
         <v/>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="12" t="n">
         <v>2000000</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="8">
         <f>ROUND(F13*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="8">
         <f>F13-D13*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="8">
         <f>SUM($H$6:H13)</f>
         <v/>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="8">
         <f>F13-'月別目標と営業利益'!F13</f>
         <v/>
       </c>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="15">
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="11">
         <f>IF(K13="","",IF(K13&gt;=G13,2,IF(K13&gt;=F13,1,0)))</f>
         <v/>
       </c>
-      <c r="M13" s="9">
+      <c r="M13" s="8">
         <f>IF(OR(L13="",L13=0),0,IF(L13=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
@@ -3098,46 +3817,46 @@
           <t>4月</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="14" t="n">
         <v>4500000</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="16">
         <f>B14/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="8">
         <f>ROUND(F14/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="8">
         <f>ROUND(入力!$B$5*C14,-3)</f>
         <v/>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="12" t="n">
         <v>1600000</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="8">
         <f>ROUND(F14*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="8">
         <f>F14-D14*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="8">
         <f>SUM($H$6:H14)</f>
         <v/>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="8">
         <f>F14-'月別目標と営業利益'!F14</f>
         <v/>
       </c>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="15">
+      <c r="K14" s="12" t="n"/>
+      <c r="L14" s="11">
         <f>IF(K14="","",IF(K14&gt;=G14,2,IF(K14&gt;=F14,1,0)))</f>
         <v/>
       </c>
-      <c r="M14" s="9">
+      <c r="M14" s="8">
         <f>IF(OR(L14="",L14=0),0,IF(L14=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
@@ -3148,46 +3867,46 @@
           <t>5月</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="14" t="n">
         <v>4500000</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="16">
         <f>B15/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="8">
         <f>ROUND(F15/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="8">
         <f>ROUND(入力!$B$5*C15,-3)</f>
         <v/>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="12" t="n">
         <v>1600000</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="8">
         <f>ROUND(F15*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="8">
         <f>F15-D15*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="8">
         <f>SUM($H$6:H15)</f>
         <v/>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="8">
         <f>F15-'月別目標と営業利益'!F15</f>
         <v/>
       </c>
-      <c r="K15" s="4" t="n"/>
-      <c r="L15" s="15">
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="11">
         <f>IF(K15="","",IF(K15&gt;=G15,2,IF(K15&gt;=F15,1,0)))</f>
         <v/>
       </c>
-      <c r="M15" s="9">
+      <c r="M15" s="8">
         <f>IF(OR(L15="",L15=0),0,IF(L15=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
@@ -3198,46 +3917,46 @@
           <t>6月</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="14" t="n">
         <v>5500000</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="16">
         <f>B16/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="8">
         <f>ROUND(F16/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="8">
         <f>ROUND(入力!$B$5*C16,-3)</f>
         <v/>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="12" t="n">
         <v>2000000</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="8">
         <f>ROUND(F16*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="8">
         <f>F16-D16*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="8">
         <f>SUM($H$6:H16)</f>
         <v/>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="8">
         <f>F16-'月別目標と営業利益'!F16</f>
         <v/>
       </c>
-      <c r="K16" s="4" t="n"/>
-      <c r="L16" s="15">
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="11">
         <f>IF(K16="","",IF(K16&gt;=G16,2,IF(K16&gt;=F16,1,0)))</f>
         <v/>
       </c>
-      <c r="M16" s="9">
+      <c r="M16" s="8">
         <f>IF(OR(L16="",L16=0),0,IF(L16=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
@@ -3248,85 +3967,85 @@
           <t>7月</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="14" t="n">
         <v>4500000</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="16">
         <f>B17/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="8">
         <f>ROUND(F17/入力!$B$6,-4)</f>
         <v/>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="8">
         <f>ROUND(入力!$B$5*C17,-3)</f>
         <v/>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="12" t="n">
         <v>1600000</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="8">
         <f>ROUND(F17*入力!$B$16/50000,0)*50000</f>
         <v/>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="8">
         <f>F17-D17*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
         <v/>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="8">
         <f>SUM($H$6:H17)</f>
         <v/>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="8">
         <f>F17-'月別目標と営業利益'!F17</f>
         <v/>
       </c>
-      <c r="K17" s="4" t="n"/>
-      <c r="L17" s="15">
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="11">
         <f>IF(K17="","",IF(K17&gt;=G17,2,IF(K17&gt;=F17,1,0)))</f>
         <v/>
       </c>
-      <c r="M17" s="9">
+      <c r="M17" s="8">
         <f>IF(OR(L17="",L17=0),0,IF(L17=2,入力!$B$15,入力!$B$14))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>年計</t>
         </is>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="10">
         <f>SUM(B6:B17)</f>
         <v/>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="10">
         <f>SUM(D6:D17)</f>
         <v/>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="10">
         <f>SUM(E6:E17)</f>
         <v/>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="10">
         <f>SUM(F6:F17)</f>
         <v/>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="10">
         <f>SUM(G6:G17)</f>
         <v/>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="10">
         <f>SUM(H6:H17)</f>
         <v/>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="10">
         <f>SUM(K6:K17)</f>
         <v/>
       </c>
-      <c r="M18" s="14">
+      <c r="M18" s="10">
         <f>SUM(M6:M17)</f>
         <v/>
       </c>
@@ -3337,7 +4056,7 @@
           <t>年間目標との差</t>
         </is>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="8">
         <f>F18-入力!B5</f>
         <v/>
       </c>
@@ -3355,7 +4074,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3386,27 +4105,27 @@
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>人数</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>重み</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>第1段階（月額）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>第2段階（月額）</t>
         </is>
@@ -3418,17 +4137,17 @@
           <t>店長</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <f>ROUND(入力!$B$14*C5/SUMPRODUCT($B$5:$B$7,$C$5:$C$7),-2)</f>
         <v/>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <f>ROUND(入力!$B$15*C5/SUMPRODUCT($B$5:$B$7,$C$5:$C$7),-2)</f>
         <v/>
       </c>
@@ -3439,17 +4158,17 @@
           <t>古参パート</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <f>ROUND(入力!$B$14*C6/SUMPRODUCT($B$5:$B$7,$C$5:$C$7),-2)</f>
         <v/>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="8">
         <f>ROUND(入力!$B$15*C6/SUMPRODUCT($B$5:$B$7,$C$5:$C$7),-2)</f>
         <v/>
       </c>
@@ -3460,51 +4179,51 @@
           <t>その他パート</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <f>ROUND(入力!$B$14*C7/SUMPRODUCT($B$5:$B$7,$C$5:$C$7),-2)</f>
         <v/>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="8">
         <f>ROUND(入力!$B$15*C7/SUMPRODUCT($B$5:$B$7,$C$5:$C$7),-2)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>店舗計（月）</t>
         </is>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="9">
         <f>SUM(B5:B7)</f>
         <v/>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="10">
         <f>SUMPRODUCT(B5:B7,D5:D7)</f>
         <v/>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="10">
         <f>SUMPRODUCT(B5:B7,E5:E7)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>全月達成した場合（年）</t>
         </is>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="10">
         <f>入力!B14*12</f>
         <v/>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="10">
         <f>入力!B15*12</f>
         <v/>
       </c>

--- a/excel/Weekends_予算と報奨金案_粗利2150万円.xlsx
+++ b/excel/Weekends_予算と報奨金案_粗利2150万円.xlsx
@@ -108,9 +108,9 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -899,7 +899,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Weekends 2027年度 月別目標（粗利2,150万円・税抜）</t>
+          <t>Weekends 2027年度 月別目標（売上6,300万円・粗利2,150万円・税抜）</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>売上の目安（粗利率35%）</t>
+          <t>売上目標</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>1日あたり売上の目安</t>
+          <t>1日あたり売上目標</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -990,7 +990,7 @@
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>ROUND(C6/入力!$B$6,-4)</f>
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!D6,'月別目標と営業利益'!D6)</f>
         <v/>
       </c>
       <c r="F6" s="8">
@@ -1028,7 +1028,7 @@
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>ROUND(C7/入力!$B$6,-4)</f>
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!D7,'月別目標と営業利益'!D7)</f>
         <v/>
       </c>
       <c r="F7" s="8">
@@ -1066,7 +1066,7 @@
         <v/>
       </c>
       <c r="E8" s="8">
-        <f>ROUND(C8/入力!$B$6,-4)</f>
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!D8,'月別目標と営業利益'!D8)</f>
         <v/>
       </c>
       <c r="F8" s="8">
@@ -1104,7 +1104,7 @@
         <v/>
       </c>
       <c r="E9" s="8">
-        <f>ROUND(C9/入力!$B$6,-4)</f>
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!D9,'月別目標と営業利益'!D9)</f>
         <v/>
       </c>
       <c r="F9" s="8">
@@ -1142,7 +1142,7 @@
         <v/>
       </c>
       <c r="E10" s="8">
-        <f>ROUND(C10/入力!$B$6,-4)</f>
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!D10,'月別目標と営業利益'!D10)</f>
         <v/>
       </c>
       <c r="F10" s="8">
@@ -1180,7 +1180,7 @@
         <v/>
       </c>
       <c r="E11" s="8">
-        <f>ROUND(C11/入力!$B$6,-4)</f>
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!D11,'月別目標と営業利益'!D11)</f>
         <v/>
       </c>
       <c r="F11" s="8">
@@ -1218,7 +1218,7 @@
         <v/>
       </c>
       <c r="E12" s="8">
-        <f>ROUND(C12/入力!$B$6,-4)</f>
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!D12,'月別目標と営業利益'!D12)</f>
         <v/>
       </c>
       <c r="F12" s="8">
@@ -1256,7 +1256,7 @@
         <v/>
       </c>
       <c r="E13" s="8">
-        <f>ROUND(C13/入力!$B$6,-4)</f>
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!D13,'月別目標と営業利益'!D13)</f>
         <v/>
       </c>
       <c r="F13" s="8">
@@ -1294,7 +1294,7 @@
         <v/>
       </c>
       <c r="E14" s="8">
-        <f>ROUND(C14/入力!$B$6,-4)</f>
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!D14,'月別目標と営業利益'!D14)</f>
         <v/>
       </c>
       <c r="F14" s="8">
@@ -1332,7 +1332,7 @@
         <v/>
       </c>
       <c r="E15" s="8">
-        <f>ROUND(C15/入力!$B$6,-4)</f>
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!D15,'月別目標と営業利益'!D15)</f>
         <v/>
       </c>
       <c r="F15" s="8">
@@ -1370,7 +1370,7 @@
         <v/>
       </c>
       <c r="E16" s="8">
-        <f>ROUND(C16/入力!$B$6,-4)</f>
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!D16,'月別目標と営業利益'!D16)</f>
         <v/>
       </c>
       <c r="F16" s="8">
@@ -1408,7 +1408,7 @@
         <v/>
       </c>
       <c r="E17" s="8">
-        <f>ROUND(C17/入力!$B$6,-4)</f>
+        <f>CHOOSE($B$3,'月別（スマレジ版）'!D17,'月別目標と営業利益'!D17)</f>
         <v/>
       </c>
       <c r="F17" s="8">
@@ -1467,6 +1467,10 @@
       </c>
       <c r="C19" s="8">
         <f>C18-入力!B5</f>
+        <v/>
+      </c>
+      <c r="E19" s="8">
+        <f>E18-入力!B19</f>
         <v/>
       </c>
     </row>
@@ -1563,7 +1567,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>・その月の粗利（スマレジ・税抜）が「粗利目標（100%）」以上で第1段階、「粗利目標（105%）」以上で第2段階。</t>
+          <t>・その月の粗利（スマレジ・税抜）が「粗利目標（100%）」以上で第1段階、「粗利目標（105%）」以上で第2段階。売上目標は判定に使わない（目安）。</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1614,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Weekends 2027年度 予算と報奨金案（粗利2,150万円）　入力値</t>
+          <t>Weekends 2027年度 予算と報奨金案（売上6,300万円・粗利2,150万円）　入力値</t>
         </is>
       </c>
     </row>
@@ -1656,15 +1660,16 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>目標粗利率</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n">
-        <v>0.35</v>
+          <t>目標粗利率（粗利÷売上）</t>
+        </is>
+      </c>
+      <c r="B6" s="13">
+        <f>B5/B19</f>
+        <v/>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>検討案</t>
+          <t>計算値：2,150万円÷6,300万円</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1709,7 @@
           <t>テナント経費の売上連動率</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="13" t="n">
         <v>0.0692</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1809,7 +1814,7 @@
           <t>第2段階のライン</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="15" t="n">
         <v>1.05</v>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
@@ -1827,13 +1832,12 @@
           <t>年間の目標売上</t>
         </is>
       </c>
-      <c r="B19" s="8">
-        <f>ROUND(B5/B6,0)</f>
-        <v/>
+      <c r="B19" s="12" t="n">
+        <v>63000000</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>粗利÷粗利率</t>
+          <t>検討案（税抜）</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1965,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>粗利÷35%</t>
+          <t>年6,300万円×達成度</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2440,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="15" t="n">
         <v>0.31</v>
       </c>
       <c r="B4" s="8">
@@ -2457,8 +2461,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
-        <v>0.33</v>
+      <c r="A5" s="15" t="n">
+        <v>0.32</v>
       </c>
       <c r="B5" s="8">
         <f>入力!$B$19*A5</f>
@@ -2478,8 +2482,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
-        <v>0.34</v>
+      <c r="A6" s="15" t="n">
+        <v>0.33</v>
       </c>
       <c r="B6" s="8">
         <f>入力!$B$19*A6</f>
@@ -2499,8 +2503,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
-        <v>0.35</v>
+      <c r="A7" s="15">
+        <f>入力!B6</f>
+        <v/>
       </c>
       <c r="B7" s="8">
         <f>入力!$B$19*A7</f>
@@ -2520,8 +2525,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
-        <v>0.36</v>
+      <c r="A8" s="15" t="n">
+        <v>0.35</v>
       </c>
       <c r="B8" s="8">
         <f>入力!$B$19*A8</f>
@@ -2541,8 +2546,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
-        <v>0.37</v>
+      <c r="A9" s="15" t="n">
+        <v>0.36</v>
       </c>
       <c r="B9" s="8">
         <f>入力!$B$19*A9</f>
@@ -2618,7 +2623,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>黄色の「粗利目標100%」は5万円単位に丸めた目標（年計2,150万円に合わせて調整済み）。105%は5万円単位。目標売上は粗利目標÷粗利率を1万円単位で表示。</t>
+          <t>黄色の「売上目標」は10万円単位（年計6,300万円）、「粗利目標100%」は5万円単位（年計2,150万円）に丸めた目標。105%は5万円単位。</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2645,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>目標売上（参考）</t>
+          <t>売上目標</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -2697,9 +2702,8 @@
         <f>B6/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D6" s="8">
-        <f>ROUND(F6/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D6" s="12" t="n">
+        <v>3600000</v>
       </c>
       <c r="E6" s="8">
         <f>ROUND(入力!$B$5*C6,-3)</f>
@@ -2743,9 +2747,8 @@
         <f>B7/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D7" s="8">
-        <f>ROUND(F7/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D7" s="12" t="n">
+        <v>4300000</v>
       </c>
       <c r="E7" s="8">
         <f>ROUND(入力!$B$5*C7,-3)</f>
@@ -2789,9 +2792,8 @@
         <f>B8/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D8" s="8">
-        <f>ROUND(F8/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D8" s="12" t="n">
+        <v>5800000</v>
       </c>
       <c r="E8" s="8">
         <f>ROUND(入力!$B$5*C8,-3)</f>
@@ -2835,9 +2837,8 @@
         <f>B9/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D9" s="8">
-        <f>ROUND(F9/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D9" s="12" t="n">
+        <v>6000000</v>
       </c>
       <c r="E9" s="8">
         <f>ROUND(入力!$B$5*C9,-3)</f>
@@ -2881,9 +2882,8 @@
         <f>B10/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D10" s="8">
-        <f>ROUND(F10/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D10" s="12" t="n">
+        <v>8000000</v>
       </c>
       <c r="E10" s="8">
         <f>ROUND(入力!$B$5*C10,-3)</f>
@@ -2927,9 +2927,8 @@
         <f>B11/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D11" s="8">
-        <f>ROUND(F11/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D11" s="12" t="n">
+        <v>5700000</v>
       </c>
       <c r="E11" s="8">
         <f>ROUND(入力!$B$5*C11,-3)</f>
@@ -2973,9 +2972,8 @@
         <f>B12/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D12" s="8">
-        <f>ROUND(F12/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D12" s="12" t="n">
+        <v>3300000</v>
       </c>
       <c r="E12" s="8">
         <f>ROUND(入力!$B$5*C12,-3)</f>
@@ -3019,9 +3017,8 @@
         <f>B13/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D13" s="8">
-        <f>ROUND(F13/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D13" s="12" t="n">
+        <v>5200000</v>
       </c>
       <c r="E13" s="8">
         <f>ROUND(入力!$B$5*C13,-3)</f>
@@ -3065,9 +3062,8 @@
         <f>B14/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D14" s="8">
-        <f>ROUND(F14/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D14" s="12" t="n">
+        <v>4200000</v>
       </c>
       <c r="E14" s="8">
         <f>ROUND(入力!$B$5*C14,-3)</f>
@@ -3111,9 +3107,8 @@
         <f>B15/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D15" s="8">
-        <f>ROUND(F15/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D15" s="12" t="n">
+        <v>5600000</v>
       </c>
       <c r="E15" s="8">
         <f>ROUND(入力!$B$5*C15,-3)</f>
@@ -3157,9 +3152,8 @@
         <f>B16/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D16" s="8">
-        <f>ROUND(F16/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D16" s="12" t="n">
+        <v>5700000</v>
       </c>
       <c r="E16" s="8">
         <f>ROUND(入力!$B$5*C16,-3)</f>
@@ -3203,9 +3197,8 @@
         <f>B17/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D17" s="8">
-        <f>ROUND(F17/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D17" s="12" t="n">
+        <v>5600000</v>
       </c>
       <c r="E17" s="8">
         <f>ROUND(入力!$B$5*C17,-3)</f>
@@ -3281,6 +3274,10 @@
           <t>年間目標との差</t>
         </is>
       </c>
+      <c r="D19" s="8">
+        <f>D18-入力!B19</f>
+        <v/>
+      </c>
       <c r="F19" s="8">
         <f>F18-入力!B5</f>
         <v/>
@@ -3289,7 +3286,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>（丸めた目標を直したら、F19が0円になるように調整してください）</t>
+          <t>（丸めた目標を直したら、D19とF19が0円になるように調整してください）</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3337,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>黄色の「粗利目標100%」は5万円単位に丸めた目標（年計2,150万円に合わせて調整済み）。105%は5万円単位。目標売上は粗利目標÷粗利率を1万円単位で表示。</t>
+          <t>黄色の「売上目標」は10万円単位（年計6,300万円）、「粗利目標100%」は5万円単位（年計2,150万円）に丸めた目標。105%は5万円単位。</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3359,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>目標売上（参考）</t>
+          <t>売上目標</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -3424,9 +3421,8 @@
         <f>B6/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D6" s="8">
-        <f>ROUND(F6/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D6" s="12" t="n">
+        <v>3700000</v>
       </c>
       <c r="E6" s="8">
         <f>ROUND(入力!$B$5*C6,-3)</f>
@@ -3474,9 +3470,8 @@
         <f>B7/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D7" s="8">
-        <f>ROUND(F7/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D7" s="12" t="n">
+        <v>4700000</v>
       </c>
       <c r="E7" s="8">
         <f>ROUND(入力!$B$5*C7,-3)</f>
@@ -3524,9 +3519,8 @@
         <f>B8/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D8" s="8">
-        <f>ROUND(F8/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D8" s="12" t="n">
+        <v>5800000</v>
       </c>
       <c r="E8" s="8">
         <f>ROUND(入力!$B$5*C8,-3)</f>
@@ -3574,9 +3568,8 @@
         <f>B9/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D9" s="8">
-        <f>ROUND(F9/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D9" s="12" t="n">
+        <v>5800000</v>
       </c>
       <c r="E9" s="8">
         <f>ROUND(入力!$B$5*C9,-3)</f>
@@ -3624,9 +3617,8 @@
         <f>B10/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D10" s="8">
-        <f>ROUND(F10/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D10" s="12" t="n">
+        <v>7300000</v>
       </c>
       <c r="E10" s="8">
         <f>ROUND(入力!$B$5*C10,-3)</f>
@@ -3674,9 +3666,8 @@
         <f>B11/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D11" s="8">
-        <f>ROUND(F11/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D11" s="12" t="n">
+        <v>6300000</v>
       </c>
       <c r="E11" s="8">
         <f>ROUND(入力!$B$5*C11,-3)</f>
@@ -3724,9 +3715,8 @@
         <f>B12/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D12" s="8">
-        <f>ROUND(F12/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D12" s="12" t="n">
+        <v>3700000</v>
       </c>
       <c r="E12" s="8">
         <f>ROUND(入力!$B$5*C12,-3)</f>
@@ -3774,9 +3764,8 @@
         <f>B13/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D13" s="8">
-        <f>ROUND(F13/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D13" s="12" t="n">
+        <v>5800000</v>
       </c>
       <c r="E13" s="8">
         <f>ROUND(入力!$B$5*C13,-3)</f>
@@ -3824,9 +3813,8 @@
         <f>B14/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D14" s="8">
-        <f>ROUND(F14/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D14" s="12" t="n">
+        <v>4700000</v>
       </c>
       <c r="E14" s="8">
         <f>ROUND(入力!$B$5*C14,-3)</f>
@@ -3874,9 +3862,8 @@
         <f>B15/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D15" s="8">
-        <f>ROUND(F15/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D15" s="12" t="n">
+        <v>4700000</v>
       </c>
       <c r="E15" s="8">
         <f>ROUND(入力!$B$5*C15,-3)</f>
@@ -3924,9 +3911,8 @@
         <f>B16/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D16" s="8">
-        <f>ROUND(F16/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D16" s="12" t="n">
+        <v>5800000</v>
       </c>
       <c r="E16" s="8">
         <f>ROUND(入力!$B$5*C16,-3)</f>
@@ -3974,9 +3960,8 @@
         <f>B17/SUM($B$6:$B$17)</f>
         <v/>
       </c>
-      <c r="D17" s="8">
-        <f>ROUND(F17/入力!$B$6,-4)</f>
-        <v/>
+      <c r="D17" s="12" t="n">
+        <v>4700000</v>
       </c>
       <c r="E17" s="8">
         <f>ROUND(入力!$B$5*C17,-3)</f>
@@ -4056,6 +4041,10 @@
           <t>年間目標との差</t>
         </is>
       </c>
+      <c r="D19" s="8">
+        <f>D18-入力!B19</f>
+        <v/>
+      </c>
       <c r="F19" s="8">
         <f>F18-入力!B5</f>
         <v/>
@@ -4064,7 +4053,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>（丸めた目標を直したら、F19が0円になるように調整してください）</t>
+          <t>（丸めた目標を直したら、D19とF19が0円になるように調整してください）</t>
         </is>
       </c>
     </row>

--- a/excel/Weekends_予算と報奨金案_粗利2150万円.xlsx
+++ b/excel/Weekends_予算と報奨金案_粗利2150万円.xlsx
@@ -1784,12 +1784,13 @@
           <t>報奨金 第1段階（店舗計・月）</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n">
-        <v>30000</v>
+      <c r="B14" s="14">
+        <f>'報奨金（例B）'!D8</f>
+        <v/>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>粗利が月の目標の100%以上（例B）</t>
+          <t>粗利が月の目標の100%以上。1人あたりの額は「報奨金（例B）」シートで入力</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1800,13 @@
           <t>報奨金 第2段階（店舗計・月）</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
-        <v>50000</v>
+      <c r="B15" s="14">
+        <f>'報奨金（例B）'!E8</f>
+        <v/>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>粗利が月の目標の105%以上（例B）</t>
+          <t>粗利が月の目標の105%以上。同上</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4089,7 +4091,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>毎月、その月の粗利（スマレジ・税抜）が目標の100%以上で第1段階、105%以上で第2段階。店舗計を重みで配分。</t>
+          <t>毎月、その月の粗利（スマレジ・税抜）が目標の100%以上で第1段階、105%以上で第2段階。黄色の1人あたり月額を直接入力（店舗計は自動で入力シートに反映）。</t>
         </is>
       </c>
     </row>
@@ -4106,17 +4108,17 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>重み</t>
+          <t>店舗計に占める割合</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>第1段階（月額）</t>
+          <t>第1段階 1人月額（100%以上）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>第2段階（月額）</t>
+          <t>第2段階 1人月額（105%以上）</t>
         </is>
       </c>
     </row>
@@ -4129,16 +4131,15 @@
       <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="D5" s="8">
-        <f>ROUND(入力!$B$14*C5/SUMPRODUCT($B$5:$B$7,$C$5:$C$7),-2)</f>
-        <v/>
-      </c>
-      <c r="E5" s="8">
-        <f>ROUND(入力!$B$15*C5/SUMPRODUCT($B$5:$B$7,$C$5:$C$7),-2)</f>
-        <v/>
+      <c r="C5" s="16">
+        <f>B5*D5/$D$8</f>
+        <v/>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>23000</v>
       </c>
     </row>
     <row r="6">
@@ -4150,16 +4151,15 @@
       <c r="B6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D6" s="8">
-        <f>ROUND(入力!$B$14*C6/SUMPRODUCT($B$5:$B$7,$C$5:$C$7),-2)</f>
-        <v/>
-      </c>
-      <c r="E6" s="8">
-        <f>ROUND(入力!$B$15*C6/SUMPRODUCT($B$5:$B$7,$C$5:$C$7),-2)</f>
-        <v/>
+      <c r="C6" s="16">
+        <f>B6*D6/$D$8</f>
+        <v/>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>15000</v>
       </c>
     </row>
     <row r="7">
@@ -4171,16 +4171,15 @@
       <c r="B7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D7" s="8">
-        <f>ROUND(入力!$B$14*C7/SUMPRODUCT($B$5:$B$7,$C$5:$C$7),-2)</f>
-        <v/>
-      </c>
-      <c r="E7" s="8">
-        <f>ROUND(入力!$B$15*C7/SUMPRODUCT($B$5:$B$7,$C$5:$C$7),-2)</f>
-        <v/>
+      <c r="C7" s="16">
+        <f>B7*D7/$D$8</f>
+        <v/>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>6000</v>
       </c>
     </row>
     <row r="8">
@@ -4209,23 +4208,30 @@
         </is>
       </c>
       <c r="D9" s="10">
-        <f>入力!B14*12</f>
+        <f>D8*12</f>
         <v/>
       </c>
       <c r="E9" s="10">
-        <f>入力!B15*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>・判定は粗利額だけ（値引きで売上を作っても出ない）。処分品は粗利の計算から除く。</t>
+        <f>E8*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>（第1段階は社長案の店舗計3万円に対し2.6万円。第2段階は同じ比率12:8:3で5万円に配分した案）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>・判定は粗利額だけ（値引きで売上を作っても出ない）。処分品は粗利の計算から除く。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>・判定は毎月、支払いは夏冬の賞与にまとめる案（社会保険・扶養への影響は社労士に確認）。</t>
         </is>

--- a/excel/Weekends_予算と報奨金案_粗利2150万円.xlsx
+++ b/excel/Weekends_予算と報奨金案_粗利2150万円.xlsx
@@ -4139,7 +4139,7 @@
         <v>12000</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>23000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="6">
@@ -4159,7 +4159,7 @@
         <v>8000</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>15000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="7">
@@ -4176,10 +4176,10 @@
         <v/>
       </c>
       <c r="D7" s="12" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>6000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="8">
@@ -4219,7 +4219,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>（第1段階は社長案の店舗計3万円に対し2.6万円。第2段階は同じ比率12:8:3で5万円に配分した案）</t>
+          <t>（第1段階は社長案の店舗計3万円を店長1.2万・古参0.8万・パート各0.5万で配分。第2段階は同じ比率で5万円を配分）</t>
         </is>
       </c>
     </row>

--- a/excel/Weekends_予算と報奨金案_粗利2150万円.xlsx
+++ b/excel/Weekends_予算と報奨金案_粗利2150万円.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yataka-02\AppData\Local\Temp\claude\C--Users-yataka-02-Desktop-Claude\76fa42a7-01fc-42d8-86c7-11cf90447c56\scratchpad\margin-calculator\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9408D53-C28D-450B-AD43-39BFDE71A695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D69B8E-865B-4E64-8006-4D4705C3B0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="164">
   <si>
     <t>Weekends 2027年度 月別目標（売上6,300万円・粗利2,150万円・税抜）</t>
   </si>
@@ -154,9 +154,6 @@
     <t>・日数は暦日。定休日を除いた営業日数にしたい場合は青字の日数を書き換える。</t>
   </si>
   <si>
-    <t>Weekends 2027年度 予算と報奨金案（売上6,300万円・粗利2,150万円）　入力値</t>
-  </si>
-  <si>
     <t>青字・黄色＝入力値（変えると全シートが再計算）。金額はすべて税抜・円。</t>
   </si>
   <si>
@@ -172,9 +169,6 @@
     <t>年間の目標粗利</t>
   </si>
   <si>
-    <t>検討案</t>
-  </si>
-  <si>
     <t>目標粗利率（粗利÷売上）</t>
   </si>
   <si>
@@ -244,9 +238,6 @@
     <t>年間の目標売上</t>
   </si>
   <si>
-    <t>検討案（税抜）</t>
-  </si>
-  <si>
     <t>年間の固定費</t>
   </si>
   <si>
@@ -346,9 +337,6 @@
     <t>粗利率1ポイントあたりの営業利益の変化</t>
   </si>
   <si>
-    <t>月別の目標と営業利益　構成比版（全月で100%達成した場合）</t>
-  </si>
-  <si>
     <t>月の目標は前年（2025/8〜2026/7）の売上構成比で配分。固定費は12等分。黄色の実績粗利（スマレジ・税抜）を入れると段階と報奨金が出る。</t>
   </si>
   <si>
@@ -383,9 +371,6 @@
   </si>
   <si>
     <t>（丸めた目標を直したら、D19とF19が0円になるように調整してください）</t>
-  </si>
-  <si>
-    <t>月別の目標と営業利益　スマレジ版（全月で100%達成した場合）</t>
   </si>
   <si>
     <t>月の目標は、店長がスマレジに登録した店舗予算（年6,000万円・税抜）の月比率で配分。同じ予算額の月は同じ目標にそろえた。</t>
@@ -536,6 +521,30 @@
   </si>
   <si>
     <t>赤字の月数</t>
+  </si>
+  <si>
+    <t>2026-10-06：毎月の営業利益がマイナスにならないよう、閑散月の粗利目標を180万円に引き上げ（旧2,150万円）</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>同上（旧6,300万円）。閑散月の売上目標を530万円に引き上げ</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>Weekends 2027年度 予算と報奨金案（売上6,860万円・粗利2,340万円）　入力値</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>月別の目標と営業利益　スマレジ版（全月で100%達成した場合）</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>黄色の「売上目標」は10万円単位、「粗利目標100%」は5万円単位。2026-10-06に、毎月の営業利益がマイナスにならないよう8・9・2・4・5・7月を粗利180万円・売上530万円に引き上げた（年計 売上6,860万円・粗利2,340万円）。</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>月別の目標と営業利益　構成比版（旧案：年2,150万円のまま。現在は使っていない）</t>
+    <phoneticPr fontId="9"/>
   </si>
 </sst>
 </file>
@@ -545,7 +554,7 @@
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="#,##0;[Red]\-#,##0;\-"/>
     <numFmt numFmtId="177" formatCode="0.0%"/>
-    <numFmt numFmtId="181" formatCode="0&quot;か月&quot;"/>
+    <numFmt numFmtId="178" formatCode="0&quot;か月&quot;"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -668,7 +677,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -710,11 +719,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -817,22 +825,22 @@
                 <c:formatCode>#,##0;[Red]\-#,##0;\-</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>-1128264</c:v>
+                  <c:v>232968</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-271244</c:v>
+                  <c:v>1165612</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>225776</c:v>
+                  <c:v>1738256</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>739988</c:v>
+                  <c:v>2297842.3999999985</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>842796</c:v>
+                  <c:v>2430900</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1699816.0000000037</c:v>
+                  <c:v>3363544.0000000037</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1320,10 +1328,10 @@
                 <c:formatCode>#,##0;[Red]\-#,##0;\-</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>-415592</c:v>
+                  <c:v>23688</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-134792</c:v>
+                  <c:v>23688</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>189088</c:v>
@@ -1338,22 +1346,22 @@
                   <c:v>254488</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-415592</c:v>
+                  <c:v>23688</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>189088</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-134792</c:v>
+                  <c:v>23688</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-134792</c:v>
+                  <c:v>23688</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>189088</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-134792</c:v>
+                  <c:v>23688</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1408,40 +1416,40 @@
                 <c:formatCode>#,##0;[Red]\-#,##0;\-</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>-415592</c:v>
+                  <c:v>23688</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-550384</c:v>
+                  <c:v>47376</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-361296</c:v>
+                  <c:v>236464</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-172208</c:v>
+                  <c:v>425552</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>413080</c:v>
+                  <c:v>1010840</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>667568</c:v>
+                  <c:v>1265328</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>251976</c:v>
+                  <c:v>1289016</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>441064</c:v>
+                  <c:v>1478104</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>306272</c:v>
+                  <c:v>1501792</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>171480</c:v>
+                  <c:v>1525480</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>360568</c:v>
+                  <c:v>1714568</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>225776</c:v>
+                  <c:v>1738256</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1921,67 +1929,53 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
+      <c r="A2" s="19" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
+      <c r="A3" s="19" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="21" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="G6" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>155</v>
-      </c>
       <c r="H6" s="22" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B7" s="23">
         <f>1</f>
@@ -2010,71 +2004,71 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B8" s="24">
         <f>入力!$B$19*B7</f>
-        <v>63000000</v>
+        <v>68600000</v>
       </c>
       <c r="C8" s="24">
         <f>入力!$B$19*C7</f>
-        <v>63000000</v>
+        <v>68600000</v>
       </c>
       <c r="D8" s="24">
         <f>入力!$B$19*D7</f>
-        <v>63000000</v>
+        <v>68600000</v>
       </c>
       <c r="E8" s="24">
         <f>入力!$B$19*E7</f>
-        <v>66150000</v>
+        <v>72030000</v>
       </c>
       <c r="F8" s="24">
         <f>入力!$B$19*F7</f>
-        <v>66150000</v>
+        <v>72030000</v>
       </c>
       <c r="G8" s="24">
         <f>入力!$B$19*G7</f>
-        <v>66150000</v>
+        <v>72030000</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B9" s="24">
         <f>入力!$B$5*B7</f>
-        <v>21500000</v>
+        <v>23400000</v>
       </c>
       <c r="C9" s="24">
         <f>入力!$B$5*C7</f>
-        <v>21500000</v>
+        <v>23400000</v>
       </c>
       <c r="D9" s="24">
         <f>入力!$B$5*D7</f>
-        <v>21500000</v>
+        <v>23400000</v>
       </c>
       <c r="E9" s="24">
         <f>入力!$B$5*E7</f>
-        <v>22575000</v>
+        <v>24570000</v>
       </c>
       <c r="F9" s="24">
         <f>入力!$B$5*F7</f>
-        <v>22575000</v>
+        <v>24570000</v>
       </c>
       <c r="G9" s="24">
         <f>入力!$B$5*G7</f>
-        <v>22575000</v>
+        <v>24570000</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B10" s="24">
         <f>入力!$B$7*12</f>
@@ -2101,12 +2095,12 @@
         <v>9600000</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B11" s="24">
         <f>IF(B7&gt;=入力!$B$16,入力!$B$15,IF(B7&gt;=1,入力!$B$14,0))*12</f>
@@ -2133,44 +2127,44 @@
         <v>600000</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B12" s="24">
         <f>入力!$B$8*12+B8*入力!$B$9</f>
-        <v>6877104</v>
+        <v>7264624</v>
       </c>
       <c r="C12" s="24">
         <f>入力!$B$8*12+C8*入力!$B$9</f>
-        <v>6877104</v>
+        <v>7264624</v>
       </c>
       <c r="D12" s="24">
         <f>入力!$B$8*12+D8*入力!$B$9</f>
-        <v>6877104</v>
+        <v>7264624</v>
       </c>
       <c r="E12" s="24">
         <f>入力!$B$8*12+E8*入力!$B$9</f>
-        <v>7095084</v>
+        <v>7501980</v>
       </c>
       <c r="F12" s="24">
         <f>入力!$B$8*12+F8*入力!$B$9</f>
-        <v>7095084</v>
+        <v>7501980</v>
       </c>
       <c r="G12" s="24">
         <f>入力!$B$8*12+G8*入力!$B$9</f>
-        <v>7095084</v>
+        <v>7501980</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B13" s="24">
         <f>入力!$B$10</f>
@@ -2199,71 +2193,71 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="26" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B14" s="27">
-        <f>SUM(B10:B13)</f>
-        <v>20330372</v>
+        <f t="shared" ref="B14:G14" si="0">SUM(B10:B13)</f>
+        <v>20717892</v>
       </c>
       <c r="C14" s="27">
-        <f>SUM(C10:C13)</f>
-        <v>20330372</v>
+        <f t="shared" si="0"/>
+        <v>20717892</v>
       </c>
       <c r="D14" s="27">
-        <f>SUM(D10:D13)</f>
-        <v>20330372</v>
+        <f t="shared" si="0"/>
+        <v>20717892</v>
       </c>
       <c r="E14" s="27">
-        <f>SUM(E10:E13)</f>
-        <v>20788352</v>
+        <f t="shared" si="0"/>
+        <v>21195248</v>
       </c>
       <c r="F14" s="27">
-        <f>SUM(F10:F13)</f>
-        <v>20788352</v>
+        <f t="shared" si="0"/>
+        <v>21195248</v>
       </c>
       <c r="G14" s="27">
-        <f>SUM(G10:G13)</f>
-        <v>20788352</v>
+        <f t="shared" si="0"/>
+        <v>21195248</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="26" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B15" s="27">
-        <f>B9-B14</f>
-        <v>1169628</v>
+        <f t="shared" ref="B15:G15" si="1">B9-B14</f>
+        <v>2682108</v>
       </c>
       <c r="C15" s="27">
-        <f>C9-C14</f>
-        <v>1169628</v>
+        <f t="shared" si="1"/>
+        <v>2682108</v>
       </c>
       <c r="D15" s="27">
-        <f>D9-D14</f>
-        <v>1169628</v>
+        <f t="shared" si="1"/>
+        <v>2682108</v>
       </c>
       <c r="E15" s="27">
-        <f>E9-E14</f>
-        <v>1786648</v>
+        <f t="shared" si="1"/>
+        <v>3374752</v>
       </c>
       <c r="F15" s="27">
-        <f>F9-F14</f>
-        <v>1786648</v>
+        <f t="shared" si="1"/>
+        <v>3374752</v>
       </c>
       <c r="G15" s="27">
-        <f>G9-G14</f>
-        <v>1786648</v>
+        <f t="shared" si="1"/>
+        <v>3374752</v>
       </c>
       <c r="H15" s="26" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B16" s="24">
         <v>0</v>
@@ -2286,12 +2280,12 @@
         <v>0</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B17" s="24">
         <v>0</v>
@@ -2314,44 +2308,44 @@
         <v>1896000</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="26" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B18" s="27">
-        <f>B15-B16-B17</f>
-        <v>1169628</v>
+        <f t="shared" ref="B18:G18" si="2">B15-B16-B17</f>
+        <v>2682108</v>
       </c>
       <c r="C18" s="27">
-        <f>C15-C16-C17</f>
-        <v>225776</v>
+        <f t="shared" si="2"/>
+        <v>1738256</v>
       </c>
       <c r="D18" s="27">
-        <f>D15-D16-D17</f>
-        <v>-726372</v>
+        <f t="shared" si="2"/>
+        <v>786108</v>
       </c>
       <c r="E18" s="27">
-        <f>E15-E16-E17</f>
-        <v>1786648</v>
+        <f t="shared" si="2"/>
+        <v>3374752</v>
       </c>
       <c r="F18" s="27">
-        <f>F15-F16-F17</f>
-        <v>842796</v>
+        <f t="shared" si="2"/>
+        <v>2430900</v>
       </c>
       <c r="G18" s="27">
-        <f>G15-G16-G17</f>
-        <v>-109352</v>
+        <f t="shared" si="2"/>
+        <v>1478752</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B19" s="24">
         <f>入力!$B$13</f>
@@ -2380,118 +2374,118 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="26" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B20" s="27">
-        <f>B18-B19</f>
-        <v>869628</v>
+        <f t="shared" ref="B20:G20" si="3">B18-B19</f>
+        <v>2382108</v>
       </c>
       <c r="C20" s="27">
-        <f>C18-C19</f>
-        <v>-74224</v>
+        <f t="shared" si="3"/>
+        <v>1438256</v>
       </c>
       <c r="D20" s="27">
-        <f>D18-D19</f>
-        <v>-1026372</v>
+        <f t="shared" si="3"/>
+        <v>486108</v>
       </c>
       <c r="E20" s="27">
-        <f>E18-E19</f>
-        <v>1486648</v>
+        <f t="shared" si="3"/>
+        <v>3074752</v>
       </c>
       <c r="F20" s="27">
-        <f>F18-F19</f>
-        <v>542796</v>
+        <f t="shared" si="3"/>
+        <v>2130900</v>
       </c>
       <c r="G20" s="27">
-        <f>G18-G19</f>
-        <v>-409352</v>
+        <f t="shared" si="3"/>
+        <v>1178752</v>
       </c>
       <c r="H20" s="26"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B21" s="24">
         <f>(入力!$B$7*12+入力!$B$8*12+入力!$B$10+B16+B17)/入力!$B$21</f>
-        <v>57377811.25294625</v>
+        <v>57411989.95543851</v>
       </c>
       <c r="C21" s="24">
         <f>(入力!$B$7*12+入力!$B$8*12+入力!$B$10+C16+C17)/入力!$B$21</f>
-        <v>60846964.598259076</v>
+        <v>60883209.79923743</v>
       </c>
       <c r="D21" s="24">
         <f>(入力!$B$7*12+入力!$B$8*12+入力!$B$10+D16+D17)/入力!$B$21</f>
-        <v>64346610.114116348</v>
+        <v>64384939.977097362</v>
       </c>
       <c r="E21" s="24">
         <f>(入力!$B$7*12+入力!$B$8*12+入力!$B$10+E16+E17)/入力!$B$21</f>
-        <v>57377811.25294625</v>
+        <v>57411989.95543851</v>
       </c>
       <c r="F21" s="24">
         <f>(入力!$B$7*12+入力!$B$8*12+入力!$B$10+F16+F17)/入力!$B$21</f>
-        <v>60846964.598259076</v>
+        <v>60883209.79923743</v>
       </c>
       <c r="G21" s="24">
         <f>(入力!$B$7*12+入力!$B$8*12+入力!$B$10+G16+G17)/入力!$B$21</f>
-        <v>64346610.114116348</v>
+        <v>64384939.977097362</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B22" s="25">
         <f>B21/入力!$B$19</f>
-        <v>0.91075890877692456</v>
+        <v>0.8369094745690745</v>
       </c>
       <c r="C22" s="25">
         <f>C21/入力!$B$19</f>
-        <v>0.96582483489300119</v>
+        <v>0.88751034692765929</v>
       </c>
       <c r="D22" s="25">
         <f>D21/入力!$B$19</f>
-        <v>1.0213747637161326</v>
+        <v>0.93855597634252719</v>
       </c>
       <c r="E22" s="25">
         <f>E21/入力!$B$19</f>
-        <v>0.91075890877692456</v>
+        <v>0.8369094745690745</v>
       </c>
       <c r="F22" s="25">
         <f>F21/入力!$B$19</f>
-        <v>0.96582483489300119</v>
+        <v>0.88751034692765929</v>
       </c>
       <c r="G22" s="25">
         <f>G21/入力!$B$19</f>
-        <v>1.0213747637161326</v>
+        <v>0.93855597634252719</v>
       </c>
       <c r="H22" s="19" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="21" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="30" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -2501,18 +2495,18 @@
       </c>
       <c r="B27" s="24">
         <f>C27+入力!$B$11</f>
-        <v>-184412</v>
+        <v>1176820</v>
       </c>
       <c r="C27" s="24">
         <f>達成度別!E4</f>
-        <v>-1128264</v>
+        <v>232968</v>
       </c>
       <c r="D27" s="24">
         <f>C27+入力!$B$11-入力!$B$12*12</f>
-        <v>-2080412</v>
+        <v>-719180</v>
       </c>
       <c r="E27" s="24">
-        <f>B27-C27</f>
+        <f t="shared" ref="E27:E32" si="4">B27-C27</f>
         <v>943852</v>
       </c>
     </row>
@@ -2523,18 +2517,18 @@
       </c>
       <c r="B28" s="24">
         <f>C28+入力!$B$11</f>
-        <v>672608</v>
+        <v>2109464</v>
       </c>
       <c r="C28" s="24">
         <f>達成度別!E5</f>
-        <v>-271244</v>
+        <v>1165612</v>
       </c>
       <c r="D28" s="24">
         <f>C28+入力!$B$11-入力!$B$12*12</f>
-        <v>-1223392</v>
+        <v>213464</v>
       </c>
       <c r="E28" s="24">
-        <f>B28-C28</f>
+        <f t="shared" si="4"/>
         <v>943852</v>
       </c>
     </row>
@@ -2545,18 +2539,18 @@
       </c>
       <c r="B29" s="27">
         <f>C29+入力!$B$11</f>
-        <v>1169628</v>
+        <v>2682108</v>
       </c>
       <c r="C29" s="27">
         <f>達成度別!E6</f>
-        <v>225776</v>
+        <v>1738256</v>
       </c>
       <c r="D29" s="27">
         <f>C29+入力!$B$11-入力!$B$12*12</f>
-        <v>-726372</v>
+        <v>786108</v>
       </c>
       <c r="E29" s="27">
-        <f>B29-C29</f>
+        <f t="shared" si="4"/>
         <v>943852</v>
       </c>
     </row>
@@ -2567,18 +2561,18 @@
       </c>
       <c r="B30" s="24">
         <f>C30+入力!$B$11</f>
-        <v>1683840</v>
+        <v>3241694.3999999985</v>
       </c>
       <c r="C30" s="24">
         <f>達成度別!E7</f>
-        <v>739988</v>
+        <v>2297842.3999999985</v>
       </c>
       <c r="D30" s="24">
         <f>C30+入力!$B$11-入力!$B$12*12</f>
-        <v>-212160</v>
+        <v>1345694.3999999985</v>
       </c>
       <c r="E30" s="24">
-        <f>B30-C30</f>
+        <f t="shared" si="4"/>
         <v>943852</v>
       </c>
     </row>
@@ -2589,18 +2583,18 @@
       </c>
       <c r="B31" s="24">
         <f>C31+入力!$B$11</f>
-        <v>1786648</v>
+        <v>3374752</v>
       </c>
       <c r="C31" s="24">
         <f>達成度別!E8</f>
-        <v>842796</v>
+        <v>2430900</v>
       </c>
       <c r="D31" s="24">
         <f>C31+入力!$B$11-入力!$B$12*12</f>
-        <v>-109352</v>
+        <v>1478752</v>
       </c>
       <c r="E31" s="24">
-        <f>B31-C31</f>
+        <f t="shared" si="4"/>
         <v>943852</v>
       </c>
     </row>
@@ -2611,24 +2605,24 @@
       </c>
       <c r="B32" s="24">
         <f>C32+入力!$B$11</f>
-        <v>2643668.0000000037</v>
+        <v>4307396.0000000037</v>
       </c>
       <c r="C32" s="24">
         <f>達成度別!E9</f>
-        <v>1699816.0000000037</v>
+        <v>3363544.0000000037</v>
       </c>
       <c r="D32" s="24">
         <f>C32+入力!$B$11-入力!$B$12*12</f>
-        <v>747668.00000000373</v>
+        <v>2411396.0000000037</v>
       </c>
       <c r="E32" s="24">
-        <f>B32-C32</f>
+        <f t="shared" si="4"/>
         <v>943852</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="21" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="30" x14ac:dyDescent="0.3">
@@ -2636,16 +2630,16 @@
         <v>4</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -2655,19 +2649,19 @@
       </c>
       <c r="B37" s="24">
         <f>'月別（スマレジ版）'!F6</f>
-        <v>1250000</v>
+        <v>1800000</v>
       </c>
       <c r="C37" s="24">
         <f>D37+入力!$B$11/12</f>
-        <v>-336937.66666666669</v>
+        <v>102342.33333333333</v>
       </c>
       <c r="D37" s="24">
         <f>'月別（スマレジ版）'!H6</f>
-        <v>-415592</v>
+        <v>23688</v>
       </c>
       <c r="E37" s="24">
         <f>D37+入力!$B$11/12-入力!$B$12</f>
-        <v>-494937.66666666669</v>
+        <v>-55657.666666666672</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -2677,19 +2671,19 @@
       </c>
       <c r="B38" s="24">
         <f>'月別（スマレジ版）'!F7</f>
-        <v>1600000</v>
+        <v>1800000</v>
       </c>
       <c r="C38" s="24">
         <f>D38+入力!$B$11/12</f>
-        <v>-56137.666666666672</v>
+        <v>102342.33333333333</v>
       </c>
       <c r="D38" s="24">
         <f>'月別（スマレジ版）'!H7</f>
-        <v>-134792</v>
+        <v>23688</v>
       </c>
       <c r="E38" s="24">
         <f>D38+入力!$B$11/12-入力!$B$12</f>
-        <v>-214137.66666666669</v>
+        <v>-55657.666666666672</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -2787,19 +2781,19 @@
       </c>
       <c r="B43" s="24">
         <f>'月別（スマレジ版）'!F12</f>
-        <v>1250000</v>
+        <v>1800000</v>
       </c>
       <c r="C43" s="24">
         <f>D43+入力!$B$11/12</f>
-        <v>-336937.66666666669</v>
+        <v>102342.33333333333</v>
       </c>
       <c r="D43" s="24">
         <f>'月別（スマレジ版）'!H12</f>
-        <v>-415592</v>
+        <v>23688</v>
       </c>
       <c r="E43" s="24">
         <f>D43+入力!$B$11/12-入力!$B$12</f>
-        <v>-494937.66666666669</v>
+        <v>-55657.666666666672</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -2831,19 +2825,19 @@
       </c>
       <c r="B45" s="24">
         <f>'月別（スマレジ版）'!F14</f>
-        <v>1600000</v>
+        <v>1800000</v>
       </c>
       <c r="C45" s="24">
         <f>D45+入力!$B$11/12</f>
-        <v>-56137.666666666672</v>
+        <v>102342.33333333333</v>
       </c>
       <c r="D45" s="24">
         <f>'月別（スマレジ版）'!H14</f>
-        <v>-134792</v>
+        <v>23688</v>
       </c>
       <c r="E45" s="24">
         <f>D45+入力!$B$11/12-入力!$B$12</f>
-        <v>-214137.66666666669</v>
+        <v>-55657.666666666672</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -2853,19 +2847,19 @@
       </c>
       <c r="B46" s="24">
         <f>'月別（スマレジ版）'!F15</f>
-        <v>1600000</v>
+        <v>1800000</v>
       </c>
       <c r="C46" s="24">
         <f>D46+入力!$B$11/12</f>
-        <v>-56137.666666666672</v>
+        <v>102342.33333333333</v>
       </c>
       <c r="D46" s="24">
         <f>'月別（スマレジ版）'!H15</f>
-        <v>-134792</v>
+        <v>23688</v>
       </c>
       <c r="E46" s="24">
         <f>D46+入力!$B$11/12-入力!$B$12</f>
-        <v>-214137.66666666669</v>
+        <v>-55657.666666666672</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -2897,19 +2891,19 @@
       </c>
       <c r="B48" s="24">
         <f>'月別（スマレジ版）'!F17</f>
-        <v>1600000</v>
+        <v>1800000</v>
       </c>
       <c r="C48" s="24">
         <f>D48+入力!$B$11/12</f>
-        <v>-56137.666666666672</v>
+        <v>102342.33333333333</v>
       </c>
       <c r="D48" s="24">
         <f>'月別（スマレジ版）'!H17</f>
-        <v>-134792</v>
+        <v>23688</v>
       </c>
       <c r="E48" s="24">
         <f>D48+入力!$B$11/12-入力!$B$12</f>
-        <v>-214137.66666666669</v>
+        <v>-55657.666666666672</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -2918,32 +2912,32 @@
       </c>
       <c r="B49" s="27">
         <f>SUM(B37:B48)</f>
-        <v>21500000</v>
+        <v>23400000</v>
       </c>
       <c r="C49" s="27">
         <f>SUM(C37:C48)</f>
-        <v>1169627.9999999998</v>
+        <v>2682108.0000000005</v>
       </c>
       <c r="D49" s="27">
         <f>SUM(D37:D48)</f>
-        <v>225776</v>
+        <v>1738256</v>
       </c>
       <c r="E49" s="27">
         <f>SUM(E37:E48)</f>
-        <v>-726372.00000000012</v>
+        <v>786108.00000000012</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="30" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C50" s="31">
         <f>COUNTIF(C37:C48,"&lt;0")</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D50" s="31">
         <f>COUNTIF(D37:D48,"&lt;0")</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E50" s="31">
         <f>COUNTIF(E37:E48,"&lt;0")</f>
@@ -3025,23 +3019,23 @@
       </c>
       <c r="C6" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F6,月別目標と営業利益!F6)</f>
-        <v>1250000</v>
+        <v>1800000</v>
       </c>
       <c r="D6" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G6,月別目標と営業利益!G6)</f>
-        <v>1300000</v>
+        <v>1900000</v>
       </c>
       <c r="E6" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D6,月別目標と営業利益!D6)</f>
-        <v>3700000</v>
+        <v>5300000</v>
       </c>
       <c r="F6" s="8">
         <f t="shared" ref="F6:F17" si="0">ROUND(C6/B6,-3)</f>
-        <v>40000</v>
+        <v>58000</v>
       </c>
       <c r="G6" s="8">
         <f t="shared" ref="G6:G17" si="1">ROUND(E6/B6,-3)</f>
-        <v>119000</v>
+        <v>171000</v>
       </c>
       <c r="H6" s="8">
         <f>入力!$B$14</f>
@@ -3061,23 +3055,23 @@
       </c>
       <c r="C7" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F7,月別目標と営業利益!F7)</f>
-        <v>1600000</v>
+        <v>1800000</v>
       </c>
       <c r="D7" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G7,月別目標と営業利益!G7)</f>
-        <v>1700000</v>
+        <v>1900000</v>
       </c>
       <c r="E7" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D7,月別目標と営業利益!D7)</f>
-        <v>4700000</v>
+        <v>5300000</v>
       </c>
       <c r="F7" s="8">
         <f t="shared" si="0"/>
-        <v>53000</v>
+        <v>60000</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="1"/>
-        <v>157000</v>
+        <v>177000</v>
       </c>
       <c r="H7" s="8">
         <f>入力!$B$14</f>
@@ -3241,23 +3235,23 @@
       </c>
       <c r="C12" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F12,月別目標と営業利益!F12)</f>
-        <v>1250000</v>
+        <v>1800000</v>
       </c>
       <c r="D12" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G12,月別目標と営業利益!G12)</f>
-        <v>1300000</v>
+        <v>1900000</v>
       </c>
       <c r="E12" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D12,月別目標と営業利益!D12)</f>
-        <v>3700000</v>
+        <v>5300000</v>
       </c>
       <c r="F12" s="8">
         <f t="shared" si="0"/>
-        <v>45000</v>
+        <v>64000</v>
       </c>
       <c r="G12" s="8">
         <f t="shared" si="1"/>
-        <v>132000</v>
+        <v>189000</v>
       </c>
       <c r="H12" s="8">
         <f>入力!$B$14</f>
@@ -3313,23 +3307,23 @@
       </c>
       <c r="C14" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F14,月別目標と営業利益!F14)</f>
-        <v>1600000</v>
+        <v>1800000</v>
       </c>
       <c r="D14" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G14,月別目標と営業利益!G14)</f>
-        <v>1700000</v>
+        <v>1900000</v>
       </c>
       <c r="E14" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D14,月別目標と営業利益!D14)</f>
-        <v>4700000</v>
+        <v>5300000</v>
       </c>
       <c r="F14" s="8">
         <f t="shared" si="0"/>
-        <v>53000</v>
+        <v>60000</v>
       </c>
       <c r="G14" s="8">
         <f t="shared" si="1"/>
-        <v>157000</v>
+        <v>177000</v>
       </c>
       <c r="H14" s="8">
         <f>入力!$B$14</f>
@@ -3349,23 +3343,23 @@
       </c>
       <c r="C15" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F15,月別目標と営業利益!F15)</f>
-        <v>1600000</v>
+        <v>1800000</v>
       </c>
       <c r="D15" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G15,月別目標と営業利益!G15)</f>
-        <v>1700000</v>
+        <v>1900000</v>
       </c>
       <c r="E15" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D15,月別目標と営業利益!D15)</f>
-        <v>4700000</v>
+        <v>5300000</v>
       </c>
       <c r="F15" s="8">
         <f t="shared" si="0"/>
-        <v>52000</v>
+        <v>58000</v>
       </c>
       <c r="G15" s="8">
         <f t="shared" si="1"/>
-        <v>152000</v>
+        <v>171000</v>
       </c>
       <c r="H15" s="8">
         <f>入力!$B$14</f>
@@ -3421,23 +3415,23 @@
       </c>
       <c r="C17" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F17,月別目標と営業利益!F17)</f>
-        <v>1600000</v>
+        <v>1800000</v>
       </c>
       <c r="D17" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G17,月別目標と営業利益!G17)</f>
-        <v>1700000</v>
+        <v>1900000</v>
       </c>
       <c r="E17" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D17,月別目標と営業利益!D17)</f>
-        <v>4700000</v>
+        <v>5300000</v>
       </c>
       <c r="F17" s="8">
         <f t="shared" si="0"/>
-        <v>52000</v>
+        <v>58000</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="1"/>
-        <v>152000</v>
+        <v>171000</v>
       </c>
       <c r="H17" s="8">
         <f>入力!$B$14</f>
@@ -3458,15 +3452,15 @@
       </c>
       <c r="C18" s="10">
         <f>SUM(C6:C17)</f>
-        <v>21500000</v>
+        <v>23400000</v>
       </c>
       <c r="D18" s="10">
         <f>SUM(D6:D17)</f>
-        <v>22650000</v>
+        <v>24650000</v>
       </c>
       <c r="E18" s="10">
         <f>SUM(E6:E17)</f>
-        <v>63000000</v>
+        <v>68600000</v>
       </c>
       <c r="H18" s="10">
         <f>SUM(H6:H17)</f>
@@ -3606,152 +3600,152 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="31.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" s="12">
-        <v>21500000</v>
+        <v>23400000</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>43</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B6" s="13">
         <f>B5/B19</f>
-        <v>0.34126984126984128</v>
+        <v>0.34110787172011664</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B7" s="12">
         <v>800000</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B8" s="14">
         <v>209792</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B9" s="13">
         <v>6.9199999999999998E-2</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B10" s="14">
         <v>3493268</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B11" s="14">
         <v>943852</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B12" s="14">
         <v>158000</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B13" s="14">
         <v>300000</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B14" s="14">
         <f>'報奨金（例B）'!D8</f>
         <v>30000</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B15" s="14">
         <f>'報奨金（例B）'!E8</f>
         <v>50000</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B16" s="15">
         <v>1.05</v>
@@ -3760,51 +3754,51 @@
     </row>
     <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B19" s="12">
-        <v>63000000</v>
+        <v>68600000</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>67</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B20" s="8">
         <f>B7*12+B8*12+B10+B11</f>
         <v>16554624</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B21" s="16">
         <f>B6-B9</f>
-        <v>0.27206984126984129</v>
+        <v>0.27190787172011666</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B22" s="8">
         <f>B20/B21</f>
-        <v>60846964.598259076</v>
+        <v>60883209.79923743</v>
       </c>
       <c r="C22" s="2"/>
     </row>
@@ -3826,26 +3820,26 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="31.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B4" s="16">
         <v>1</v>
@@ -3858,37 +3852,37 @@
     </row>
     <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B5" s="8">
         <f>入力!$B$19*B4</f>
-        <v>63000000</v>
+        <v>68600000</v>
       </c>
       <c r="C5" s="8">
         <f>入力!$B$19*C4</f>
-        <v>66150000</v>
+        <v>72030000</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B6" s="8">
         <f>入力!$B$5*B4</f>
-        <v>21500000</v>
+        <v>23400000</v>
       </c>
       <c r="C6" s="8">
         <f>入力!$B$5*C4</f>
-        <v>22575000</v>
+        <v>24570000</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B7" s="8">
         <f>入力!$B$7*12</f>
@@ -3899,12 +3893,12 @@
         <v>9600000</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B8" s="8">
         <f>入力!$B$14*12</f>
@@ -3915,28 +3909,28 @@
         <v>600000</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B9" s="8">
         <f>入力!$B$8*12+B5*入力!$B$9</f>
-        <v>6877104</v>
+        <v>7264624</v>
       </c>
       <c r="C9" s="8">
         <f>入力!$B$8*12+C5*入力!$B$9</f>
-        <v>7095084</v>
+        <v>7501980</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B10" s="8">
         <f>入力!$B$10</f>
@@ -3950,7 +3944,7 @@
     </row>
     <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B11" s="8">
         <f>入力!$B$11</f>
@@ -3964,35 +3958,35 @@
     </row>
     <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B12" s="8">
         <f>SUM(B7:B11)</f>
-        <v>21274224</v>
+        <v>21661744</v>
       </c>
       <c r="C12" s="8">
         <f>SUM(C7:C11)</f>
-        <v>21732204</v>
+        <v>22139100</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B13" s="7">
         <f>B6-B12</f>
-        <v>225776</v>
+        <v>1738256</v>
       </c>
       <c r="C13" s="7">
         <f>C6-C12</f>
-        <v>842796</v>
+        <v>2430900</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B14" s="8">
         <f>入力!$B$13</f>
@@ -4006,32 +4000,32 @@
     </row>
     <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B15" s="7">
         <f>B13-B14</f>
-        <v>-74224</v>
+        <v>1438256</v>
       </c>
       <c r="C15" s="7">
         <f>C13-C14</f>
-        <v>542796</v>
+        <v>2130900</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B16" s="8">
         <f>B13+B11-入力!$B$12*12</f>
-        <v>-726372</v>
+        <v>786108</v>
       </c>
       <c r="C16" s="8">
         <f>C13+C11-入力!$B$12*12</f>
-        <v>-109352</v>
+        <v>1478752</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -4053,27 +4047,27 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>80</v>
-      </c>
       <c r="D3" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.3">
@@ -4082,11 +4076,11 @@
       </c>
       <c r="B4" s="8">
         <f>入力!$B$19*A4</f>
-        <v>56700000</v>
+        <v>61740000</v>
       </c>
       <c r="C4" s="8">
         <f>入力!$B$5*A4</f>
-        <v>19350000</v>
+        <v>21060000</v>
       </c>
       <c r="D4" s="8">
         <f>IF(A4&gt;=入力!$B$16,入力!$B$15,IF(A4&gt;=1,入力!$B$14,0))*12</f>
@@ -4094,11 +4088,11 @@
       </c>
       <c r="E4" s="10">
         <f>C4-B4*入力!$B$9-入力!$B$20-D4</f>
-        <v>-1128264</v>
+        <v>232968</v>
       </c>
       <c r="F4" s="8">
         <f>E4-入力!$B$13</f>
-        <v>-1428264</v>
+        <v>-67032</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.3">
@@ -4107,11 +4101,11 @@
       </c>
       <c r="B5" s="8">
         <f>入力!$B$19*A5</f>
-        <v>59850000</v>
+        <v>65170000</v>
       </c>
       <c r="C5" s="8">
         <f>入力!$B$5*A5</f>
-        <v>20425000</v>
+        <v>22230000</v>
       </c>
       <c r="D5" s="8">
         <f>IF(A5&gt;=入力!$B$16,入力!$B$15,IF(A5&gt;=1,入力!$B$14,0))*12</f>
@@ -4119,11 +4113,11 @@
       </c>
       <c r="E5" s="10">
         <f>C5-B5*入力!$B$9-入力!$B$20-D5</f>
-        <v>-271244</v>
+        <v>1165612</v>
       </c>
       <c r="F5" s="8">
         <f>E5-入力!$B$13</f>
-        <v>-571244</v>
+        <v>865612</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.3">
@@ -4132,11 +4126,11 @@
       </c>
       <c r="B6" s="8">
         <f>入力!$B$19*A6</f>
-        <v>63000000</v>
+        <v>68600000</v>
       </c>
       <c r="C6" s="8">
         <f>入力!$B$5*A6</f>
-        <v>21500000</v>
+        <v>23400000</v>
       </c>
       <c r="D6" s="8">
         <f>IF(A6&gt;=入力!$B$16,入力!$B$15,IF(A6&gt;=1,入力!$B$14,0))*12</f>
@@ -4144,11 +4138,11 @@
       </c>
       <c r="E6" s="10">
         <f>C6-B6*入力!$B$9-入力!$B$20-D6</f>
-        <v>225776</v>
+        <v>1738256</v>
       </c>
       <c r="F6" s="8">
         <f>E6-入力!$B$13</f>
-        <v>-74224</v>
+        <v>1438256</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.3">
@@ -4157,11 +4151,11 @@
       </c>
       <c r="B7" s="8">
         <f>入力!$B$19*A7</f>
-        <v>64890000</v>
+        <v>70658000</v>
       </c>
       <c r="C7" s="8">
         <f>入力!$B$5*A7</f>
-        <v>22145000</v>
+        <v>24102000</v>
       </c>
       <c r="D7" s="8">
         <f>IF(A7&gt;=入力!$B$16,入力!$B$15,IF(A7&gt;=1,入力!$B$14,0))*12</f>
@@ -4169,11 +4163,11 @@
       </c>
       <c r="E7" s="10">
         <f>C7-B7*入力!$B$9-入力!$B$20-D7</f>
-        <v>739988</v>
+        <v>2297842.3999999985</v>
       </c>
       <c r="F7" s="8">
         <f>E7-入力!$B$13</f>
-        <v>439988</v>
+        <v>1997842.3999999985</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.3">
@@ -4182,11 +4176,11 @@
       </c>
       <c r="B8" s="8">
         <f>入力!$B$19*A8</f>
-        <v>66150000</v>
+        <v>72030000</v>
       </c>
       <c r="C8" s="8">
         <f>入力!$B$5*A8</f>
-        <v>22575000</v>
+        <v>24570000</v>
       </c>
       <c r="D8" s="8">
         <f>IF(A8&gt;=入力!$B$16,入力!$B$15,IF(A8&gt;=1,入力!$B$14,0))*12</f>
@@ -4194,11 +4188,11 @@
       </c>
       <c r="E8" s="10">
         <f>C8-B8*入力!$B$9-入力!$B$20-D8</f>
-        <v>842796</v>
+        <v>2430900</v>
       </c>
       <c r="F8" s="8">
         <f>E8-入力!$B$13</f>
-        <v>542796</v>
+        <v>2130900</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.3">
@@ -4207,11 +4201,11 @@
       </c>
       <c r="B9" s="8">
         <f>入力!$B$19*A9</f>
-        <v>69300000</v>
+        <v>75460000</v>
       </c>
       <c r="C9" s="8">
         <f>入力!$B$5*A9</f>
-        <v>23650000.000000004</v>
+        <v>25740000.000000004</v>
       </c>
       <c r="D9" s="8">
         <f>IF(A9&gt;=入力!$B$16,入力!$B$15,IF(A9&gt;=1,入力!$B$14,0))*12</f>
@@ -4219,20 +4213,20 @@
       </c>
       <c r="E9" s="10">
         <f>C9-B9*入力!$B$9-入力!$B$20-D9</f>
-        <v>1699816.0000000037</v>
+        <v>3363544.0000000037</v>
       </c>
       <c r="F9" s="8">
         <f>E9-入力!$B$13</f>
-        <v>1399816.0000000037</v>
+        <v>3063544.0000000037</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E11" s="8">
         <f>入力!B19*0.01*入力!B21</f>
-        <v>171404.00000000003</v>
+        <v>186528.80000000002</v>
       </c>
     </row>
   </sheetData>
@@ -4255,24 +4249,24 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.3">
@@ -4281,7 +4275,7 @@
       </c>
       <c r="B4" s="8">
         <f>入力!$B$19*A4</f>
-        <v>19530000</v>
+        <v>21266000</v>
       </c>
       <c r="C4" s="8">
         <f>IF(B4&gt;=入力!$B$5*入力!$B$16-1,入力!$B$15,IF(B4&gt;=入力!$B$5-1,入力!$B$14,0))*12</f>
@@ -4289,11 +4283,11 @@
       </c>
       <c r="D4" s="10">
         <f>B4-入力!$B$19*入力!$B$9-入力!$B$20-C4</f>
-        <v>-1384224</v>
+        <v>-35744</v>
       </c>
       <c r="E4" s="8">
         <f>D4-入力!$B$13</f>
-        <v>-1684224</v>
+        <v>-335744</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.3">
@@ -4302,7 +4296,7 @@
       </c>
       <c r="B5" s="8">
         <f>入力!$B$19*A5</f>
-        <v>20160000</v>
+        <v>21952000</v>
       </c>
       <c r="C5" s="8">
         <f>IF(B5&gt;=入力!$B$5*入力!$B$16-1,入力!$B$15,IF(B5&gt;=入力!$B$5-1,入力!$B$14,0))*12</f>
@@ -4310,11 +4304,11 @@
       </c>
       <c r="D5" s="10">
         <f>B5-入力!$B$19*入力!$B$9-入力!$B$20-C5</f>
-        <v>-754224</v>
+        <v>650256</v>
       </c>
       <c r="E5" s="8">
         <f>D5-入力!$B$13</f>
-        <v>-1054224</v>
+        <v>350256</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.3">
@@ -4323,7 +4317,7 @@
       </c>
       <c r="B6" s="8">
         <f>入力!$B$19*A6</f>
-        <v>20790000</v>
+        <v>22638000</v>
       </c>
       <c r="C6" s="8">
         <f>IF(B6&gt;=入力!$B$5*入力!$B$16-1,入力!$B$15,IF(B6&gt;=入力!$B$5-1,入力!$B$14,0))*12</f>
@@ -4331,21 +4325,21 @@
       </c>
       <c r="D6" s="10">
         <f>B6-入力!$B$19*入力!$B$9-入力!$B$20-C6</f>
-        <v>-124224</v>
+        <v>1336256</v>
       </c>
       <c r="E6" s="8">
         <f>D6-入力!$B$13</f>
-        <v>-424224</v>
+        <v>1036256</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="15">
         <f>入力!B6</f>
-        <v>0.34126984126984128</v>
+        <v>0.34110787172011664</v>
       </c>
       <c r="B7" s="8">
         <f>入力!$B$19*A7</f>
-        <v>21500000</v>
+        <v>23400000</v>
       </c>
       <c r="C7" s="8">
         <f>IF(B7&gt;=入力!$B$5*入力!$B$16-1,入力!$B$15,IF(B7&gt;=入力!$B$5-1,入力!$B$14,0))*12</f>
@@ -4353,11 +4347,11 @@
       </c>
       <c r="D7" s="10">
         <f>B7-入力!$B$19*入力!$B$9-入力!$B$20-C7</f>
-        <v>225776</v>
+        <v>1738256</v>
       </c>
       <c r="E7" s="8">
         <f>D7-入力!$B$13</f>
-        <v>-74224</v>
+        <v>1438256</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.3">
@@ -4366,7 +4360,7 @@
       </c>
       <c r="B8" s="8">
         <f>入力!$B$19*A8</f>
-        <v>22050000</v>
+        <v>24010000</v>
       </c>
       <c r="C8" s="8">
         <f>IF(B8&gt;=入力!$B$5*入力!$B$16-1,入力!$B$15,IF(B8&gt;=入力!$B$5-1,入力!$B$14,0))*12</f>
@@ -4374,11 +4368,11 @@
       </c>
       <c r="D8" s="10">
         <f>B8-入力!$B$19*入力!$B$9-入力!$B$20-C8</f>
-        <v>775776</v>
+        <v>2348256</v>
       </c>
       <c r="E8" s="8">
         <f>D8-入力!$B$13</f>
-        <v>475776</v>
+        <v>2048256</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.3">
@@ -4387,7 +4381,7 @@
       </c>
       <c r="B9" s="8">
         <f>入力!$B$19*A9</f>
-        <v>22680000</v>
+        <v>24696000</v>
       </c>
       <c r="C9" s="8">
         <f>IF(B9&gt;=入力!$B$5*入力!$B$16-1,入力!$B$15,IF(B9&gt;=入力!$B$5-1,入力!$B$14,0))*12</f>
@@ -4395,20 +4389,20 @@
       </c>
       <c r="D9" s="10">
         <f>B9-入力!$B$19*入力!$B$9-入力!$B$20-C9</f>
-        <v>1165776</v>
+        <v>2794256</v>
       </c>
       <c r="E9" s="8">
         <f>D9-入力!$B$13</f>
-        <v>865776</v>
+        <v>2494256</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D11" s="8">
         <f>入力!B19*0.01</f>
-        <v>630000</v>
+        <v>686000</v>
       </c>
     </row>
   </sheetData>
@@ -4430,17 +4424,17 @@
   <sheetData>
     <row r="1" spans="1:12" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="31.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -4448,37 +4442,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="K5" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>112</v>
-      </c>
       <c r="L5" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" x14ac:dyDescent="0.3">
@@ -4497,7 +4491,7 @@
       </c>
       <c r="E6" s="8">
         <f>ROUND(入力!$B$5*C6,-3)</f>
-        <v>1218000</v>
+        <v>1326000</v>
       </c>
       <c r="F6" s="12">
         <v>1200000</v>
@@ -4540,7 +4534,7 @@
       </c>
       <c r="E7" s="8">
         <f>ROUND(入力!$B$5*C7,-3)</f>
-        <v>1458000</v>
+        <v>1587000</v>
       </c>
       <c r="F7" s="12">
         <v>1450000</v>
@@ -4583,7 +4577,7 @@
       </c>
       <c r="E8" s="8">
         <f>ROUND(入力!$B$5*C8,-3)</f>
-        <v>1977000</v>
+        <v>2152000</v>
       </c>
       <c r="F8" s="12">
         <v>2000000</v>
@@ -4626,7 +4620,7 @@
       </c>
       <c r="E9" s="8">
         <f>ROUND(入力!$B$5*C9,-3)</f>
-        <v>2063000</v>
+        <v>2246000</v>
       </c>
       <c r="F9" s="12">
         <v>2050000</v>
@@ -4669,7 +4663,7 @@
       </c>
       <c r="E10" s="8">
         <f>ROUND(入力!$B$5*C10,-3)</f>
-        <v>2733000</v>
+        <v>2974000</v>
       </c>
       <c r="F10" s="12">
         <v>2750000</v>
@@ -4712,7 +4706,7 @@
       </c>
       <c r="E11" s="8">
         <f>ROUND(入力!$B$5*C11,-3)</f>
-        <v>1944000</v>
+        <v>2115000</v>
       </c>
       <c r="F11" s="12">
         <v>1950000</v>
@@ -4755,7 +4749,7 @@
       </c>
       <c r="E12" s="8">
         <f>ROUND(入力!$B$5*C12,-3)</f>
-        <v>1120000</v>
+        <v>1219000</v>
       </c>
       <c r="F12" s="12">
         <v>1100000</v>
@@ -4798,7 +4792,7 @@
       </c>
       <c r="E13" s="8">
         <f>ROUND(入力!$B$5*C13,-3)</f>
-        <v>1771000</v>
+        <v>1927000</v>
       </c>
       <c r="F13" s="12">
         <v>1750000</v>
@@ -4841,7 +4835,7 @@
       </c>
       <c r="E14" s="8">
         <f>ROUND(入力!$B$5*C14,-3)</f>
-        <v>1435000</v>
+        <v>1562000</v>
       </c>
       <c r="F14" s="12">
         <v>1450000</v>
@@ -4884,7 +4878,7 @@
       </c>
       <c r="E15" s="8">
         <f>ROUND(入力!$B$5*C15,-3)</f>
-        <v>1923000</v>
+        <v>2093000</v>
       </c>
       <c r="F15" s="12">
         <v>1950000</v>
@@ -4927,7 +4921,7 @@
       </c>
       <c r="E16" s="8">
         <f>ROUND(入力!$B$5*C16,-3)</f>
-        <v>1959000</v>
+        <v>2132000</v>
       </c>
       <c r="F16" s="12">
         <v>1950000</v>
@@ -4970,7 +4964,7 @@
       </c>
       <c r="E17" s="8">
         <f>ROUND(入力!$B$5*C17,-3)</f>
-        <v>1900000</v>
+        <v>2067000</v>
       </c>
       <c r="F17" s="12">
         <v>1900000</v>
@@ -5011,7 +5005,7 @@
       </c>
       <c r="E18" s="10">
         <f>SUM(E6:E17)</f>
-        <v>21501000</v>
+        <v>23400000</v>
       </c>
       <c r="F18" s="10">
         <f>SUM(F6:F17)</f>
@@ -5040,16 +5034,16 @@
       </c>
       <c r="D19" s="8">
         <f>D18-入力!B19</f>
-        <v>0</v>
+        <v>-5600000</v>
       </c>
       <c r="F19" s="8">
         <f>F18-入力!B5</f>
-        <v>0</v>
+        <v>-1900000</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -5072,17 +5066,17 @@
   <sheetData>
     <row r="1" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>103</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -5090,40 +5084,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="J5" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="K5" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="L5" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>112</v>
-      </c>
       <c r="M5" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" x14ac:dyDescent="0.3">
@@ -5138,30 +5132,30 @@
         <v>5.8333333333333334E-2</v>
       </c>
       <c r="D6" s="12">
-        <v>3700000</v>
+        <v>5300000</v>
       </c>
       <c r="E6" s="8">
         <f>ROUND(入力!$B$5*C6,-3)</f>
-        <v>1254000</v>
+        <v>1365000</v>
       </c>
       <c r="F6" s="12">
-        <v>1250000</v>
+        <v>1800000</v>
       </c>
       <c r="G6" s="8">
         <f>ROUND(F6*入力!$B$16/50000,0)*50000</f>
-        <v>1300000</v>
+        <v>1900000</v>
       </c>
       <c r="H6" s="8">
         <f>F6-D6*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>-415592</v>
+        <v>23688</v>
       </c>
       <c r="I6" s="8">
         <f>SUM($H$6:H6)</f>
-        <v>-415592</v>
+        <v>23688</v>
       </c>
       <c r="J6" s="8">
         <f>F6-月別目標と営業利益!F6</f>
-        <v>50000</v>
+        <v>600000</v>
       </c>
       <c r="K6" s="12"/>
       <c r="L6" s="11" t="str">
@@ -5185,30 +5179,30 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D7" s="12">
-        <v>4700000</v>
+        <v>5300000</v>
       </c>
       <c r="E7" s="8">
         <f>ROUND(入力!$B$5*C7,-3)</f>
-        <v>1613000</v>
+        <v>1755000</v>
       </c>
       <c r="F7" s="12">
-        <v>1600000</v>
+        <v>1800000</v>
       </c>
       <c r="G7" s="8">
         <f>ROUND(F7*入力!$B$16/50000,0)*50000</f>
-        <v>1700000</v>
+        <v>1900000</v>
       </c>
       <c r="H7" s="8">
         <f>F7-D7*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>-134792</v>
+        <v>23688</v>
       </c>
       <c r="I7" s="8">
         <f>SUM($H$6:H7)</f>
-        <v>-550384</v>
+        <v>47376</v>
       </c>
       <c r="J7" s="8">
         <f>F7-月別目標と営業利益!F7</f>
-        <v>150000</v>
+        <v>350000</v>
       </c>
       <c r="K7" s="12"/>
       <c r="L7" s="11" t="str">
@@ -5236,7 +5230,7 @@
       </c>
       <c r="E8" s="8">
         <f>ROUND(入力!$B$5*C8,-3)</f>
-        <v>1971000</v>
+        <v>2145000</v>
       </c>
       <c r="F8" s="12">
         <v>2000000</v>
@@ -5251,7 +5245,7 @@
       </c>
       <c r="I8" s="8">
         <f>SUM($H$6:H8)</f>
-        <v>-361296</v>
+        <v>236464</v>
       </c>
       <c r="J8" s="8">
         <f>F8-月別目標と営業利益!F8</f>
@@ -5283,7 +5277,7 @@
       </c>
       <c r="E9" s="8">
         <f>ROUND(入力!$B$5*C9,-3)</f>
-        <v>1971000</v>
+        <v>2145000</v>
       </c>
       <c r="F9" s="12">
         <v>2000000</v>
@@ -5298,7 +5292,7 @@
       </c>
       <c r="I9" s="8">
         <f>SUM($H$6:H9)</f>
-        <v>-172208</v>
+        <v>425552</v>
       </c>
       <c r="J9" s="8">
         <f>F9-月別目標と営業利益!F9</f>
@@ -5330,7 +5324,7 @@
       </c>
       <c r="E10" s="8">
         <f>ROUND(入力!$B$5*C10,-3)</f>
-        <v>2508000</v>
+        <v>2730000</v>
       </c>
       <c r="F10" s="12">
         <v>2500000</v>
@@ -5345,7 +5339,7 @@
       </c>
       <c r="I10" s="8">
         <f>SUM($H$6:H10)</f>
-        <v>413080</v>
+        <v>1010840</v>
       </c>
       <c r="J10" s="8">
         <f>F10-月別目標と営業利益!F10</f>
@@ -5377,7 +5371,7 @@
       </c>
       <c r="E11" s="8">
         <f>ROUND(入力!$B$5*C11,-3)</f>
-        <v>2150000</v>
+        <v>2340000</v>
       </c>
       <c r="F11" s="12">
         <v>2100000</v>
@@ -5392,7 +5386,7 @@
       </c>
       <c r="I11" s="8">
         <f>SUM($H$6:H11)</f>
-        <v>667568</v>
+        <v>1265328</v>
       </c>
       <c r="J11" s="8">
         <f>F11-月別目標と営業利益!F11</f>
@@ -5420,30 +5414,30 @@
         <v>5.8333333333333334E-2</v>
       </c>
       <c r="D12" s="12">
-        <v>3700000</v>
+        <v>5300000</v>
       </c>
       <c r="E12" s="8">
         <f>ROUND(入力!$B$5*C12,-3)</f>
-        <v>1254000</v>
+        <v>1365000</v>
       </c>
       <c r="F12" s="12">
-        <v>1250000</v>
+        <v>1800000</v>
       </c>
       <c r="G12" s="8">
         <f>ROUND(F12*入力!$B$16/50000,0)*50000</f>
-        <v>1300000</v>
+        <v>1900000</v>
       </c>
       <c r="H12" s="8">
         <f>F12-D12*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>-415592</v>
+        <v>23688</v>
       </c>
       <c r="I12" s="8">
         <f>SUM($H$6:H12)</f>
-        <v>251976</v>
+        <v>1289016</v>
       </c>
       <c r="J12" s="8">
         <f>F12-月別目標と営業利益!F12</f>
-        <v>150000</v>
+        <v>700000</v>
       </c>
       <c r="K12" s="12"/>
       <c r="L12" s="11" t="str">
@@ -5471,7 +5465,7 @@
       </c>
       <c r="E13" s="8">
         <f>ROUND(入力!$B$5*C13,-3)</f>
-        <v>1971000</v>
+        <v>2145000</v>
       </c>
       <c r="F13" s="12">
         <v>2000000</v>
@@ -5486,7 +5480,7 @@
       </c>
       <c r="I13" s="8">
         <f>SUM($H$6:H13)</f>
-        <v>441064</v>
+        <v>1478104</v>
       </c>
       <c r="J13" s="8">
         <f>F13-月別目標と営業利益!F13</f>
@@ -5514,30 +5508,30 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D14" s="12">
-        <v>4700000</v>
+        <v>5300000</v>
       </c>
       <c r="E14" s="8">
         <f>ROUND(入力!$B$5*C14,-3)</f>
-        <v>1613000</v>
+        <v>1755000</v>
       </c>
       <c r="F14" s="12">
-        <v>1600000</v>
+        <v>1800000</v>
       </c>
       <c r="G14" s="8">
         <f>ROUND(F14*入力!$B$16/50000,0)*50000</f>
-        <v>1700000</v>
+        <v>1900000</v>
       </c>
       <c r="H14" s="8">
         <f>F14-D14*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>-134792</v>
+        <v>23688</v>
       </c>
       <c r="I14" s="8">
         <f>SUM($H$6:H14)</f>
-        <v>306272</v>
+        <v>1501792</v>
       </c>
       <c r="J14" s="8">
         <f>F14-月別目標と営業利益!F14</f>
-        <v>150000</v>
+        <v>350000</v>
       </c>
       <c r="K14" s="12"/>
       <c r="L14" s="11" t="str">
@@ -5561,30 +5555,30 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D15" s="12">
-        <v>4700000</v>
+        <v>5300000</v>
       </c>
       <c r="E15" s="8">
         <f>ROUND(入力!$B$5*C15,-3)</f>
-        <v>1613000</v>
+        <v>1755000</v>
       </c>
       <c r="F15" s="12">
-        <v>1600000</v>
+        <v>1800000</v>
       </c>
       <c r="G15" s="8">
         <f>ROUND(F15*入力!$B$16/50000,0)*50000</f>
-        <v>1700000</v>
+        <v>1900000</v>
       </c>
       <c r="H15" s="8">
         <f>F15-D15*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>-134792</v>
+        <v>23688</v>
       </c>
       <c r="I15" s="8">
         <f>SUM($H$6:H15)</f>
-        <v>171480</v>
+        <v>1525480</v>
       </c>
       <c r="J15" s="8">
         <f>F15-月別目標と営業利益!F15</f>
-        <v>-350000</v>
+        <v>-150000</v>
       </c>
       <c r="K15" s="12"/>
       <c r="L15" s="11" t="str">
@@ -5612,7 +5606,7 @@
       </c>
       <c r="E16" s="8">
         <f>ROUND(入力!$B$5*C16,-3)</f>
-        <v>1971000</v>
+        <v>2145000</v>
       </c>
       <c r="F16" s="12">
         <v>2000000</v>
@@ -5627,7 +5621,7 @@
       </c>
       <c r="I16" s="8">
         <f>SUM($H$6:H16)</f>
-        <v>360568</v>
+        <v>1714568</v>
       </c>
       <c r="J16" s="8">
         <f>F16-月別目標と営業利益!F16</f>
@@ -5655,30 +5649,30 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D17" s="12">
-        <v>4700000</v>
+        <v>5300000</v>
       </c>
       <c r="E17" s="8">
         <f>ROUND(入力!$B$5*C17,-3)</f>
-        <v>1613000</v>
+        <v>1755000</v>
       </c>
       <c r="F17" s="12">
-        <v>1600000</v>
+        <v>1800000</v>
       </c>
       <c r="G17" s="8">
         <f>ROUND(F17*入力!$B$16/50000,0)*50000</f>
-        <v>1700000</v>
+        <v>1900000</v>
       </c>
       <c r="H17" s="8">
         <f>F17-D17*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>-134792</v>
+        <v>23688</v>
       </c>
       <c r="I17" s="8">
         <f>SUM($H$6:H17)</f>
-        <v>225776</v>
+        <v>1738256</v>
       </c>
       <c r="J17" s="8">
         <f>F17-月別目標と営業利益!F17</f>
-        <v>-300000</v>
+        <v>-100000</v>
       </c>
       <c r="K17" s="12"/>
       <c r="L17" s="11" t="str">
@@ -5700,23 +5694,23 @@
       </c>
       <c r="D18" s="10">
         <f>SUM(D6:D17)</f>
-        <v>63000000</v>
+        <v>68600000</v>
       </c>
       <c r="E18" s="10">
         <f>SUM(E6:E17)</f>
-        <v>21502000</v>
+        <v>23400000</v>
       </c>
       <c r="F18" s="10">
         <f>SUM(F6:F17)</f>
-        <v>21500000</v>
+        <v>23400000</v>
       </c>
       <c r="G18" s="10">
         <f>SUM(G6:G17)</f>
-        <v>22650000</v>
+        <v>24650000</v>
       </c>
       <c r="H18" s="10">
         <f>SUM(H6:H17)</f>
-        <v>225776</v>
+        <v>1738256</v>
       </c>
       <c r="K18" s="10">
         <f>SUM(K6:K17)</f>
@@ -5742,7 +5736,7 @@
     </row>
     <row r="20" spans="1:13" ht="15" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -5764,12 +5758,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -5780,18 +5774,18 @@
         <v>29</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B5" s="4">
         <v>1</v>
@@ -5809,7 +5803,7 @@
     </row>
     <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B6" s="4">
         <v>1</v>
@@ -5827,7 +5821,7 @@
     </row>
     <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B7" s="4">
         <v>2</v>
@@ -5845,7 +5839,7 @@
     </row>
     <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B8" s="9">
         <f>SUM(B5:B7)</f>
@@ -5862,7 +5856,7 @@
     </row>
     <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D9" s="10">
         <f>D8*12</f>
@@ -5875,12 +5869,12 @@
     </row>
     <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" x14ac:dyDescent="0.3">

--- a/excel/Weekends_予算と報奨金案_粗利2150万円.xlsx
+++ b/excel/Weekends_予算と報奨金案_粗利2150万円.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yataka-02\AppData\Local\Temp\claude\C--Users-yataka-02-Desktop-Claude\76fa42a7-01fc-42d8-86c7-11cf90447c56\scratchpad\margin-calculator\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D69B8E-865B-4E64-8006-4D4705C3B0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C24036CC-0A49-4021-AB43-0189274730BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -523,27 +523,27 @@
     <t>赤字の月数</t>
   </si>
   <si>
-    <t>2026-10-06：毎月の営業利益がマイナスにならないよう、閑散月の粗利目標を180万円に引き上げ（旧2,150万円）</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>同上（旧6,300万円）。閑散月の売上目標を530万円に引き上げ</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>Weekends 2027年度 予算と報奨金案（売上6,860万円・粗利2,340万円）　入力値</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
     <t>月別の目標と営業利益　スマレジ版（全月で100%達成した場合）</t>
     <phoneticPr fontId="9"/>
   </si>
   <si>
-    <t>黄色の「売上目標」は10万円単位、「粗利目標100%」は5万円単位。2026-10-06に、毎月の営業利益がマイナスにならないよう8・9・2・4・5・7月を粗利180万円・売上530万円に引き上げた（年計 売上6,860万円・粗利2,340万円）。</t>
+    <t>2026-10-07：粗利2,150万円に戻し、月の目標をならした（閑散月の売上は前年の1.4倍以内）</t>
     <phoneticPr fontId="9"/>
   </si>
   <si>
-    <t>月別の目標と営業利益　構成比版（旧案：年2,150万円のまま。現在は使っていない）</t>
+    <t>検討案（税抜）</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>Weekends 2027年度 予算と報奨金案（売上6,300万円・粗利2,150万円）　入力値</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>黄色の「売上目標」は10万円単位、「粗利目標100%」は5万円単位。2026-10-07に、営業利益の赤字月を減らすよう月の目標をならした：前年の売上が少ない月（8・9・2・4月）は前年の1.4倍まで引き上げ、残りは前年比が同じになるよう配分（年計 売上6,300万円・粗利2,150万円）。</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>月別の目標と営業利益　構成比版（参考。現在の月別目標はスマレジ版シート）</t>
     <phoneticPr fontId="9"/>
   </si>
 </sst>
@@ -825,22 +825,22 @@
                 <c:formatCode>#,##0;[Red]\-#,##0;\-</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>232968</c:v>
+                  <c:v>-1128264</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1165612</c:v>
+                  <c:v>-271244</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1738256</c:v>
+                  <c:v>225776</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2297842.3999999985</c:v>
+                  <c:v>739988</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2430900</c:v>
+                  <c:v>842796</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3363544.0000000037</c:v>
+                  <c:v>1699816.0000000037</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1328,40 +1328,40 @@
                 <c:formatCode>#,##0;[Red]\-#,##0;\-</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
+                  <c:v>-250192</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-55552</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>66768</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>102928</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>621448</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>23688</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="6">
+                  <c:v>-329432</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>23688</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>189088</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>189088</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>585288</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>254488</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>23688</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>189088</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>23688</c:v>
+                  <c:v>-55552</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>23688</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>189088</c:v>
+                  <c:v>23688</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>23688</c:v>
+                  <c:v>30608</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1416,40 +1416,40 @@
                 <c:formatCode>#,##0;[Red]\-#,##0;\-</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>23688</c:v>
+                  <c:v>-250192</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>47376</c:v>
+                  <c:v>-305744</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>236464</c:v>
+                  <c:v>-238976</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>425552</c:v>
+                  <c:v>-136048</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1010840</c:v>
+                  <c:v>485400</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1265328</c:v>
+                  <c:v>509088</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1289016</c:v>
+                  <c:v>179656</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1478104</c:v>
+                  <c:v>203344</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1501792</c:v>
+                  <c:v>147792</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1525480</c:v>
+                  <c:v>171480</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1714568</c:v>
+                  <c:v>195168</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1738256</c:v>
+                  <c:v>225776</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2008,27 +2008,27 @@
       </c>
       <c r="B8" s="24">
         <f>入力!$B$19*B7</f>
-        <v>68600000</v>
+        <v>63000000</v>
       </c>
       <c r="C8" s="24">
         <f>入力!$B$19*C7</f>
-        <v>68600000</v>
+        <v>63000000</v>
       </c>
       <c r="D8" s="24">
         <f>入力!$B$19*D7</f>
-        <v>68600000</v>
+        <v>63000000</v>
       </c>
       <c r="E8" s="24">
         <f>入力!$B$19*E7</f>
-        <v>72030000</v>
+        <v>66150000</v>
       </c>
       <c r="F8" s="24">
         <f>入力!$B$19*F7</f>
-        <v>72030000</v>
+        <v>66150000</v>
       </c>
       <c r="G8" s="24">
         <f>入力!$B$19*G7</f>
-        <v>72030000</v>
+        <v>66150000</v>
       </c>
       <c r="H8" s="19" t="s">
         <v>134</v>
@@ -2040,27 +2040,27 @@
       </c>
       <c r="B9" s="24">
         <f>入力!$B$5*B7</f>
-        <v>23400000</v>
+        <v>21500000</v>
       </c>
       <c r="C9" s="24">
         <f>入力!$B$5*C7</f>
-        <v>23400000</v>
+        <v>21500000</v>
       </c>
       <c r="D9" s="24">
         <f>入力!$B$5*D7</f>
-        <v>23400000</v>
+        <v>21500000</v>
       </c>
       <c r="E9" s="24">
         <f>入力!$B$5*E7</f>
-        <v>24570000</v>
+        <v>22575000</v>
       </c>
       <c r="F9" s="24">
         <f>入力!$B$5*F7</f>
-        <v>24570000</v>
+        <v>22575000</v>
       </c>
       <c r="G9" s="24">
         <f>入力!$B$5*G7</f>
-        <v>24570000</v>
+        <v>22575000</v>
       </c>
       <c r="H9" s="19" t="s">
         <v>135</v>
@@ -2136,27 +2136,27 @@
       </c>
       <c r="B12" s="24">
         <f>入力!$B$8*12+B8*入力!$B$9</f>
-        <v>7264624</v>
+        <v>6877104</v>
       </c>
       <c r="C12" s="24">
         <f>入力!$B$8*12+C8*入力!$B$9</f>
-        <v>7264624</v>
+        <v>6877104</v>
       </c>
       <c r="D12" s="24">
         <f>入力!$B$8*12+D8*入力!$B$9</f>
-        <v>7264624</v>
+        <v>6877104</v>
       </c>
       <c r="E12" s="24">
         <f>入力!$B$8*12+E8*入力!$B$9</f>
-        <v>7501980</v>
+        <v>7095084</v>
       </c>
       <c r="F12" s="24">
         <f>入力!$B$8*12+F8*入力!$B$9</f>
-        <v>7501980</v>
+        <v>7095084</v>
       </c>
       <c r="G12" s="24">
         <f>入力!$B$8*12+G8*入力!$B$9</f>
-        <v>7501980</v>
+        <v>7095084</v>
       </c>
       <c r="H12" s="19" t="s">
         <v>137</v>
@@ -2197,27 +2197,27 @@
       </c>
       <c r="B14" s="27">
         <f t="shared" ref="B14:G14" si="0">SUM(B10:B13)</f>
-        <v>20717892</v>
+        <v>20330372</v>
       </c>
       <c r="C14" s="27">
         <f t="shared" si="0"/>
-        <v>20717892</v>
+        <v>20330372</v>
       </c>
       <c r="D14" s="27">
         <f t="shared" si="0"/>
-        <v>20717892</v>
+        <v>20330372</v>
       </c>
       <c r="E14" s="27">
         <f t="shared" si="0"/>
-        <v>21195248</v>
+        <v>20788352</v>
       </c>
       <c r="F14" s="27">
         <f t="shared" si="0"/>
-        <v>21195248</v>
+        <v>20788352</v>
       </c>
       <c r="G14" s="27">
         <f t="shared" si="0"/>
-        <v>21195248</v>
+        <v>20788352</v>
       </c>
       <c r="H14" s="26" t="s">
         <v>138</v>
@@ -2229,27 +2229,27 @@
       </c>
       <c r="B15" s="27">
         <f t="shared" ref="B15:G15" si="1">B9-B14</f>
-        <v>2682108</v>
+        <v>1169628</v>
       </c>
       <c r="C15" s="27">
         <f t="shared" si="1"/>
-        <v>2682108</v>
+        <v>1169628</v>
       </c>
       <c r="D15" s="27">
         <f t="shared" si="1"/>
-        <v>2682108</v>
+        <v>1169628</v>
       </c>
       <c r="E15" s="27">
         <f t="shared" si="1"/>
-        <v>3374752</v>
+        <v>1786648</v>
       </c>
       <c r="F15" s="27">
         <f t="shared" si="1"/>
-        <v>3374752</v>
+        <v>1786648</v>
       </c>
       <c r="G15" s="27">
         <f t="shared" si="1"/>
-        <v>3374752</v>
+        <v>1786648</v>
       </c>
       <c r="H15" s="26" t="s">
         <v>139</v>
@@ -2317,27 +2317,27 @@
       </c>
       <c r="B18" s="27">
         <f t="shared" ref="B18:G18" si="2">B15-B16-B17</f>
-        <v>2682108</v>
+        <v>1169628</v>
       </c>
       <c r="C18" s="27">
         <f t="shared" si="2"/>
-        <v>1738256</v>
+        <v>225776</v>
       </c>
       <c r="D18" s="27">
         <f t="shared" si="2"/>
-        <v>786108</v>
+        <v>-726372</v>
       </c>
       <c r="E18" s="27">
         <f t="shared" si="2"/>
-        <v>3374752</v>
+        <v>1786648</v>
       </c>
       <c r="F18" s="27">
         <f t="shared" si="2"/>
-        <v>2430900</v>
+        <v>842796</v>
       </c>
       <c r="G18" s="27">
         <f t="shared" si="2"/>
-        <v>1478752</v>
+        <v>-109352</v>
       </c>
       <c r="H18" s="26" t="s">
         <v>142</v>
@@ -2378,27 +2378,27 @@
       </c>
       <c r="B20" s="27">
         <f t="shared" ref="B20:G20" si="3">B18-B19</f>
-        <v>2382108</v>
+        <v>869628</v>
       </c>
       <c r="C20" s="27">
         <f t="shared" si="3"/>
-        <v>1438256</v>
+        <v>-74224</v>
       </c>
       <c r="D20" s="27">
         <f t="shared" si="3"/>
-        <v>486108</v>
+        <v>-1026372</v>
       </c>
       <c r="E20" s="27">
         <f t="shared" si="3"/>
-        <v>3074752</v>
+        <v>1486648</v>
       </c>
       <c r="F20" s="27">
         <f t="shared" si="3"/>
-        <v>2130900</v>
+        <v>542796</v>
       </c>
       <c r="G20" s="27">
         <f t="shared" si="3"/>
-        <v>1178752</v>
+        <v>-409352</v>
       </c>
       <c r="H20" s="26"/>
     </row>
@@ -2408,27 +2408,27 @@
       </c>
       <c r="B21" s="24">
         <f>(入力!$B$7*12+入力!$B$8*12+入力!$B$10+B16+B17)/入力!$B$21</f>
-        <v>57411989.95543851</v>
+        <v>57377811.25294625</v>
       </c>
       <c r="C21" s="24">
         <f>(入力!$B$7*12+入力!$B$8*12+入力!$B$10+C16+C17)/入力!$B$21</f>
-        <v>60883209.79923743</v>
+        <v>60846964.598259076</v>
       </c>
       <c r="D21" s="24">
         <f>(入力!$B$7*12+入力!$B$8*12+入力!$B$10+D16+D17)/入力!$B$21</f>
-        <v>64384939.977097362</v>
+        <v>64346610.114116348</v>
       </c>
       <c r="E21" s="24">
         <f>(入力!$B$7*12+入力!$B$8*12+入力!$B$10+E16+E17)/入力!$B$21</f>
-        <v>57411989.95543851</v>
+        <v>57377811.25294625</v>
       </c>
       <c r="F21" s="24">
         <f>(入力!$B$7*12+入力!$B$8*12+入力!$B$10+F16+F17)/入力!$B$21</f>
-        <v>60883209.79923743</v>
+        <v>60846964.598259076</v>
       </c>
       <c r="G21" s="24">
         <f>(入力!$B$7*12+入力!$B$8*12+入力!$B$10+G16+G17)/入力!$B$21</f>
-        <v>64384939.977097362</v>
+        <v>64346610.114116348</v>
       </c>
       <c r="H21" s="19" t="s">
         <v>143</v>
@@ -2440,27 +2440,27 @@
       </c>
       <c r="B22" s="25">
         <f>B21/入力!$B$19</f>
-        <v>0.8369094745690745</v>
+        <v>0.91075890877692456</v>
       </c>
       <c r="C22" s="25">
         <f>C21/入力!$B$19</f>
-        <v>0.88751034692765929</v>
+        <v>0.96582483489300119</v>
       </c>
       <c r="D22" s="25">
         <f>D21/入力!$B$19</f>
-        <v>0.93855597634252719</v>
+        <v>1.0213747637161326</v>
       </c>
       <c r="E22" s="25">
         <f>E21/入力!$B$19</f>
-        <v>0.8369094745690745</v>
+        <v>0.91075890877692456</v>
       </c>
       <c r="F22" s="25">
         <f>F21/入力!$B$19</f>
-        <v>0.88751034692765929</v>
+        <v>0.96582483489300119</v>
       </c>
       <c r="G22" s="25">
         <f>G21/入力!$B$19</f>
-        <v>0.93855597634252719</v>
+        <v>1.0213747637161326</v>
       </c>
       <c r="H22" s="19" t="s">
         <v>144</v>
@@ -2495,15 +2495,15 @@
       </c>
       <c r="B27" s="24">
         <f>C27+入力!$B$11</f>
-        <v>1176820</v>
+        <v>-184412</v>
       </c>
       <c r="C27" s="24">
         <f>達成度別!E4</f>
-        <v>232968</v>
+        <v>-1128264</v>
       </c>
       <c r="D27" s="24">
         <f>C27+入力!$B$11-入力!$B$12*12</f>
-        <v>-719180</v>
+        <v>-2080412</v>
       </c>
       <c r="E27" s="24">
         <f t="shared" ref="E27:E32" si="4">B27-C27</f>
@@ -2517,15 +2517,15 @@
       </c>
       <c r="B28" s="24">
         <f>C28+入力!$B$11</f>
-        <v>2109464</v>
+        <v>672608</v>
       </c>
       <c r="C28" s="24">
         <f>達成度別!E5</f>
-        <v>1165612</v>
+        <v>-271244</v>
       </c>
       <c r="D28" s="24">
         <f>C28+入力!$B$11-入力!$B$12*12</f>
-        <v>213464</v>
+        <v>-1223392</v>
       </c>
       <c r="E28" s="24">
         <f t="shared" si="4"/>
@@ -2539,15 +2539,15 @@
       </c>
       <c r="B29" s="27">
         <f>C29+入力!$B$11</f>
-        <v>2682108</v>
+        <v>1169628</v>
       </c>
       <c r="C29" s="27">
         <f>達成度別!E6</f>
-        <v>1738256</v>
+        <v>225776</v>
       </c>
       <c r="D29" s="27">
         <f>C29+入力!$B$11-入力!$B$12*12</f>
-        <v>786108</v>
+        <v>-726372</v>
       </c>
       <c r="E29" s="27">
         <f t="shared" si="4"/>
@@ -2561,15 +2561,15 @@
       </c>
       <c r="B30" s="24">
         <f>C30+入力!$B$11</f>
-        <v>3241694.3999999985</v>
+        <v>1683840</v>
       </c>
       <c r="C30" s="24">
         <f>達成度別!E7</f>
-        <v>2297842.3999999985</v>
+        <v>739988</v>
       </c>
       <c r="D30" s="24">
         <f>C30+入力!$B$11-入力!$B$12*12</f>
-        <v>1345694.3999999985</v>
+        <v>-212160</v>
       </c>
       <c r="E30" s="24">
         <f t="shared" si="4"/>
@@ -2583,15 +2583,15 @@
       </c>
       <c r="B31" s="24">
         <f>C31+入力!$B$11</f>
-        <v>3374752</v>
+        <v>1786648</v>
       </c>
       <c r="C31" s="24">
         <f>達成度別!E8</f>
-        <v>2430900</v>
+        <v>842796</v>
       </c>
       <c r="D31" s="24">
         <f>C31+入力!$B$11-入力!$B$12*12</f>
-        <v>1478752</v>
+        <v>-109352</v>
       </c>
       <c r="E31" s="24">
         <f t="shared" si="4"/>
@@ -2605,15 +2605,15 @@
       </c>
       <c r="B32" s="24">
         <f>C32+入力!$B$11</f>
-        <v>4307396.0000000037</v>
+        <v>2643668.0000000037</v>
       </c>
       <c r="C32" s="24">
         <f>達成度別!E9</f>
-        <v>3363544.0000000037</v>
+        <v>1699816.0000000037</v>
       </c>
       <c r="D32" s="24">
         <f>C32+入力!$B$11-入力!$B$12*12</f>
-        <v>2411396.0000000037</v>
+        <v>747668.00000000373</v>
       </c>
       <c r="E32" s="24">
         <f t="shared" si="4"/>
@@ -2649,19 +2649,19 @@
       </c>
       <c r="B37" s="24">
         <f>'月別（スマレジ版）'!F6</f>
-        <v>1800000</v>
+        <v>1450000</v>
       </c>
       <c r="C37" s="24">
         <f>D37+入力!$B$11/12</f>
-        <v>102342.33333333333</v>
+        <v>-171537.66666666669</v>
       </c>
       <c r="D37" s="24">
         <f>'月別（スマレジ版）'!H6</f>
-        <v>23688</v>
+        <v>-250192</v>
       </c>
       <c r="E37" s="24">
         <f>D37+入力!$B$11/12-入力!$B$12</f>
-        <v>-55657.666666666672</v>
+        <v>-329537.66666666669</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -2671,19 +2671,19 @@
       </c>
       <c r="B38" s="24">
         <f>'月別（スマレジ版）'!F7</f>
-        <v>1800000</v>
+        <v>1700000</v>
       </c>
       <c r="C38" s="24">
         <f>D38+入力!$B$11/12</f>
-        <v>102342.33333333333</v>
+        <v>23102.333333333328</v>
       </c>
       <c r="D38" s="24">
         <f>'月別（スマレジ版）'!H7</f>
-        <v>23688</v>
+        <v>-55552</v>
       </c>
       <c r="E38" s="24">
         <f>D38+入力!$B$11/12-入力!$B$12</f>
-        <v>-55657.666666666672</v>
+        <v>-134897.66666666669</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -2693,19 +2693,19 @@
       </c>
       <c r="B39" s="24">
         <f>'月別（スマレジ版）'!F8</f>
-        <v>2000000</v>
+        <v>1850000</v>
       </c>
       <c r="C39" s="24">
         <f>D39+入力!$B$11/12</f>
-        <v>267742.33333333331</v>
+        <v>145422.33333333331</v>
       </c>
       <c r="D39" s="24">
         <f>'月別（スマレジ版）'!H8</f>
-        <v>189088</v>
+        <v>66768</v>
       </c>
       <c r="E39" s="24">
         <f>D39+入力!$B$11/12-入力!$B$12</f>
-        <v>109742.33333333331</v>
+        <v>-12577.666666666686</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -2715,19 +2715,19 @@
       </c>
       <c r="B40" s="24">
         <f>'月別（スマレジ版）'!F9</f>
-        <v>2000000</v>
+        <v>1900000</v>
       </c>
       <c r="C40" s="24">
         <f>D40+入力!$B$11/12</f>
-        <v>267742.33333333331</v>
+        <v>181582.33333333331</v>
       </c>
       <c r="D40" s="24">
         <f>'月別（スマレジ版）'!H9</f>
-        <v>189088</v>
+        <v>102928</v>
       </c>
       <c r="E40" s="24">
         <f>D40+入力!$B$11/12-入力!$B$12</f>
-        <v>109742.33333333331</v>
+        <v>23582.333333333314</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -2737,19 +2737,19 @@
       </c>
       <c r="B41" s="24">
         <f>'月別（スマレジ版）'!F10</f>
-        <v>2500000</v>
+        <v>2550000</v>
       </c>
       <c r="C41" s="24">
         <f>D41+入力!$B$11/12</f>
-        <v>663942.33333333337</v>
+        <v>700102.33333333337</v>
       </c>
       <c r="D41" s="24">
         <f>'月別（スマレジ版）'!H10</f>
-        <v>585288</v>
+        <v>621448</v>
       </c>
       <c r="E41" s="24">
         <f>D41+入力!$B$11/12-入力!$B$12</f>
-        <v>505942.33333333337</v>
+        <v>542102.33333333337</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -2759,19 +2759,19 @@
       </c>
       <c r="B42" s="24">
         <f>'月別（スマレジ版）'!F11</f>
-        <v>2100000</v>
+        <v>1800000</v>
       </c>
       <c r="C42" s="24">
         <f>D42+入力!$B$11/12</f>
-        <v>333142.33333333331</v>
+        <v>102342.33333333333</v>
       </c>
       <c r="D42" s="24">
         <f>'月別（スマレジ版）'!H11</f>
-        <v>254488</v>
+        <v>23688</v>
       </c>
       <c r="E42" s="24">
         <f>D42+入力!$B$11/12-入力!$B$12</f>
-        <v>175142.33333333331</v>
+        <v>-55657.666666666672</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -2781,19 +2781,19 @@
       </c>
       <c r="B43" s="24">
         <f>'月別（スマレジ版）'!F12</f>
-        <v>1800000</v>
+        <v>1350000</v>
       </c>
       <c r="C43" s="24">
         <f>D43+入力!$B$11/12</f>
-        <v>102342.33333333333</v>
+        <v>-250777.66666666669</v>
       </c>
       <c r="D43" s="24">
         <f>'月別（スマレジ版）'!H12</f>
-        <v>23688</v>
+        <v>-329432</v>
       </c>
       <c r="E43" s="24">
         <f>D43+入力!$B$11/12-入力!$B$12</f>
-        <v>-55657.666666666672</v>
+        <v>-408777.66666666669</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -2803,19 +2803,19 @@
       </c>
       <c r="B44" s="24">
         <f>'月別（スマレジ版）'!F13</f>
-        <v>2000000</v>
+        <v>1800000</v>
       </c>
       <c r="C44" s="24">
         <f>D44+入力!$B$11/12</f>
-        <v>267742.33333333331</v>
+        <v>102342.33333333333</v>
       </c>
       <c r="D44" s="24">
         <f>'月別（スマレジ版）'!H13</f>
-        <v>189088</v>
+        <v>23688</v>
       </c>
       <c r="E44" s="24">
         <f>D44+入力!$B$11/12-入力!$B$12</f>
-        <v>109742.33333333331</v>
+        <v>-55657.666666666672</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -2825,19 +2825,19 @@
       </c>
       <c r="B45" s="24">
         <f>'月別（スマレジ版）'!F14</f>
-        <v>1800000</v>
+        <v>1700000</v>
       </c>
       <c r="C45" s="24">
         <f>D45+入力!$B$11/12</f>
-        <v>102342.33333333333</v>
+        <v>23102.333333333328</v>
       </c>
       <c r="D45" s="24">
         <f>'月別（スマレジ版）'!H14</f>
-        <v>23688</v>
+        <v>-55552</v>
       </c>
       <c r="E45" s="24">
         <f>D45+入力!$B$11/12-入力!$B$12</f>
-        <v>-55657.666666666672</v>
+        <v>-134897.66666666669</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -2869,19 +2869,19 @@
       </c>
       <c r="B47" s="24">
         <f>'月別（スマレジ版）'!F16</f>
-        <v>2000000</v>
+        <v>1800000</v>
       </c>
       <c r="C47" s="24">
         <f>D47+入力!$B$11/12</f>
-        <v>267742.33333333331</v>
+        <v>102342.33333333333</v>
       </c>
       <c r="D47" s="24">
         <f>'月別（スマレジ版）'!H16</f>
-        <v>189088</v>
+        <v>23688</v>
       </c>
       <c r="E47" s="24">
         <f>D47+入力!$B$11/12-入力!$B$12</f>
-        <v>109742.33333333331</v>
+        <v>-55657.666666666672</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -2895,15 +2895,15 @@
       </c>
       <c r="C48" s="24">
         <f>D48+入力!$B$11/12</f>
-        <v>102342.33333333333</v>
+        <v>109262.33333333333</v>
       </c>
       <c r="D48" s="24">
         <f>'月別（スマレジ版）'!H17</f>
-        <v>23688</v>
+        <v>30608</v>
       </c>
       <c r="E48" s="24">
         <f>D48+入力!$B$11/12-入力!$B$12</f>
-        <v>-55657.666666666672</v>
+        <v>-48737.666666666672</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -2912,19 +2912,19 @@
       </c>
       <c r="B49" s="27">
         <f>SUM(B37:B48)</f>
-        <v>23400000</v>
+        <v>21500000</v>
       </c>
       <c r="C49" s="27">
         <f>SUM(C37:C48)</f>
-        <v>2682108.0000000005</v>
+        <v>1169628</v>
       </c>
       <c r="D49" s="27">
         <f>SUM(D37:D48)</f>
-        <v>1738256</v>
+        <v>225776</v>
       </c>
       <c r="E49" s="27">
         <f>SUM(E37:E48)</f>
-        <v>786108.00000000012</v>
+        <v>-726372</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -2933,15 +2933,15 @@
       </c>
       <c r="C50" s="31">
         <f>COUNTIF(C37:C48,"&lt;0")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D50" s="31">
         <f>COUNTIF(D37:D48,"&lt;0")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E50" s="31">
         <f>COUNTIF(E37:E48,"&lt;0")</f>
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3019,23 +3019,23 @@
       </c>
       <c r="C6" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F6,月別目標と営業利益!F6)</f>
-        <v>1800000</v>
+        <v>1450000</v>
       </c>
       <c r="D6" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G6,月別目標と営業利益!G6)</f>
-        <v>1900000</v>
+        <v>1500000</v>
       </c>
       <c r="E6" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D6,月別目標と営業利益!D6)</f>
-        <v>5300000</v>
+        <v>4200000</v>
       </c>
       <c r="F6" s="8">
         <f t="shared" ref="F6:F17" si="0">ROUND(C6/B6,-3)</f>
-        <v>58000</v>
+        <v>47000</v>
       </c>
       <c r="G6" s="8">
         <f t="shared" ref="G6:G17" si="1">ROUND(E6/B6,-3)</f>
-        <v>171000</v>
+        <v>135000</v>
       </c>
       <c r="H6" s="8">
         <f>入力!$B$14</f>
@@ -3055,23 +3055,23 @@
       </c>
       <c r="C7" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F7,月別目標と営業利益!F7)</f>
-        <v>1800000</v>
+        <v>1700000</v>
       </c>
       <c r="D7" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G7,月別目標と営業利益!G7)</f>
-        <v>1900000</v>
+        <v>1800000</v>
       </c>
       <c r="E7" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D7,月別目標と営業利益!D7)</f>
-        <v>5300000</v>
+        <v>5000000</v>
       </c>
       <c r="F7" s="8">
         <f t="shared" si="0"/>
-        <v>60000</v>
+        <v>57000</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="1"/>
-        <v>177000</v>
+        <v>167000</v>
       </c>
       <c r="H7" s="8">
         <f>入力!$B$14</f>
@@ -3091,23 +3091,23 @@
       </c>
       <c r="C8" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F8,月別目標と営業利益!F8)</f>
-        <v>2000000</v>
+        <v>1850000</v>
       </c>
       <c r="D8" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G8,月別目標と営業利益!G8)</f>
-        <v>2100000</v>
+        <v>1950000</v>
       </c>
       <c r="E8" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D8,月別目標と営業利益!D8)</f>
-        <v>5800000</v>
+        <v>5400000</v>
       </c>
       <c r="F8" s="8">
         <f t="shared" si="0"/>
-        <v>65000</v>
+        <v>60000</v>
       </c>
       <c r="G8" s="8">
         <f t="shared" si="1"/>
-        <v>187000</v>
+        <v>174000</v>
       </c>
       <c r="H8" s="8">
         <f>入力!$B$14</f>
@@ -3127,23 +3127,23 @@
       </c>
       <c r="C9" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F9,月別目標と営業利益!F9)</f>
-        <v>2000000</v>
+        <v>1900000</v>
       </c>
       <c r="D9" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G9,月別目標と営業利益!G9)</f>
-        <v>2100000</v>
+        <v>2000000</v>
       </c>
       <c r="E9" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D9,月別目標と営業利益!D9)</f>
-        <v>5800000</v>
+        <v>5600000</v>
       </c>
       <c r="F9" s="8">
         <f t="shared" si="0"/>
-        <v>67000</v>
+        <v>63000</v>
       </c>
       <c r="G9" s="8">
         <f t="shared" si="1"/>
-        <v>193000</v>
+        <v>187000</v>
       </c>
       <c r="H9" s="8">
         <f>入力!$B$14</f>
@@ -3163,23 +3163,23 @@
       </c>
       <c r="C10" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F10,月別目標と営業利益!F10)</f>
-        <v>2500000</v>
+        <v>2550000</v>
       </c>
       <c r="D10" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G10,月別目標と営業利益!G10)</f>
-        <v>2650000</v>
+        <v>2700000</v>
       </c>
       <c r="E10" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D10,月別目標と営業利益!D10)</f>
-        <v>7300000</v>
+        <v>7500000</v>
       </c>
       <c r="F10" s="8">
         <f t="shared" si="0"/>
-        <v>81000</v>
+        <v>82000</v>
       </c>
       <c r="G10" s="8">
         <f t="shared" si="1"/>
-        <v>235000</v>
+        <v>242000</v>
       </c>
       <c r="H10" s="8">
         <f>入力!$B$14</f>
@@ -3199,23 +3199,23 @@
       </c>
       <c r="C11" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F11,月別目標と営業利益!F11)</f>
-        <v>2100000</v>
+        <v>1800000</v>
       </c>
       <c r="D11" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G11,月別目標と営業利益!G11)</f>
-        <v>2200000</v>
+        <v>1900000</v>
       </c>
       <c r="E11" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D11,月別目標と営業利益!D11)</f>
-        <v>6300000</v>
+        <v>5300000</v>
       </c>
       <c r="F11" s="8">
         <f t="shared" si="0"/>
-        <v>68000</v>
+        <v>58000</v>
       </c>
       <c r="G11" s="8">
         <f t="shared" si="1"/>
-        <v>203000</v>
+        <v>171000</v>
       </c>
       <c r="H11" s="8">
         <f>入力!$B$14</f>
@@ -3235,23 +3235,23 @@
       </c>
       <c r="C12" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F12,月別目標と営業利益!F12)</f>
-        <v>1800000</v>
+        <v>1350000</v>
       </c>
       <c r="D12" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G12,月別目標と営業利益!G12)</f>
-        <v>1900000</v>
+        <v>1400000</v>
       </c>
       <c r="E12" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D12,月別目標と営業利益!D12)</f>
-        <v>5300000</v>
+        <v>3900000</v>
       </c>
       <c r="F12" s="8">
         <f t="shared" si="0"/>
-        <v>64000</v>
+        <v>48000</v>
       </c>
       <c r="G12" s="8">
         <f t="shared" si="1"/>
-        <v>189000</v>
+        <v>139000</v>
       </c>
       <c r="H12" s="8">
         <f>入力!$B$14</f>
@@ -3271,23 +3271,23 @@
       </c>
       <c r="C13" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F13,月別目標と営業利益!F13)</f>
-        <v>2000000</v>
+        <v>1800000</v>
       </c>
       <c r="D13" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G13,月別目標と営業利益!G13)</f>
-        <v>2100000</v>
+        <v>1900000</v>
       </c>
       <c r="E13" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D13,月別目標と営業利益!D13)</f>
-        <v>5800000</v>
+        <v>5300000</v>
       </c>
       <c r="F13" s="8">
         <f t="shared" si="0"/>
-        <v>65000</v>
+        <v>58000</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="1"/>
-        <v>187000</v>
+        <v>171000</v>
       </c>
       <c r="H13" s="8">
         <f>入力!$B$14</f>
@@ -3307,23 +3307,23 @@
       </c>
       <c r="C14" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F14,月別目標と営業利益!F14)</f>
-        <v>1800000</v>
+        <v>1700000</v>
       </c>
       <c r="D14" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G14,月別目標と営業利益!G14)</f>
-        <v>1900000</v>
+        <v>1800000</v>
       </c>
       <c r="E14" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D14,月別目標と営業利益!D14)</f>
-        <v>5300000</v>
+        <v>5000000</v>
       </c>
       <c r="F14" s="8">
         <f t="shared" si="0"/>
-        <v>60000</v>
+        <v>57000</v>
       </c>
       <c r="G14" s="8">
         <f t="shared" si="1"/>
-        <v>177000</v>
+        <v>167000</v>
       </c>
       <c r="H14" s="8">
         <f>入力!$B$14</f>
@@ -3379,23 +3379,23 @@
       </c>
       <c r="C16" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F16,月別目標と営業利益!F16)</f>
-        <v>2000000</v>
+        <v>1800000</v>
       </c>
       <c r="D16" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G16,月別目標と営業利益!G16)</f>
-        <v>2100000</v>
+        <v>1900000</v>
       </c>
       <c r="E16" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D16,月別目標と営業利益!D16)</f>
-        <v>5800000</v>
+        <v>5300000</v>
       </c>
       <c r="F16" s="8">
         <f t="shared" si="0"/>
-        <v>67000</v>
+        <v>60000</v>
       </c>
       <c r="G16" s="8">
         <f t="shared" si="1"/>
-        <v>193000</v>
+        <v>177000</v>
       </c>
       <c r="H16" s="8">
         <f>入力!$B$14</f>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="E17" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D17,月別目標と営業利益!D17)</f>
-        <v>5300000</v>
+        <v>5200000</v>
       </c>
       <c r="F17" s="8">
         <f t="shared" si="0"/>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="G17" s="8">
         <f t="shared" si="1"/>
-        <v>171000</v>
+        <v>168000</v>
       </c>
       <c r="H17" s="8">
         <f>入力!$B$14</f>
@@ -3452,15 +3452,15 @@
       </c>
       <c r="C18" s="10">
         <f>SUM(C6:C17)</f>
-        <v>23400000</v>
+        <v>21500000</v>
       </c>
       <c r="D18" s="10">
         <f>SUM(D6:D17)</f>
-        <v>24650000</v>
+        <v>22650000</v>
       </c>
       <c r="E18" s="10">
         <f>SUM(E6:E17)</f>
-        <v>68600000</v>
+        <v>63000000</v>
       </c>
       <c r="H18" s="10">
         <f>SUM(H6:H17)</f>
@@ -3600,7 +3600,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
@@ -3624,10 +3624,10 @@
         <v>41</v>
       </c>
       <c r="B5" s="12">
-        <v>23400000</v>
+        <v>21500000</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.3">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="B6" s="13">
         <f>B5/B19</f>
-        <v>0.34110787172011664</v>
+        <v>0.34126984126984128</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>43</v>
@@ -3762,10 +3762,10 @@
         <v>64</v>
       </c>
       <c r="B19" s="12">
-        <v>68600000</v>
+        <v>63000000</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" x14ac:dyDescent="0.3">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="B21" s="16">
         <f>B6-B9</f>
-        <v>0.27190787172011666</v>
+        <v>0.27206984126984129</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>68</v>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="B22" s="8">
         <f>B20/B21</f>
-        <v>60883209.79923743</v>
+        <v>60846964.598259076</v>
       </c>
       <c r="C22" s="2"/>
     </row>
@@ -3856,11 +3856,11 @@
       </c>
       <c r="B5" s="8">
         <f>入力!$B$19*B4</f>
-        <v>68600000</v>
+        <v>63000000</v>
       </c>
       <c r="C5" s="8">
         <f>入力!$B$19*C4</f>
-        <v>72030000</v>
+        <v>66150000</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>76</v>
@@ -3872,11 +3872,11 @@
       </c>
       <c r="B6" s="8">
         <f>入力!$B$5*B4</f>
-        <v>23400000</v>
+        <v>21500000</v>
       </c>
       <c r="C6" s="8">
         <f>入力!$B$5*C4</f>
-        <v>24570000</v>
+        <v>22575000</v>
       </c>
       <c r="D6" s="2"/>
     </row>
@@ -3918,11 +3918,11 @@
       </c>
       <c r="B9" s="8">
         <f>入力!$B$8*12+B5*入力!$B$9</f>
-        <v>7264624</v>
+        <v>6877104</v>
       </c>
       <c r="C9" s="8">
         <f>入力!$B$8*12+C5*入力!$B$9</f>
-        <v>7501980</v>
+        <v>7095084</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>83</v>
@@ -3962,11 +3962,11 @@
       </c>
       <c r="B12" s="8">
         <f>SUM(B7:B11)</f>
-        <v>21661744</v>
+        <v>21274224</v>
       </c>
       <c r="C12" s="8">
         <f>SUM(C7:C11)</f>
-        <v>22139100</v>
+        <v>21732204</v>
       </c>
       <c r="D12" s="2"/>
     </row>
@@ -3976,11 +3976,11 @@
       </c>
       <c r="B13" s="7">
         <f>B6-B12</f>
-        <v>1738256</v>
+        <v>225776</v>
       </c>
       <c r="C13" s="7">
         <f>C6-C12</f>
-        <v>2430900</v>
+        <v>842796</v>
       </c>
       <c r="D13" s="2"/>
     </row>
@@ -4004,11 +4004,11 @@
       </c>
       <c r="B15" s="7">
         <f>B13-B14</f>
-        <v>1438256</v>
+        <v>-74224</v>
       </c>
       <c r="C15" s="7">
         <f>C13-C14</f>
-        <v>2130900</v>
+        <v>542796</v>
       </c>
       <c r="D15" s="2"/>
     </row>
@@ -4018,11 +4018,11 @@
       </c>
       <c r="B16" s="8">
         <f>B13+B11-入力!$B$12*12</f>
-        <v>786108</v>
+        <v>-726372</v>
       </c>
       <c r="C16" s="8">
         <f>C13+C11-入力!$B$12*12</f>
-        <v>1478752</v>
+        <v>-109352</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>91</v>
@@ -4076,11 +4076,11 @@
       </c>
       <c r="B4" s="8">
         <f>入力!$B$19*A4</f>
-        <v>61740000</v>
+        <v>56700000</v>
       </c>
       <c r="C4" s="8">
         <f>入力!$B$5*A4</f>
-        <v>21060000</v>
+        <v>19350000</v>
       </c>
       <c r="D4" s="8">
         <f>IF(A4&gt;=入力!$B$16,入力!$B$15,IF(A4&gt;=1,入力!$B$14,0))*12</f>
@@ -4088,11 +4088,11 @@
       </c>
       <c r="E4" s="10">
         <f>C4-B4*入力!$B$9-入力!$B$20-D4</f>
-        <v>232968</v>
+        <v>-1128264</v>
       </c>
       <c r="F4" s="8">
         <f>E4-入力!$B$13</f>
-        <v>-67032</v>
+        <v>-1428264</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.3">
@@ -4101,11 +4101,11 @@
       </c>
       <c r="B5" s="8">
         <f>入力!$B$19*A5</f>
-        <v>65170000</v>
+        <v>59850000</v>
       </c>
       <c r="C5" s="8">
         <f>入力!$B$5*A5</f>
-        <v>22230000</v>
+        <v>20425000</v>
       </c>
       <c r="D5" s="8">
         <f>IF(A5&gt;=入力!$B$16,入力!$B$15,IF(A5&gt;=1,入力!$B$14,0))*12</f>
@@ -4113,11 +4113,11 @@
       </c>
       <c r="E5" s="10">
         <f>C5-B5*入力!$B$9-入力!$B$20-D5</f>
-        <v>1165612</v>
+        <v>-271244</v>
       </c>
       <c r="F5" s="8">
         <f>E5-入力!$B$13</f>
-        <v>865612</v>
+        <v>-571244</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.3">
@@ -4126,11 +4126,11 @@
       </c>
       <c r="B6" s="8">
         <f>入力!$B$19*A6</f>
-        <v>68600000</v>
+        <v>63000000</v>
       </c>
       <c r="C6" s="8">
         <f>入力!$B$5*A6</f>
-        <v>23400000</v>
+        <v>21500000</v>
       </c>
       <c r="D6" s="8">
         <f>IF(A6&gt;=入力!$B$16,入力!$B$15,IF(A6&gt;=1,入力!$B$14,0))*12</f>
@@ -4138,11 +4138,11 @@
       </c>
       <c r="E6" s="10">
         <f>C6-B6*入力!$B$9-入力!$B$20-D6</f>
-        <v>1738256</v>
+        <v>225776</v>
       </c>
       <c r="F6" s="8">
         <f>E6-入力!$B$13</f>
-        <v>1438256</v>
+        <v>-74224</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.3">
@@ -4151,11 +4151,11 @@
       </c>
       <c r="B7" s="8">
         <f>入力!$B$19*A7</f>
-        <v>70658000</v>
+        <v>64890000</v>
       </c>
       <c r="C7" s="8">
         <f>入力!$B$5*A7</f>
-        <v>24102000</v>
+        <v>22145000</v>
       </c>
       <c r="D7" s="8">
         <f>IF(A7&gt;=入力!$B$16,入力!$B$15,IF(A7&gt;=1,入力!$B$14,0))*12</f>
@@ -4163,11 +4163,11 @@
       </c>
       <c r="E7" s="10">
         <f>C7-B7*入力!$B$9-入力!$B$20-D7</f>
-        <v>2297842.3999999985</v>
+        <v>739988</v>
       </c>
       <c r="F7" s="8">
         <f>E7-入力!$B$13</f>
-        <v>1997842.3999999985</v>
+        <v>439988</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.3">
@@ -4176,11 +4176,11 @@
       </c>
       <c r="B8" s="8">
         <f>入力!$B$19*A8</f>
-        <v>72030000</v>
+        <v>66150000</v>
       </c>
       <c r="C8" s="8">
         <f>入力!$B$5*A8</f>
-        <v>24570000</v>
+        <v>22575000</v>
       </c>
       <c r="D8" s="8">
         <f>IF(A8&gt;=入力!$B$16,入力!$B$15,IF(A8&gt;=1,入力!$B$14,0))*12</f>
@@ -4188,11 +4188,11 @@
       </c>
       <c r="E8" s="10">
         <f>C8-B8*入力!$B$9-入力!$B$20-D8</f>
-        <v>2430900</v>
+        <v>842796</v>
       </c>
       <c r="F8" s="8">
         <f>E8-入力!$B$13</f>
-        <v>2130900</v>
+        <v>542796</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.3">
@@ -4201,11 +4201,11 @@
       </c>
       <c r="B9" s="8">
         <f>入力!$B$19*A9</f>
-        <v>75460000</v>
+        <v>69300000</v>
       </c>
       <c r="C9" s="8">
         <f>入力!$B$5*A9</f>
-        <v>25740000.000000004</v>
+        <v>23650000.000000004</v>
       </c>
       <c r="D9" s="8">
         <f>IF(A9&gt;=入力!$B$16,入力!$B$15,IF(A9&gt;=1,入力!$B$14,0))*12</f>
@@ -4213,11 +4213,11 @@
       </c>
       <c r="E9" s="10">
         <f>C9-B9*入力!$B$9-入力!$B$20-D9</f>
-        <v>3363544.0000000037</v>
+        <v>1699816.0000000037</v>
       </c>
       <c r="F9" s="8">
         <f>E9-入力!$B$13</f>
-        <v>3063544.0000000037</v>
+        <v>1399816.0000000037</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.3">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="E11" s="8">
         <f>入力!B19*0.01*入力!B21</f>
-        <v>186528.80000000002</v>
+        <v>171404.00000000003</v>
       </c>
     </row>
   </sheetData>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="B4" s="8">
         <f>入力!$B$19*A4</f>
-        <v>21266000</v>
+        <v>19530000</v>
       </c>
       <c r="C4" s="8">
         <f>IF(B4&gt;=入力!$B$5*入力!$B$16-1,入力!$B$15,IF(B4&gt;=入力!$B$5-1,入力!$B$14,0))*12</f>
@@ -4283,11 +4283,11 @@
       </c>
       <c r="D4" s="10">
         <f>B4-入力!$B$19*入力!$B$9-入力!$B$20-C4</f>
-        <v>-35744</v>
+        <v>-1384224</v>
       </c>
       <c r="E4" s="8">
         <f>D4-入力!$B$13</f>
-        <v>-335744</v>
+        <v>-1684224</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.3">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="B5" s="8">
         <f>入力!$B$19*A5</f>
-        <v>21952000</v>
+        <v>20160000</v>
       </c>
       <c r="C5" s="8">
         <f>IF(B5&gt;=入力!$B$5*入力!$B$16-1,入力!$B$15,IF(B5&gt;=入力!$B$5-1,入力!$B$14,0))*12</f>
@@ -4304,11 +4304,11 @@
       </c>
       <c r="D5" s="10">
         <f>B5-入力!$B$19*入力!$B$9-入力!$B$20-C5</f>
-        <v>650256</v>
+        <v>-754224</v>
       </c>
       <c r="E5" s="8">
         <f>D5-入力!$B$13</f>
-        <v>350256</v>
+        <v>-1054224</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.3">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="B6" s="8">
         <f>入力!$B$19*A6</f>
-        <v>22638000</v>
+        <v>20790000</v>
       </c>
       <c r="C6" s="8">
         <f>IF(B6&gt;=入力!$B$5*入力!$B$16-1,入力!$B$15,IF(B6&gt;=入力!$B$5-1,入力!$B$14,0))*12</f>
@@ -4325,21 +4325,21 @@
       </c>
       <c r="D6" s="10">
         <f>B6-入力!$B$19*入力!$B$9-入力!$B$20-C6</f>
-        <v>1336256</v>
+        <v>-124224</v>
       </c>
       <c r="E6" s="8">
         <f>D6-入力!$B$13</f>
-        <v>1036256</v>
+        <v>-424224</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="15">
         <f>入力!B6</f>
-        <v>0.34110787172011664</v>
+        <v>0.34126984126984128</v>
       </c>
       <c r="B7" s="8">
         <f>入力!$B$19*A7</f>
-        <v>23400000</v>
+        <v>21500000</v>
       </c>
       <c r="C7" s="8">
         <f>IF(B7&gt;=入力!$B$5*入力!$B$16-1,入力!$B$15,IF(B7&gt;=入力!$B$5-1,入力!$B$14,0))*12</f>
@@ -4347,11 +4347,11 @@
       </c>
       <c r="D7" s="10">
         <f>B7-入力!$B$19*入力!$B$9-入力!$B$20-C7</f>
-        <v>1738256</v>
+        <v>225776</v>
       </c>
       <c r="E7" s="8">
         <f>D7-入力!$B$13</f>
-        <v>1438256</v>
+        <v>-74224</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.3">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="B8" s="8">
         <f>入力!$B$19*A8</f>
-        <v>24010000</v>
+        <v>22050000</v>
       </c>
       <c r="C8" s="8">
         <f>IF(B8&gt;=入力!$B$5*入力!$B$16-1,入力!$B$15,IF(B8&gt;=入力!$B$5-1,入力!$B$14,0))*12</f>
@@ -4368,11 +4368,11 @@
       </c>
       <c r="D8" s="10">
         <f>B8-入力!$B$19*入力!$B$9-入力!$B$20-C8</f>
-        <v>2348256</v>
+        <v>775776</v>
       </c>
       <c r="E8" s="8">
         <f>D8-入力!$B$13</f>
-        <v>2048256</v>
+        <v>475776</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.3">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="B9" s="8">
         <f>入力!$B$19*A9</f>
-        <v>24696000</v>
+        <v>22680000</v>
       </c>
       <c r="C9" s="8">
         <f>IF(B9&gt;=入力!$B$5*入力!$B$16-1,入力!$B$15,IF(B9&gt;=入力!$B$5-1,入力!$B$14,0))*12</f>
@@ -4389,11 +4389,11 @@
       </c>
       <c r="D9" s="10">
         <f>B9-入力!$B$19*入力!$B$9-入力!$B$20-C9</f>
-        <v>2794256</v>
+        <v>1165776</v>
       </c>
       <c r="E9" s="8">
         <f>D9-入力!$B$13</f>
-        <v>2494256</v>
+        <v>865776</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.3">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="D11" s="8">
         <f>入力!B19*0.01</f>
-        <v>686000</v>
+        <v>630000</v>
       </c>
     </row>
   </sheetData>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="E6" s="8">
         <f>ROUND(入力!$B$5*C6,-3)</f>
-        <v>1326000</v>
+        <v>1218000</v>
       </c>
       <c r="F6" s="12">
         <v>1200000</v>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="E7" s="8">
         <f>ROUND(入力!$B$5*C7,-3)</f>
-        <v>1587000</v>
+        <v>1458000</v>
       </c>
       <c r="F7" s="12">
         <v>1450000</v>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="E8" s="8">
         <f>ROUND(入力!$B$5*C8,-3)</f>
-        <v>2152000</v>
+        <v>1977000</v>
       </c>
       <c r="F8" s="12">
         <v>2000000</v>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="E9" s="8">
         <f>ROUND(入力!$B$5*C9,-3)</f>
-        <v>2246000</v>
+        <v>2063000</v>
       </c>
       <c r="F9" s="12">
         <v>2050000</v>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="E10" s="8">
         <f>ROUND(入力!$B$5*C10,-3)</f>
-        <v>2974000</v>
+        <v>2733000</v>
       </c>
       <c r="F10" s="12">
         <v>2750000</v>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="E11" s="8">
         <f>ROUND(入力!$B$5*C11,-3)</f>
-        <v>2115000</v>
+        <v>1944000</v>
       </c>
       <c r="F11" s="12">
         <v>1950000</v>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="E12" s="8">
         <f>ROUND(入力!$B$5*C12,-3)</f>
-        <v>1219000</v>
+        <v>1120000</v>
       </c>
       <c r="F12" s="12">
         <v>1100000</v>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="E13" s="8">
         <f>ROUND(入力!$B$5*C13,-3)</f>
-        <v>1927000</v>
+        <v>1771000</v>
       </c>
       <c r="F13" s="12">
         <v>1750000</v>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="E14" s="8">
         <f>ROUND(入力!$B$5*C14,-3)</f>
-        <v>1562000</v>
+        <v>1435000</v>
       </c>
       <c r="F14" s="12">
         <v>1450000</v>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="E15" s="8">
         <f>ROUND(入力!$B$5*C15,-3)</f>
-        <v>2093000</v>
+        <v>1923000</v>
       </c>
       <c r="F15" s="12">
         <v>1950000</v>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="E16" s="8">
         <f>ROUND(入力!$B$5*C16,-3)</f>
-        <v>2132000</v>
+        <v>1959000</v>
       </c>
       <c r="F16" s="12">
         <v>1950000</v>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="E17" s="8">
         <f>ROUND(入力!$B$5*C17,-3)</f>
-        <v>2067000</v>
+        <v>1900000</v>
       </c>
       <c r="F17" s="12">
         <v>1900000</v>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="E18" s="10">
         <f>SUM(E6:E17)</f>
-        <v>23400000</v>
+        <v>21501000</v>
       </c>
       <c r="F18" s="10">
         <f>SUM(F6:F17)</f>
@@ -5034,11 +5034,11 @@
       </c>
       <c r="D19" s="8">
         <f>D18-入力!B19</f>
-        <v>-5600000</v>
+        <v>0</v>
       </c>
       <c r="F19" s="8">
         <f>F18-入力!B5</f>
-        <v>-1900000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15" x14ac:dyDescent="0.3">
@@ -5066,7 +5066,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" x14ac:dyDescent="0.3">
@@ -5132,30 +5132,30 @@
         <v>5.8333333333333334E-2</v>
       </c>
       <c r="D6" s="12">
-        <v>5300000</v>
+        <v>4200000</v>
       </c>
       <c r="E6" s="8">
         <f>ROUND(入力!$B$5*C6,-3)</f>
-        <v>1365000</v>
+        <v>1254000</v>
       </c>
       <c r="F6" s="12">
-        <v>1800000</v>
+        <v>1450000</v>
       </c>
       <c r="G6" s="8">
         <f>ROUND(F6*入力!$B$16/50000,0)*50000</f>
-        <v>1900000</v>
+        <v>1500000</v>
       </c>
       <c r="H6" s="8">
         <f>F6-D6*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>23688</v>
+        <v>-250192</v>
       </c>
       <c r="I6" s="8">
         <f>SUM($H$6:H6)</f>
-        <v>23688</v>
+        <v>-250192</v>
       </c>
       <c r="J6" s="8">
         <f>F6-月別目標と営業利益!F6</f>
-        <v>600000</v>
+        <v>250000</v>
       </c>
       <c r="K6" s="12"/>
       <c r="L6" s="11" t="str">
@@ -5179,30 +5179,30 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D7" s="12">
-        <v>5300000</v>
+        <v>5000000</v>
       </c>
       <c r="E7" s="8">
         <f>ROUND(入力!$B$5*C7,-3)</f>
-        <v>1755000</v>
+        <v>1613000</v>
       </c>
       <c r="F7" s="12">
-        <v>1800000</v>
+        <v>1700000</v>
       </c>
       <c r="G7" s="8">
         <f>ROUND(F7*入力!$B$16/50000,0)*50000</f>
-        <v>1900000</v>
+        <v>1800000</v>
       </c>
       <c r="H7" s="8">
         <f>F7-D7*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>23688</v>
+        <v>-55552</v>
       </c>
       <c r="I7" s="8">
         <f>SUM($H$6:H7)</f>
-        <v>47376</v>
+        <v>-305744</v>
       </c>
       <c r="J7" s="8">
         <f>F7-月別目標と営業利益!F7</f>
-        <v>350000</v>
+        <v>250000</v>
       </c>
       <c r="K7" s="12"/>
       <c r="L7" s="11" t="str">
@@ -5226,30 +5226,30 @@
         <v>9.166666666666666E-2</v>
       </c>
       <c r="D8" s="12">
-        <v>5800000</v>
+        <v>5400000</v>
       </c>
       <c r="E8" s="8">
         <f>ROUND(入力!$B$5*C8,-3)</f>
-        <v>2145000</v>
+        <v>1971000</v>
       </c>
       <c r="F8" s="12">
-        <v>2000000</v>
+        <v>1850000</v>
       </c>
       <c r="G8" s="8">
         <f>ROUND(F8*入力!$B$16/50000,0)*50000</f>
-        <v>2100000</v>
+        <v>1950000</v>
       </c>
       <c r="H8" s="8">
         <f>F8-D8*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>189088</v>
+        <v>66768</v>
       </c>
       <c r="I8" s="8">
         <f>SUM($H$6:H8)</f>
-        <v>236464</v>
+        <v>-238976</v>
       </c>
       <c r="J8" s="8">
         <f>F8-月別目標と営業利益!F8</f>
-        <v>0</v>
+        <v>-150000</v>
       </c>
       <c r="K8" s="12"/>
       <c r="L8" s="11" t="str">
@@ -5273,30 +5273,30 @@
         <v>9.166666666666666E-2</v>
       </c>
       <c r="D9" s="12">
-        <v>5800000</v>
+        <v>5600000</v>
       </c>
       <c r="E9" s="8">
         <f>ROUND(入力!$B$5*C9,-3)</f>
-        <v>2145000</v>
+        <v>1971000</v>
       </c>
       <c r="F9" s="12">
-        <v>2000000</v>
+        <v>1900000</v>
       </c>
       <c r="G9" s="8">
         <f>ROUND(F9*入力!$B$16/50000,0)*50000</f>
-        <v>2100000</v>
+        <v>2000000</v>
       </c>
       <c r="H9" s="8">
         <f>F9-D9*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>189088</v>
+        <v>102928</v>
       </c>
       <c r="I9" s="8">
         <f>SUM($H$6:H9)</f>
-        <v>425552</v>
+        <v>-136048</v>
       </c>
       <c r="J9" s="8">
         <f>F9-月別目標と営業利益!F9</f>
-        <v>-50000</v>
+        <v>-150000</v>
       </c>
       <c r="K9" s="12"/>
       <c r="L9" s="11" t="str">
@@ -5320,30 +5320,30 @@
         <v>0.11666666666666667</v>
       </c>
       <c r="D10" s="12">
-        <v>7300000</v>
+        <v>7500000</v>
       </c>
       <c r="E10" s="8">
         <f>ROUND(入力!$B$5*C10,-3)</f>
-        <v>2730000</v>
+        <v>2508000</v>
       </c>
       <c r="F10" s="12">
-        <v>2500000</v>
+        <v>2550000</v>
       </c>
       <c r="G10" s="8">
         <f>ROUND(F10*入力!$B$16/50000,0)*50000</f>
-        <v>2650000</v>
+        <v>2700000</v>
       </c>
       <c r="H10" s="8">
         <f>F10-D10*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>585288</v>
+        <v>621448</v>
       </c>
       <c r="I10" s="8">
         <f>SUM($H$6:H10)</f>
-        <v>1010840</v>
+        <v>485400</v>
       </c>
       <c r="J10" s="8">
         <f>F10-月別目標と営業利益!F10</f>
-        <v>-250000</v>
+        <v>-200000</v>
       </c>
       <c r="K10" s="12"/>
       <c r="L10" s="11" t="str">
@@ -5367,30 +5367,30 @@
         <v>0.1</v>
       </c>
       <c r="D11" s="12">
-        <v>6300000</v>
+        <v>5300000</v>
       </c>
       <c r="E11" s="8">
         <f>ROUND(入力!$B$5*C11,-3)</f>
-        <v>2340000</v>
+        <v>2150000</v>
       </c>
       <c r="F11" s="12">
-        <v>2100000</v>
+        <v>1800000</v>
       </c>
       <c r="G11" s="8">
         <f>ROUND(F11*入力!$B$16/50000,0)*50000</f>
-        <v>2200000</v>
+        <v>1900000</v>
       </c>
       <c r="H11" s="8">
         <f>F11-D11*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>254488</v>
+        <v>23688</v>
       </c>
       <c r="I11" s="8">
         <f>SUM($H$6:H11)</f>
-        <v>1265328</v>
+        <v>509088</v>
       </c>
       <c r="J11" s="8">
         <f>F11-月別目標と営業利益!F11</f>
-        <v>150000</v>
+        <v>-150000</v>
       </c>
       <c r="K11" s="12"/>
       <c r="L11" s="11" t="str">
@@ -5414,30 +5414,30 @@
         <v>5.8333333333333334E-2</v>
       </c>
       <c r="D12" s="12">
-        <v>5300000</v>
+        <v>3900000</v>
       </c>
       <c r="E12" s="8">
         <f>ROUND(入力!$B$5*C12,-3)</f>
-        <v>1365000</v>
+        <v>1254000</v>
       </c>
       <c r="F12" s="12">
-        <v>1800000</v>
+        <v>1350000</v>
       </c>
       <c r="G12" s="8">
         <f>ROUND(F12*入力!$B$16/50000,0)*50000</f>
-        <v>1900000</v>
+        <v>1400000</v>
       </c>
       <c r="H12" s="8">
         <f>F12-D12*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>23688</v>
+        <v>-329432</v>
       </c>
       <c r="I12" s="8">
         <f>SUM($H$6:H12)</f>
-        <v>1289016</v>
+        <v>179656</v>
       </c>
       <c r="J12" s="8">
         <f>F12-月別目標と営業利益!F12</f>
-        <v>700000</v>
+        <v>250000</v>
       </c>
       <c r="K12" s="12"/>
       <c r="L12" s="11" t="str">
@@ -5461,30 +5461,30 @@
         <v>9.166666666666666E-2</v>
       </c>
       <c r="D13" s="12">
-        <v>5800000</v>
+        <v>5300000</v>
       </c>
       <c r="E13" s="8">
         <f>ROUND(入力!$B$5*C13,-3)</f>
-        <v>2145000</v>
+        <v>1971000</v>
       </c>
       <c r="F13" s="12">
-        <v>2000000</v>
+        <v>1800000</v>
       </c>
       <c r="G13" s="8">
         <f>ROUND(F13*入力!$B$16/50000,0)*50000</f>
-        <v>2100000</v>
+        <v>1900000</v>
       </c>
       <c r="H13" s="8">
         <f>F13-D13*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>189088</v>
+        <v>23688</v>
       </c>
       <c r="I13" s="8">
         <f>SUM($H$6:H13)</f>
-        <v>1478104</v>
+        <v>203344</v>
       </c>
       <c r="J13" s="8">
         <f>F13-月別目標と営業利益!F13</f>
-        <v>250000</v>
+        <v>50000</v>
       </c>
       <c r="K13" s="12"/>
       <c r="L13" s="11" t="str">
@@ -5508,30 +5508,30 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D14" s="12">
-        <v>5300000</v>
+        <v>5000000</v>
       </c>
       <c r="E14" s="8">
         <f>ROUND(入力!$B$5*C14,-3)</f>
-        <v>1755000</v>
+        <v>1613000</v>
       </c>
       <c r="F14" s="12">
-        <v>1800000</v>
+        <v>1700000</v>
       </c>
       <c r="G14" s="8">
         <f>ROUND(F14*入力!$B$16/50000,0)*50000</f>
-        <v>1900000</v>
+        <v>1800000</v>
       </c>
       <c r="H14" s="8">
         <f>F14-D14*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>23688</v>
+        <v>-55552</v>
       </c>
       <c r="I14" s="8">
         <f>SUM($H$6:H14)</f>
-        <v>1501792</v>
+        <v>147792</v>
       </c>
       <c r="J14" s="8">
         <f>F14-月別目標と営業利益!F14</f>
-        <v>350000</v>
+        <v>250000</v>
       </c>
       <c r="K14" s="12"/>
       <c r="L14" s="11" t="str">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="E15" s="8">
         <f>ROUND(入力!$B$5*C15,-3)</f>
-        <v>1755000</v>
+        <v>1613000</v>
       </c>
       <c r="F15" s="12">
         <v>1800000</v>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="I15" s="8">
         <f>SUM($H$6:H15)</f>
-        <v>1525480</v>
+        <v>171480</v>
       </c>
       <c r="J15" s="8">
         <f>F15-月別目標と営業利益!F15</f>
@@ -5602,30 +5602,30 @@
         <v>9.166666666666666E-2</v>
       </c>
       <c r="D16" s="12">
-        <v>5800000</v>
+        <v>5300000</v>
       </c>
       <c r="E16" s="8">
         <f>ROUND(入力!$B$5*C16,-3)</f>
-        <v>2145000</v>
+        <v>1971000</v>
       </c>
       <c r="F16" s="12">
-        <v>2000000</v>
+        <v>1800000</v>
       </c>
       <c r="G16" s="8">
         <f>ROUND(F16*入力!$B$16/50000,0)*50000</f>
-        <v>2100000</v>
+        <v>1900000</v>
       </c>
       <c r="H16" s="8">
         <f>F16-D16*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>189088</v>
+        <v>23688</v>
       </c>
       <c r="I16" s="8">
         <f>SUM($H$6:H16)</f>
-        <v>1714568</v>
+        <v>195168</v>
       </c>
       <c r="J16" s="8">
         <f>F16-月別目標と営業利益!F16</f>
-        <v>50000</v>
+        <v>-150000</v>
       </c>
       <c r="K16" s="12"/>
       <c r="L16" s="11" t="str">
@@ -5649,11 +5649,11 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D17" s="12">
-        <v>5300000</v>
+        <v>5200000</v>
       </c>
       <c r="E17" s="8">
         <f>ROUND(入力!$B$5*C17,-3)</f>
-        <v>1755000</v>
+        <v>1613000</v>
       </c>
       <c r="F17" s="12">
         <v>1800000</v>
@@ -5664,11 +5664,11 @@
       </c>
       <c r="H17" s="8">
         <f>F17-D17*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>23688</v>
+        <v>30608</v>
       </c>
       <c r="I17" s="8">
         <f>SUM($H$6:H17)</f>
-        <v>1738256</v>
+        <v>225776</v>
       </c>
       <c r="J17" s="8">
         <f>F17-月別目標と営業利益!F17</f>
@@ -5694,23 +5694,23 @@
       </c>
       <c r="D18" s="10">
         <f>SUM(D6:D17)</f>
-        <v>68600000</v>
+        <v>63000000</v>
       </c>
       <c r="E18" s="10">
         <f>SUM(E6:E17)</f>
-        <v>23400000</v>
+        <v>21502000</v>
       </c>
       <c r="F18" s="10">
         <f>SUM(F6:F17)</f>
-        <v>23400000</v>
+        <v>21500000</v>
       </c>
       <c r="G18" s="10">
         <f>SUM(G6:G17)</f>
-        <v>24650000</v>
+        <v>22650000</v>
       </c>
       <c r="H18" s="10">
         <f>SUM(H6:H17)</f>
-        <v>1738256</v>
+        <v>225776</v>
       </c>
       <c r="K18" s="10">
         <f>SUM(K6:K17)</f>

--- a/excel/Weekends_予算と報奨金案_粗利2150万円.xlsx
+++ b/excel/Weekends_予算と報奨金案_粗利2150万円.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yataka-02\AppData\Local\Temp\claude\C--Users-yataka-02-Desktop-Claude\76fa42a7-01fc-42d8-86c7-11cf90447c56\scratchpad\margin-calculator\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C24036CC-0A49-4021-AB43-0189274730BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF397974-1E34-4FE5-9D9D-CFC2F24D1D57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="166">
   <si>
     <t>Weekends 2027年度 月別目標（売上6,300万円・粗利2,150万円・税抜）</t>
   </si>
@@ -371,9 +371,6 @@
   </si>
   <si>
     <t>（丸めた目標を直したら、D19とF19が0円になるように調整してください）</t>
-  </si>
-  <si>
-    <t>月の目標は、店長がスマレジに登録した店舗予算（年6,000万円・税抜）の月比率で配分。同じ予算額の月は同じ目標にそろえた。</t>
   </si>
   <si>
     <t>スマレジ予算（参考）</t>
@@ -527,10 +524,6 @@
     <phoneticPr fontId="9"/>
   </si>
   <si>
-    <t>2026-10-07：粗利2,150万円に戻し、月の目標をならした（閑散月の売上は前年の1.4倍以内）</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
     <t>検討案（税抜）</t>
     <phoneticPr fontId="9"/>
   </si>
@@ -539,11 +532,27 @@
     <phoneticPr fontId="9"/>
   </si>
   <si>
-    <t>黄色の「売上目標」は10万円単位、「粗利目標100%」は5万円単位。2026-10-07に、営業利益の赤字月を減らすよう月の目標をならした：前年の売上が少ない月（8・9・2・4月）は前年の1.4倍まで引き上げ、残りは前年比が同じになるよう配分（年計 売上6,300万円・粗利2,150万円）。</t>
+    <t>月別の目標と営業利益　構成比版（参考。現在の月別目標はスマレジ版シート）</t>
     <phoneticPr fontId="9"/>
   </si>
   <si>
-    <t>月別の目標と営業利益　構成比版（参考。現在の月別目標はスマレジ版シート）</t>
+    <t>年間予算（決算上の目標）。月の目標の合計は2,285万円で、予算より135万円多い（2026-10-07 ②案）</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>月の目標＝店長がスマレジに登録した予算（年6,000万円・税抜）×粗利率。ただし赤字になる月（8・9・2・4・5・7月）は、販管費を賄える粗利180万円・売上530万円に引き上げた。</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>黄色の目標は手入力。月の目標の合計（売上6,680万円・粗利2,285万円）は年間予算（6,300万円・2,150万円）より多く、その差が予算達成の余裕になる（2026-10-07 ②案）。</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>年間予算との差（上乗せ分）</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>（月の目標の合計が年間予算をどれだけ上回るか。プラスなら、月の目標がいくつか未達でも年間予算に届く余裕がある）</t>
     <phoneticPr fontId="9"/>
   </si>
 </sst>
@@ -1328,40 +1337,40 @@
                 <c:formatCode>#,##0;[Red]\-#,##0;\-</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>-250192</c:v>
+                  <c:v>23688</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-55552</c:v>
+                  <c:v>23688</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>66768</c:v>
+                  <c:v>109848</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>102928</c:v>
+                  <c:v>109848</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>621448</c:v>
+                  <c:v>506048</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>225248</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>23688</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>-329432</c:v>
-                </c:pt>
                 <c:pt idx="7">
+                  <c:v>109848</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>23688</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-55552</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>23688</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>109848</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>23688</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>30608</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1416,40 +1425,40 @@
                 <c:formatCode>#,##0;[Red]\-#,##0;\-</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>-250192</c:v>
+                  <c:v>23688</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-305744</c:v>
+                  <c:v>47376</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-238976</c:v>
+                  <c:v>157224</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-136048</c:v>
+                  <c:v>267072</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>485400</c:v>
+                  <c:v>773120</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>509088</c:v>
+                  <c:v>998368</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>179656</c:v>
+                  <c:v>1022056</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>203344</c:v>
+                  <c:v>1131904</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>147792</c:v>
+                  <c:v>1155592</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>171480</c:v>
+                  <c:v>1179280</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>195168</c:v>
+                  <c:v>1289128</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>225776</c:v>
+                  <c:v>1312816</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1929,22 +1938,22 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1952,25 +1961,25 @@
         <v>38</v>
       </c>
       <c r="B6" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="D6" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="E6" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="F6" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="G6" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="G6" s="22" t="s">
-        <v>150</v>
-      </c>
       <c r="H6" s="22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -2031,7 +2040,7 @@
         <v>66150000</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -2063,7 +2072,7 @@
         <v>22575000</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -2095,7 +2104,7 @@
         <v>9600000</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -2159,7 +2168,7 @@
         <v>7095084</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -2193,7 +2202,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="26" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B14" s="27">
         <f t="shared" ref="B14:G14" si="0">SUM(B10:B13)</f>
@@ -2220,12 +2229,12 @@
         <v>20788352</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B15" s="27">
         <f t="shared" ref="B15:G15" si="1">B9-B14</f>
@@ -2252,7 +2261,7 @@
         <v>1786648</v>
       </c>
       <c r="H15" s="26" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -2280,12 +2289,12 @@
         <v>0</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B17" s="24">
         <v>0</v>
@@ -2308,7 +2317,7 @@
         <v>1896000</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -2340,7 +2349,7 @@
         <v>-109352</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -2431,12 +2440,12 @@
         <v>64346610.114116348</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B22" s="25">
         <f>B21/入力!$B$19</f>
@@ -2463,12 +2472,12 @@
         <v>1.0213747637161326</v>
       </c>
       <c r="H22" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="21" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="30" x14ac:dyDescent="0.3">
@@ -2476,16 +2485,16 @@
         <v>74</v>
       </c>
       <c r="B26" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="C26" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="C26" s="22" t="s">
+      <c r="D26" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="E26" s="22" t="s">
         <v>154</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -2622,7 +2631,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="30" x14ac:dyDescent="0.3">
@@ -2633,13 +2642,13 @@
         <v>103</v>
       </c>
       <c r="C36" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="D36" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="D36" s="22" t="s">
+      <c r="E36" s="22" t="s">
         <v>153</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -2649,19 +2658,19 @@
       </c>
       <c r="B37" s="24">
         <f>'月別（スマレジ版）'!F6</f>
-        <v>1450000</v>
+        <v>1800000</v>
       </c>
       <c r="C37" s="24">
         <f>D37+入力!$B$11/12</f>
-        <v>-171537.66666666669</v>
+        <v>102342.33333333333</v>
       </c>
       <c r="D37" s="24">
         <f>'月別（スマレジ版）'!H6</f>
-        <v>-250192</v>
+        <v>23688</v>
       </c>
       <c r="E37" s="24">
         <f>D37+入力!$B$11/12-入力!$B$12</f>
-        <v>-329537.66666666669</v>
+        <v>-55657.666666666672</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -2671,19 +2680,19 @@
       </c>
       <c r="B38" s="24">
         <f>'月別（スマレジ版）'!F7</f>
-        <v>1700000</v>
+        <v>1800000</v>
       </c>
       <c r="C38" s="24">
         <f>D38+入力!$B$11/12</f>
-        <v>23102.333333333328</v>
+        <v>102342.33333333333</v>
       </c>
       <c r="D38" s="24">
         <f>'月別（スマレジ版）'!H7</f>
-        <v>-55552</v>
+        <v>23688</v>
       </c>
       <c r="E38" s="24">
         <f>D38+入力!$B$11/12-入力!$B$12</f>
-        <v>-134897.66666666669</v>
+        <v>-55657.666666666672</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -2693,19 +2702,19 @@
       </c>
       <c r="B39" s="24">
         <f>'月別（スマレジ版）'!F8</f>
-        <v>1850000</v>
+        <v>1900000</v>
       </c>
       <c r="C39" s="24">
         <f>D39+入力!$B$11/12</f>
-        <v>145422.33333333331</v>
+        <v>188502.33333333331</v>
       </c>
       <c r="D39" s="24">
         <f>'月別（スマレジ版）'!H8</f>
-        <v>66768</v>
+        <v>109848</v>
       </c>
       <c r="E39" s="24">
         <f>D39+入力!$B$11/12-入力!$B$12</f>
-        <v>-12577.666666666686</v>
+        <v>30502.333333333314</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -2719,15 +2728,15 @@
       </c>
       <c r="C40" s="24">
         <f>D40+入力!$B$11/12</f>
-        <v>181582.33333333331</v>
+        <v>188502.33333333331</v>
       </c>
       <c r="D40" s="24">
         <f>'月別（スマレジ版）'!H9</f>
-        <v>102928</v>
+        <v>109848</v>
       </c>
       <c r="E40" s="24">
         <f>D40+入力!$B$11/12-入力!$B$12</f>
-        <v>23582.333333333314</v>
+        <v>30502.333333333314</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -2737,19 +2746,19 @@
       </c>
       <c r="B41" s="24">
         <f>'月別（スマレジ版）'!F10</f>
-        <v>2550000</v>
+        <v>2400000</v>
       </c>
       <c r="C41" s="24">
         <f>D41+入力!$B$11/12</f>
-        <v>700102.33333333337</v>
+        <v>584702.33333333337</v>
       </c>
       <c r="D41" s="24">
         <f>'月別（スマレジ版）'!H10</f>
-        <v>621448</v>
+        <v>506048</v>
       </c>
       <c r="E41" s="24">
         <f>D41+入力!$B$11/12-入力!$B$12</f>
-        <v>542102.33333333337</v>
+        <v>426702.33333333337</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -2759,19 +2768,19 @@
       </c>
       <c r="B42" s="24">
         <f>'月別（スマレジ版）'!F11</f>
-        <v>1800000</v>
+        <v>2050000</v>
       </c>
       <c r="C42" s="24">
         <f>D42+入力!$B$11/12</f>
-        <v>102342.33333333333</v>
+        <v>303902.33333333331</v>
       </c>
       <c r="D42" s="24">
         <f>'月別（スマレジ版）'!H11</f>
-        <v>23688</v>
+        <v>225248</v>
       </c>
       <c r="E42" s="24">
         <f>D42+入力!$B$11/12-入力!$B$12</f>
-        <v>-55657.666666666672</v>
+        <v>145902.33333333331</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -2781,19 +2790,19 @@
       </c>
       <c r="B43" s="24">
         <f>'月別（スマレジ版）'!F12</f>
-        <v>1350000</v>
+        <v>1800000</v>
       </c>
       <c r="C43" s="24">
         <f>D43+入力!$B$11/12</f>
-        <v>-250777.66666666669</v>
+        <v>102342.33333333333</v>
       </c>
       <c r="D43" s="24">
         <f>'月別（スマレジ版）'!H12</f>
-        <v>-329432</v>
+        <v>23688</v>
       </c>
       <c r="E43" s="24">
         <f>D43+入力!$B$11/12-入力!$B$12</f>
-        <v>-408777.66666666669</v>
+        <v>-55657.666666666672</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -2803,19 +2812,19 @@
       </c>
       <c r="B44" s="24">
         <f>'月別（スマレジ版）'!F13</f>
-        <v>1800000</v>
+        <v>1900000</v>
       </c>
       <c r="C44" s="24">
         <f>D44+入力!$B$11/12</f>
-        <v>102342.33333333333</v>
+        <v>188502.33333333331</v>
       </c>
       <c r="D44" s="24">
         <f>'月別（スマレジ版）'!H13</f>
-        <v>23688</v>
+        <v>109848</v>
       </c>
       <c r="E44" s="24">
         <f>D44+入力!$B$11/12-入力!$B$12</f>
-        <v>-55657.666666666672</v>
+        <v>30502.333333333314</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -2825,19 +2834,19 @@
       </c>
       <c r="B45" s="24">
         <f>'月別（スマレジ版）'!F14</f>
-        <v>1700000</v>
+        <v>1800000</v>
       </c>
       <c r="C45" s="24">
         <f>D45+入力!$B$11/12</f>
-        <v>23102.333333333328</v>
+        <v>102342.33333333333</v>
       </c>
       <c r="D45" s="24">
         <f>'月別（スマレジ版）'!H14</f>
-        <v>-55552</v>
+        <v>23688</v>
       </c>
       <c r="E45" s="24">
         <f>D45+入力!$B$11/12-入力!$B$12</f>
-        <v>-134897.66666666669</v>
+        <v>-55657.666666666672</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -2869,19 +2878,19 @@
       </c>
       <c r="B47" s="24">
         <f>'月別（スマレジ版）'!F16</f>
-        <v>1800000</v>
+        <v>1900000</v>
       </c>
       <c r="C47" s="24">
         <f>D47+入力!$B$11/12</f>
-        <v>102342.33333333333</v>
+        <v>188502.33333333331</v>
       </c>
       <c r="D47" s="24">
         <f>'月別（スマレジ版）'!H16</f>
-        <v>23688</v>
+        <v>109848</v>
       </c>
       <c r="E47" s="24">
         <f>D47+入力!$B$11/12-入力!$B$12</f>
-        <v>-55657.666666666672</v>
+        <v>30502.333333333314</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -2895,15 +2904,15 @@
       </c>
       <c r="C48" s="24">
         <f>D48+入力!$B$11/12</f>
-        <v>109262.33333333333</v>
+        <v>102342.33333333333</v>
       </c>
       <c r="D48" s="24">
         <f>'月別（スマレジ版）'!H17</f>
-        <v>30608</v>
+        <v>23688</v>
       </c>
       <c r="E48" s="24">
         <f>D48+入力!$B$11/12-入力!$B$12</f>
-        <v>-48737.666666666672</v>
+        <v>-55657.666666666672</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -2912,36 +2921,36 @@
       </c>
       <c r="B49" s="27">
         <f>SUM(B37:B48)</f>
-        <v>21500000</v>
+        <v>22850000</v>
       </c>
       <c r="C49" s="27">
         <f>SUM(C37:C48)</f>
-        <v>1169628</v>
+        <v>2256667.9999999995</v>
       </c>
       <c r="D49" s="27">
         <f>SUM(D37:D48)</f>
-        <v>225776</v>
+        <v>1312816</v>
       </c>
       <c r="E49" s="27">
         <f>SUM(E37:E48)</f>
-        <v>-726372</v>
+        <v>360667.99999999983</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="30" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C50" s="31">
         <f>COUNTIF(C37:C48,"&lt;0")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D50" s="31">
         <f>COUNTIF(D37:D48,"&lt;0")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E50" s="31">
         <f>COUNTIF(E37:E48,"&lt;0")</f>
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3019,23 +3028,23 @@
       </c>
       <c r="C6" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F6,月別目標と営業利益!F6)</f>
-        <v>1450000</v>
+        <v>1800000</v>
       </c>
       <c r="D6" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G6,月別目標と営業利益!G6)</f>
-        <v>1500000</v>
+        <v>1900000</v>
       </c>
       <c r="E6" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D6,月別目標と営業利益!D6)</f>
-        <v>4200000</v>
+        <v>5300000</v>
       </c>
       <c r="F6" s="8">
         <f t="shared" ref="F6:F17" si="0">ROUND(C6/B6,-3)</f>
-        <v>47000</v>
+        <v>58000</v>
       </c>
       <c r="G6" s="8">
         <f t="shared" ref="G6:G17" si="1">ROUND(E6/B6,-3)</f>
-        <v>135000</v>
+        <v>171000</v>
       </c>
       <c r="H6" s="8">
         <f>入力!$B$14</f>
@@ -3055,23 +3064,23 @@
       </c>
       <c r="C7" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F7,月別目標と営業利益!F7)</f>
-        <v>1700000</v>
+        <v>1800000</v>
       </c>
       <c r="D7" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G7,月別目標と営業利益!G7)</f>
-        <v>1800000</v>
+        <v>1900000</v>
       </c>
       <c r="E7" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D7,月別目標と営業利益!D7)</f>
-        <v>5000000</v>
+        <v>5300000</v>
       </c>
       <c r="F7" s="8">
         <f t="shared" si="0"/>
-        <v>57000</v>
+        <v>60000</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="1"/>
-        <v>167000</v>
+        <v>177000</v>
       </c>
       <c r="H7" s="8">
         <f>入力!$B$14</f>
@@ -3091,23 +3100,23 @@
       </c>
       <c r="C8" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F8,月別目標と営業利益!F8)</f>
-        <v>1850000</v>
+        <v>1900000</v>
       </c>
       <c r="D8" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G8,月別目標と営業利益!G8)</f>
-        <v>1950000</v>
+        <v>2000000</v>
       </c>
       <c r="E8" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D8,月別目標と営業利益!D8)</f>
-        <v>5400000</v>
+        <v>5500000</v>
       </c>
       <c r="F8" s="8">
         <f t="shared" si="0"/>
-        <v>60000</v>
+        <v>61000</v>
       </c>
       <c r="G8" s="8">
         <f t="shared" si="1"/>
-        <v>174000</v>
+        <v>177000</v>
       </c>
       <c r="H8" s="8">
         <f>入力!$B$14</f>
@@ -3135,7 +3144,7 @@
       </c>
       <c r="E9" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D9,月別目標と営業利益!D9)</f>
-        <v>5600000</v>
+        <v>5500000</v>
       </c>
       <c r="F9" s="8">
         <f t="shared" si="0"/>
@@ -3143,7 +3152,7 @@
       </c>
       <c r="G9" s="8">
         <f t="shared" si="1"/>
-        <v>187000</v>
+        <v>183000</v>
       </c>
       <c r="H9" s="8">
         <f>入力!$B$14</f>
@@ -3163,23 +3172,23 @@
       </c>
       <c r="C10" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F10,月別目標と営業利益!F10)</f>
-        <v>2550000</v>
+        <v>2400000</v>
       </c>
       <c r="D10" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G10,月別目標と営業利益!G10)</f>
-        <v>2700000</v>
+        <v>2500000</v>
       </c>
       <c r="E10" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D10,月別目標と営業利益!D10)</f>
-        <v>7500000</v>
+        <v>7000000</v>
       </c>
       <c r="F10" s="8">
         <f t="shared" si="0"/>
-        <v>82000</v>
+        <v>77000</v>
       </c>
       <c r="G10" s="8">
         <f t="shared" si="1"/>
-        <v>242000</v>
+        <v>226000</v>
       </c>
       <c r="H10" s="8">
         <f>入力!$B$14</f>
@@ -3199,23 +3208,23 @@
       </c>
       <c r="C11" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F11,月別目標と営業利益!F11)</f>
-        <v>1800000</v>
+        <v>2050000</v>
       </c>
       <c r="D11" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G11,月別目標と営業利益!G11)</f>
-        <v>1900000</v>
+        <v>2150000</v>
       </c>
       <c r="E11" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D11,月別目標と営業利益!D11)</f>
-        <v>5300000</v>
+        <v>6000000</v>
       </c>
       <c r="F11" s="8">
         <f t="shared" si="0"/>
-        <v>58000</v>
+        <v>66000</v>
       </c>
       <c r="G11" s="8">
         <f t="shared" si="1"/>
-        <v>171000</v>
+        <v>194000</v>
       </c>
       <c r="H11" s="8">
         <f>入力!$B$14</f>
@@ -3235,23 +3244,23 @@
       </c>
       <c r="C12" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F12,月別目標と営業利益!F12)</f>
-        <v>1350000</v>
+        <v>1800000</v>
       </c>
       <c r="D12" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G12,月別目標と営業利益!G12)</f>
-        <v>1400000</v>
+        <v>1900000</v>
       </c>
       <c r="E12" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D12,月別目標と営業利益!D12)</f>
-        <v>3900000</v>
+        <v>5300000</v>
       </c>
       <c r="F12" s="8">
         <f t="shared" si="0"/>
-        <v>48000</v>
+        <v>64000</v>
       </c>
       <c r="G12" s="8">
         <f t="shared" si="1"/>
-        <v>139000</v>
+        <v>189000</v>
       </c>
       <c r="H12" s="8">
         <f>入力!$B$14</f>
@@ -3271,23 +3280,23 @@
       </c>
       <c r="C13" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F13,月別目標と営業利益!F13)</f>
-        <v>1800000</v>
+        <v>1900000</v>
       </c>
       <c r="D13" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G13,月別目標と営業利益!G13)</f>
-        <v>1900000</v>
+        <v>2000000</v>
       </c>
       <c r="E13" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D13,月別目標と営業利益!D13)</f>
-        <v>5300000</v>
+        <v>5500000</v>
       </c>
       <c r="F13" s="8">
         <f t="shared" si="0"/>
-        <v>58000</v>
+        <v>61000</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="1"/>
-        <v>171000</v>
+        <v>177000</v>
       </c>
       <c r="H13" s="8">
         <f>入力!$B$14</f>
@@ -3307,23 +3316,23 @@
       </c>
       <c r="C14" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F14,月別目標と営業利益!F14)</f>
-        <v>1700000</v>
+        <v>1800000</v>
       </c>
       <c r="D14" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G14,月別目標と営業利益!G14)</f>
-        <v>1800000</v>
+        <v>1900000</v>
       </c>
       <c r="E14" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D14,月別目標と営業利益!D14)</f>
-        <v>5000000</v>
+        <v>5300000</v>
       </c>
       <c r="F14" s="8">
         <f t="shared" si="0"/>
-        <v>57000</v>
+        <v>60000</v>
       </c>
       <c r="G14" s="8">
         <f t="shared" si="1"/>
-        <v>167000</v>
+        <v>177000</v>
       </c>
       <c r="H14" s="8">
         <f>入力!$B$14</f>
@@ -3379,23 +3388,23 @@
       </c>
       <c r="C16" s="7">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!F16,月別目標と営業利益!F16)</f>
-        <v>1800000</v>
+        <v>1900000</v>
       </c>
       <c r="D16" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!G16,月別目標と営業利益!G16)</f>
-        <v>1900000</v>
+        <v>2000000</v>
       </c>
       <c r="E16" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D16,月別目標と営業利益!D16)</f>
-        <v>5300000</v>
+        <v>5500000</v>
       </c>
       <c r="F16" s="8">
         <f t="shared" si="0"/>
-        <v>60000</v>
+        <v>63000</v>
       </c>
       <c r="G16" s="8">
         <f t="shared" si="1"/>
-        <v>177000</v>
+        <v>183000</v>
       </c>
       <c r="H16" s="8">
         <f>入力!$B$14</f>
@@ -3423,7 +3432,7 @@
       </c>
       <c r="E17" s="8">
         <f>CHOOSE($B$3,'月別（スマレジ版）'!D17,月別目標と営業利益!D17)</f>
-        <v>5200000</v>
+        <v>5300000</v>
       </c>
       <c r="F17" s="8">
         <f t="shared" si="0"/>
@@ -3431,7 +3440,7 @@
       </c>
       <c r="G17" s="8">
         <f t="shared" si="1"/>
-        <v>168000</v>
+        <v>171000</v>
       </c>
       <c r="H17" s="8">
         <f>入力!$B$14</f>
@@ -3452,15 +3461,15 @@
       </c>
       <c r="C18" s="10">
         <f>SUM(C6:C17)</f>
-        <v>21500000</v>
+        <v>22850000</v>
       </c>
       <c r="D18" s="10">
         <f>SUM(D6:D17)</f>
-        <v>22650000</v>
+        <v>24050000</v>
       </c>
       <c r="E18" s="10">
         <f>SUM(E6:E17)</f>
-        <v>63000000</v>
+        <v>66800000</v>
       </c>
       <c r="H18" s="10">
         <f>SUM(H6:H17)</f>
@@ -3473,15 +3482,15 @@
     </row>
     <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>26</v>
+        <v>164</v>
       </c>
       <c r="C19" s="8">
         <f>C18-入力!B5</f>
-        <v>0</v>
+        <v>1350000</v>
       </c>
       <c r="E19" s="8">
         <f>E18-入力!B19</f>
-        <v>0</v>
+        <v>3800000</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.3">
@@ -3600,7 +3609,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
@@ -3627,7 +3636,7 @@
         <v>21500000</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.3">
@@ -3765,7 +3774,7 @@
         <v>63000000</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" x14ac:dyDescent="0.3">
@@ -4424,7 +4433,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.3">
@@ -5066,17 +5075,17 @@
   <sheetData>
     <row r="1" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>110</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -5084,7 +5093,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>101</v>
@@ -5108,7 +5117,7 @@
         <v>106</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>107</v>
@@ -5132,30 +5141,30 @@
         <v>5.8333333333333334E-2</v>
       </c>
       <c r="D6" s="12">
-        <v>4200000</v>
+        <v>5300000</v>
       </c>
       <c r="E6" s="8">
         <f>ROUND(入力!$B$5*C6,-3)</f>
         <v>1254000</v>
       </c>
       <c r="F6" s="12">
-        <v>1450000</v>
+        <v>1800000</v>
       </c>
       <c r="G6" s="8">
         <f>ROUND(F6*入力!$B$16/50000,0)*50000</f>
-        <v>1500000</v>
+        <v>1900000</v>
       </c>
       <c r="H6" s="8">
         <f>F6-D6*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>-250192</v>
+        <v>23688</v>
       </c>
       <c r="I6" s="8">
         <f>SUM($H$6:H6)</f>
-        <v>-250192</v>
+        <v>23688</v>
       </c>
       <c r="J6" s="8">
         <f>F6-月別目標と営業利益!F6</f>
-        <v>250000</v>
+        <v>600000</v>
       </c>
       <c r="K6" s="12"/>
       <c r="L6" s="11" t="str">
@@ -5179,30 +5188,30 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D7" s="12">
-        <v>5000000</v>
+        <v>5300000</v>
       </c>
       <c r="E7" s="8">
         <f>ROUND(入力!$B$5*C7,-3)</f>
         <v>1613000</v>
       </c>
       <c r="F7" s="12">
-        <v>1700000</v>
+        <v>1800000</v>
       </c>
       <c r="G7" s="8">
         <f>ROUND(F7*入力!$B$16/50000,0)*50000</f>
-        <v>1800000</v>
+        <v>1900000</v>
       </c>
       <c r="H7" s="8">
         <f>F7-D7*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>-55552</v>
+        <v>23688</v>
       </c>
       <c r="I7" s="8">
         <f>SUM($H$6:H7)</f>
-        <v>-305744</v>
+        <v>47376</v>
       </c>
       <c r="J7" s="8">
         <f>F7-月別目標と営業利益!F7</f>
-        <v>250000</v>
+        <v>350000</v>
       </c>
       <c r="K7" s="12"/>
       <c r="L7" s="11" t="str">
@@ -5226,30 +5235,30 @@
         <v>9.166666666666666E-2</v>
       </c>
       <c r="D8" s="12">
-        <v>5400000</v>
+        <v>5500000</v>
       </c>
       <c r="E8" s="8">
         <f>ROUND(入力!$B$5*C8,-3)</f>
         <v>1971000</v>
       </c>
       <c r="F8" s="12">
-        <v>1850000</v>
+        <v>1900000</v>
       </c>
       <c r="G8" s="8">
         <f>ROUND(F8*入力!$B$16/50000,0)*50000</f>
-        <v>1950000</v>
+        <v>2000000</v>
       </c>
       <c r="H8" s="8">
         <f>F8-D8*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>66768</v>
+        <v>109848</v>
       </c>
       <c r="I8" s="8">
         <f>SUM($H$6:H8)</f>
-        <v>-238976</v>
+        <v>157224</v>
       </c>
       <c r="J8" s="8">
         <f>F8-月別目標と営業利益!F8</f>
-        <v>-150000</v>
+        <v>-100000</v>
       </c>
       <c r="K8" s="12"/>
       <c r="L8" s="11" t="str">
@@ -5273,7 +5282,7 @@
         <v>9.166666666666666E-2</v>
       </c>
       <c r="D9" s="12">
-        <v>5600000</v>
+        <v>5500000</v>
       </c>
       <c r="E9" s="8">
         <f>ROUND(入力!$B$5*C9,-3)</f>
@@ -5288,11 +5297,11 @@
       </c>
       <c r="H9" s="8">
         <f>F9-D9*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>102928</v>
+        <v>109848</v>
       </c>
       <c r="I9" s="8">
         <f>SUM($H$6:H9)</f>
-        <v>-136048</v>
+        <v>267072</v>
       </c>
       <c r="J9" s="8">
         <f>F9-月別目標と営業利益!F9</f>
@@ -5320,30 +5329,30 @@
         <v>0.11666666666666667</v>
       </c>
       <c r="D10" s="12">
-        <v>7500000</v>
+        <v>7000000</v>
       </c>
       <c r="E10" s="8">
         <f>ROUND(入力!$B$5*C10,-3)</f>
         <v>2508000</v>
       </c>
       <c r="F10" s="12">
-        <v>2550000</v>
+        <v>2400000</v>
       </c>
       <c r="G10" s="8">
         <f>ROUND(F10*入力!$B$16/50000,0)*50000</f>
-        <v>2700000</v>
+        <v>2500000</v>
       </c>
       <c r="H10" s="8">
         <f>F10-D10*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>621448</v>
+        <v>506048</v>
       </c>
       <c r="I10" s="8">
         <f>SUM($H$6:H10)</f>
-        <v>485400</v>
+        <v>773120</v>
       </c>
       <c r="J10" s="8">
         <f>F10-月別目標と営業利益!F10</f>
-        <v>-200000</v>
+        <v>-350000</v>
       </c>
       <c r="K10" s="12"/>
       <c r="L10" s="11" t="str">
@@ -5367,30 +5376,30 @@
         <v>0.1</v>
       </c>
       <c r="D11" s="12">
-        <v>5300000</v>
+        <v>6000000</v>
       </c>
       <c r="E11" s="8">
         <f>ROUND(入力!$B$5*C11,-3)</f>
         <v>2150000</v>
       </c>
       <c r="F11" s="12">
-        <v>1800000</v>
+        <v>2050000</v>
       </c>
       <c r="G11" s="8">
         <f>ROUND(F11*入力!$B$16/50000,0)*50000</f>
-        <v>1900000</v>
+        <v>2150000</v>
       </c>
       <c r="H11" s="8">
         <f>F11-D11*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>23688</v>
+        <v>225248</v>
       </c>
       <c r="I11" s="8">
         <f>SUM($H$6:H11)</f>
-        <v>509088</v>
+        <v>998368</v>
       </c>
       <c r="J11" s="8">
         <f>F11-月別目標と営業利益!F11</f>
-        <v>-150000</v>
+        <v>100000</v>
       </c>
       <c r="K11" s="12"/>
       <c r="L11" s="11" t="str">
@@ -5414,30 +5423,30 @@
         <v>5.8333333333333334E-2</v>
       </c>
       <c r="D12" s="12">
-        <v>3900000</v>
+        <v>5300000</v>
       </c>
       <c r="E12" s="8">
         <f>ROUND(入力!$B$5*C12,-3)</f>
         <v>1254000</v>
       </c>
       <c r="F12" s="12">
-        <v>1350000</v>
+        <v>1800000</v>
       </c>
       <c r="G12" s="8">
         <f>ROUND(F12*入力!$B$16/50000,0)*50000</f>
-        <v>1400000</v>
+        <v>1900000</v>
       </c>
       <c r="H12" s="8">
         <f>F12-D12*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>-329432</v>
+        <v>23688</v>
       </c>
       <c r="I12" s="8">
         <f>SUM($H$6:H12)</f>
-        <v>179656</v>
+        <v>1022056</v>
       </c>
       <c r="J12" s="8">
         <f>F12-月別目標と営業利益!F12</f>
-        <v>250000</v>
+        <v>700000</v>
       </c>
       <c r="K12" s="12"/>
       <c r="L12" s="11" t="str">
@@ -5461,30 +5470,30 @@
         <v>9.166666666666666E-2</v>
       </c>
       <c r="D13" s="12">
-        <v>5300000</v>
+        <v>5500000</v>
       </c>
       <c r="E13" s="8">
         <f>ROUND(入力!$B$5*C13,-3)</f>
         <v>1971000</v>
       </c>
       <c r="F13" s="12">
-        <v>1800000</v>
+        <v>1900000</v>
       </c>
       <c r="G13" s="8">
         <f>ROUND(F13*入力!$B$16/50000,0)*50000</f>
-        <v>1900000</v>
+        <v>2000000</v>
       </c>
       <c r="H13" s="8">
         <f>F13-D13*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>23688</v>
+        <v>109848</v>
       </c>
       <c r="I13" s="8">
         <f>SUM($H$6:H13)</f>
-        <v>203344</v>
+        <v>1131904</v>
       </c>
       <c r="J13" s="8">
         <f>F13-月別目標と営業利益!F13</f>
-        <v>50000</v>
+        <v>150000</v>
       </c>
       <c r="K13" s="12"/>
       <c r="L13" s="11" t="str">
@@ -5508,30 +5517,30 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D14" s="12">
-        <v>5000000</v>
+        <v>5300000</v>
       </c>
       <c r="E14" s="8">
         <f>ROUND(入力!$B$5*C14,-3)</f>
         <v>1613000</v>
       </c>
       <c r="F14" s="12">
-        <v>1700000</v>
+        <v>1800000</v>
       </c>
       <c r="G14" s="8">
         <f>ROUND(F14*入力!$B$16/50000,0)*50000</f>
-        <v>1800000</v>
+        <v>1900000</v>
       </c>
       <c r="H14" s="8">
         <f>F14-D14*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>-55552</v>
+        <v>23688</v>
       </c>
       <c r="I14" s="8">
         <f>SUM($H$6:H14)</f>
-        <v>147792</v>
+        <v>1155592</v>
       </c>
       <c r="J14" s="8">
         <f>F14-月別目標と営業利益!F14</f>
-        <v>250000</v>
+        <v>350000</v>
       </c>
       <c r="K14" s="12"/>
       <c r="L14" s="11" t="str">
@@ -5574,7 +5583,7 @@
       </c>
       <c r="I15" s="8">
         <f>SUM($H$6:H15)</f>
-        <v>171480</v>
+        <v>1179280</v>
       </c>
       <c r="J15" s="8">
         <f>F15-月別目標と営業利益!F15</f>
@@ -5602,30 +5611,30 @@
         <v>9.166666666666666E-2</v>
       </c>
       <c r="D16" s="12">
-        <v>5300000</v>
+        <v>5500000</v>
       </c>
       <c r="E16" s="8">
         <f>ROUND(入力!$B$5*C16,-3)</f>
         <v>1971000</v>
       </c>
       <c r="F16" s="12">
-        <v>1800000</v>
+        <v>1900000</v>
       </c>
       <c r="G16" s="8">
         <f>ROUND(F16*入力!$B$16/50000,0)*50000</f>
-        <v>1900000</v>
+        <v>2000000</v>
       </c>
       <c r="H16" s="8">
         <f>F16-D16*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>23688</v>
+        <v>109848</v>
       </c>
       <c r="I16" s="8">
         <f>SUM($H$6:H16)</f>
-        <v>195168</v>
+        <v>1289128</v>
       </c>
       <c r="J16" s="8">
         <f>F16-月別目標と営業利益!F16</f>
-        <v>-150000</v>
+        <v>-50000</v>
       </c>
       <c r="K16" s="12"/>
       <c r="L16" s="11" t="str">
@@ -5649,7 +5658,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="D17" s="12">
-        <v>5200000</v>
+        <v>5300000</v>
       </c>
       <c r="E17" s="8">
         <f>ROUND(入力!$B$5*C17,-3)</f>
@@ -5664,11 +5673,11 @@
       </c>
       <c r="H17" s="8">
         <f>F17-D17*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>30608</v>
+        <v>23688</v>
       </c>
       <c r="I17" s="8">
         <f>SUM($H$6:H17)</f>
-        <v>225776</v>
+        <v>1312816</v>
       </c>
       <c r="J17" s="8">
         <f>F17-月別目標と営業利益!F17</f>
@@ -5694,7 +5703,7 @@
       </c>
       <c r="D18" s="10">
         <f>SUM(D6:D17)</f>
-        <v>63000000</v>
+        <v>66800000</v>
       </c>
       <c r="E18" s="10">
         <f>SUM(E6:E17)</f>
@@ -5702,15 +5711,15 @@
       </c>
       <c r="F18" s="10">
         <f>SUM(F6:F17)</f>
-        <v>21500000</v>
+        <v>22850000</v>
       </c>
       <c r="G18" s="10">
         <f>SUM(G6:G17)</f>
-        <v>22650000</v>
+        <v>24050000</v>
       </c>
       <c r="H18" s="10">
         <f>SUM(H6:H17)</f>
-        <v>225776</v>
+        <v>1312816</v>
       </c>
       <c r="K18" s="10">
         <f>SUM(K6:K17)</f>
@@ -5723,20 +5732,20 @@
     </row>
     <row r="19" spans="1:13" ht="15" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>26</v>
+        <v>164</v>
       </c>
       <c r="D19" s="8">
         <f>D18-入力!B19</f>
-        <v>0</v>
+        <v>3800000</v>
       </c>
       <c r="F19" s="8">
         <f>F18-入力!B5</f>
-        <v>0</v>
+        <v>1350000</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>109</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -5758,12 +5767,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -5774,18 +5783,18 @@
         <v>29</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B5" s="4">
         <v>1</v>
@@ -5803,7 +5812,7 @@
     </row>
     <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B6" s="4">
         <v>1</v>
@@ -5821,7 +5830,7 @@
     </row>
     <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B7" s="4">
         <v>2</v>
@@ -5839,7 +5848,7 @@
     </row>
     <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B8" s="9">
         <f>SUM(B5:B7)</f>
@@ -5856,7 +5865,7 @@
     </row>
     <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D9" s="10">
         <f>D8*12</f>
@@ -5869,12 +5878,12 @@
     </row>
     <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" x14ac:dyDescent="0.3">

--- a/excel/Weekends_予算と報奨金案_粗利2150万円.xlsx
+++ b/excel/Weekends_予算と報奨金案_粗利2150万円.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yataka-02\AppData\Local\Temp\claude\C--Users-yataka-02-Desktop-Claude\76fa42a7-01fc-42d8-86c7-11cf90447c56\scratchpad\margin-calculator\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF397974-1E34-4FE5-9D9D-CFC2F24D1D57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E180A3-A5EA-4934-AF8F-43848D48AB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,27 +184,15 @@
     <t>テナント経費の固定分（月）</t>
   </si>
   <si>
-    <t>売上歩合制。前年12か月の回帰の切片</t>
-  </si>
-  <si>
     <t>テナント経費の売上連動率</t>
   </si>
   <si>
-    <t>同上の傾き（決定係数0.94）</t>
-  </si>
-  <si>
     <t>その他の店舗経費（年）</t>
   </si>
   <si>
-    <t>管理諸費・減価償却・旅費など。前年実績（発展会計 営業部）</t>
-  </si>
-  <si>
     <t>共通部の実費（年）</t>
   </si>
   <si>
-    <t>主に租税公課。前年実績</t>
-  </si>
-  <si>
     <t>本部費（月）</t>
   </si>
   <si>
@@ -292,9 +280,6 @@
     <t>テナント経費</t>
   </si>
   <si>
-    <t>固定分＋売上×連動率</t>
-  </si>
-  <si>
     <t>その他の店舗経費</t>
   </si>
   <si>
@@ -416,9 +401,6 @@
   </si>
   <si>
     <t>共通部の実費を入れた場合・入れない場合の損益比較</t>
-  </si>
-  <si>
-    <t>共通部の実費＝発展会計の共通部（主に租税公課、年943,852円・前年実績）。「なし」は店舗だけの損益、「あり」は現在の計画、「本部費込み」は共通部の実費の代わりに管理会計の本部費（月15.8万円）を負担した場合（参考）。金額はすべて税抜・円。</t>
   </si>
   <si>
     <t>※租税公課の中身（消費税の納付かどうか）は未確認。確認結果で「入力」シートB11を直すと、この表も自動で変わる。</t>
@@ -553,6 +535,30 @@
   </si>
   <si>
     <t>（月の目標の合計が年間予算をどれだけ上回るか。プラスなら、月の目標がいくつか未達でも年間予算に届く余裕がある）</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>売上歩合制。前年12か月の回帰の切片209,792円を月21万円に丸め（2026-10-07）</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>同上の傾き（決定係数0.94）。歩合の金額は月ごと（年間の表は年額）に1万円単位で丸める</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>月29万円×12。前年実績3,493,268円（発展会計 営業部：管理諸費・減価償却・旅費など）を丸め</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>月8万円×12。前年実績943,852円（主に租税公課）を丸め</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>固定分（月21万円）＋売上×連動率（1万円単位に丸め）</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>共通部の実費＝発展会計の共通部（主に租税公課、予算は月8万円・年96万円、前年実績943,852円を丸め）。「なし」は店舗だけの損益、「あり」は現在の計画、「本部費込み」は共通部の実費の代わりに管理会計の本部費（月15.8万円）を負担した場合（参考）。金額はすべて税抜・円。</t>
     <phoneticPr fontId="9"/>
   </si>
 </sst>
@@ -834,22 +840,22 @@
                 <c:formatCode>#,##0;[Red]\-#,##0;\-</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>-1128264</c:v>
+                  <c:v>-1130000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-271244</c:v>
+                  <c:v>-275000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>225776</c:v>
+                  <c:v>220000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>739988</c:v>
+                  <c:v>735000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>842796</c:v>
+                  <c:v>835000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1699816.0000000037</c:v>
+                  <c:v>1690000.0000000037</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1038,40 +1044,40 @@
                 <c:formatCode>#,##0;[Red]\-#,##0;\-</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>-458672</c:v>
+                  <c:v>-460000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-257112</c:v>
+                  <c:v>-260000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>189088</c:v>
+                  <c:v>190000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>225248</c:v>
+                  <c:v>220000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>786848</c:v>
+                  <c:v>790000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>146008</c:v>
+                  <c:v>150000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-537912</c:v>
+                  <c:v>-540000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-19392</c:v>
+                  <c:v>-20000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-250192</c:v>
+                  <c:v>-250000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>152928</c:v>
+                  <c:v>150000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>146008</c:v>
+                  <c:v>150000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>102928</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1126,40 +1132,40 @@
                 <c:formatCode>#,##0;[Red]\-#,##0;\-</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>-458672</c:v>
+                  <c:v>-460000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-715784</c:v>
+                  <c:v>-720000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-526696</c:v>
+                  <c:v>-530000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-301448</c:v>
+                  <c:v>-310000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>485400</c:v>
+                  <c:v>480000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>631408</c:v>
+                  <c:v>630000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>93496</c:v>
+                  <c:v>90000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>74104</c:v>
+                  <c:v>70000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-176088</c:v>
+                  <c:v>-180000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-23160</c:v>
+                  <c:v>-30000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>122848</c:v>
+                  <c:v>120000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>225776</c:v>
+                  <c:v>220000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1337,40 +1343,40 @@
                 <c:formatCode>#,##0;[Red]\-#,##0;\-</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>23688</c:v>
+                  <c:v>20000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>23688</c:v>
+                  <c:v>20000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>109848</c:v>
+                  <c:v>110000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>109848</c:v>
+                  <c:v>110000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>506048</c:v>
+                  <c:v>510000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>225248</c:v>
+                  <c:v>220000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>23688</c:v>
+                  <c:v>20000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>109848</c:v>
+                  <c:v>110000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>23688</c:v>
+                  <c:v>20000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>23688</c:v>
+                  <c:v>20000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>109848</c:v>
+                  <c:v>110000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>23688</c:v>
+                  <c:v>20000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1425,40 +1431,40 @@
                 <c:formatCode>#,##0;[Red]\-#,##0;\-</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>23688</c:v>
+                  <c:v>20000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>47376</c:v>
+                  <c:v>40000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>157224</c:v>
+                  <c:v>150000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>267072</c:v>
+                  <c:v>260000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>773120</c:v>
+                  <c:v>770000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>998368</c:v>
+                  <c:v>990000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1022056</c:v>
+                  <c:v>1010000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1131904</c:v>
+                  <c:v>1120000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1155592</c:v>
+                  <c:v>1140000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1179280</c:v>
+                  <c:v>1160000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1289128</c:v>
+                  <c:v>1270000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1312816</c:v>
+                  <c:v>1290000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1938,22 +1944,22 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
-        <v>125</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="21" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1961,30 +1967,30 @@
         <v>38</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B7" s="23">
         <f>1</f>
@@ -2013,7 +2019,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B8" s="24">
         <f>入力!$B$19*B7</f>
@@ -2040,12 +2046,12 @@
         <v>66150000</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B9" s="24">
         <f>入力!$B$5*B7</f>
@@ -2072,12 +2078,12 @@
         <v>22575000</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B10" s="24">
         <f>入力!$B$7*12</f>
@@ -2104,12 +2110,12 @@
         <v>9600000</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B11" s="24">
         <f>IF(B7&gt;=入力!$B$16,入力!$B$15,IF(B7&gt;=1,入力!$B$14,0))*12</f>
@@ -2136,144 +2142,144 @@
         <v>600000</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B12" s="24">
-        <f>入力!$B$8*12+B8*入力!$B$9</f>
-        <v>6877104</v>
+        <f>入力!$B$8*12+ROUND(B8*入力!$B$9,-4)</f>
+        <v>6880000</v>
       </c>
       <c r="C12" s="24">
-        <f>入力!$B$8*12+C8*入力!$B$9</f>
-        <v>6877104</v>
+        <f>入力!$B$8*12+ROUND(C8*入力!$B$9,-4)</f>
+        <v>6880000</v>
       </c>
       <c r="D12" s="24">
-        <f>入力!$B$8*12+D8*入力!$B$9</f>
-        <v>6877104</v>
+        <f>入力!$B$8*12+ROUND(D8*入力!$B$9,-4)</f>
+        <v>6880000</v>
       </c>
       <c r="E12" s="24">
-        <f>入力!$B$8*12+E8*入力!$B$9</f>
-        <v>7095084</v>
+        <f>入力!$B$8*12+ROUND(E8*入力!$B$9,-4)</f>
+        <v>7100000</v>
       </c>
       <c r="F12" s="24">
-        <f>入力!$B$8*12+F8*入力!$B$9</f>
-        <v>7095084</v>
+        <f>入力!$B$8*12+ROUND(F8*入力!$B$9,-4)</f>
+        <v>7100000</v>
       </c>
       <c r="G12" s="24">
-        <f>入力!$B$8*12+G8*入力!$B$9</f>
-        <v>7095084</v>
+        <f>入力!$B$8*12+ROUND(G8*入力!$B$9,-4)</f>
+        <v>7100000</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B13" s="24">
         <f>入力!$B$10</f>
-        <v>3493268</v>
+        <v>3480000</v>
       </c>
       <c r="C13" s="24">
         <f>入力!$B$10</f>
-        <v>3493268</v>
+        <v>3480000</v>
       </c>
       <c r="D13" s="24">
         <f>入力!$B$10</f>
-        <v>3493268</v>
+        <v>3480000</v>
       </c>
       <c r="E13" s="24">
         <f>入力!$B$10</f>
-        <v>3493268</v>
+        <v>3480000</v>
       </c>
       <c r="F13" s="24">
         <f>入力!$B$10</f>
-        <v>3493268</v>
+        <v>3480000</v>
       </c>
       <c r="G13" s="24">
         <f>入力!$B$10</f>
-        <v>3493268</v>
+        <v>3480000</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="26" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B14" s="27">
         <f t="shared" ref="B14:G14" si="0">SUM(B10:B13)</f>
-        <v>20330372</v>
+        <v>20320000</v>
       </c>
       <c r="C14" s="27">
         <f t="shared" si="0"/>
-        <v>20330372</v>
+        <v>20320000</v>
       </c>
       <c r="D14" s="27">
         <f t="shared" si="0"/>
-        <v>20330372</v>
+        <v>20320000</v>
       </c>
       <c r="E14" s="27">
         <f t="shared" si="0"/>
-        <v>20788352</v>
+        <v>20780000</v>
       </c>
       <c r="F14" s="27">
         <f t="shared" si="0"/>
-        <v>20788352</v>
+        <v>20780000</v>
       </c>
       <c r="G14" s="27">
         <f t="shared" si="0"/>
-        <v>20788352</v>
+        <v>20780000</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="26" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B15" s="27">
         <f t="shared" ref="B15:G15" si="1">B9-B14</f>
-        <v>1169628</v>
+        <v>1180000</v>
       </c>
       <c r="C15" s="27">
         <f t="shared" si="1"/>
-        <v>1169628</v>
+        <v>1180000</v>
       </c>
       <c r="D15" s="27">
         <f t="shared" si="1"/>
-        <v>1169628</v>
+        <v>1180000</v>
       </c>
       <c r="E15" s="27">
         <f t="shared" si="1"/>
-        <v>1786648</v>
+        <v>1795000</v>
       </c>
       <c r="F15" s="27">
         <f t="shared" si="1"/>
-        <v>1786648</v>
+        <v>1795000</v>
       </c>
       <c r="G15" s="27">
         <f t="shared" si="1"/>
-        <v>1786648</v>
+        <v>1795000</v>
       </c>
       <c r="H15" s="26" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B16" s="24">
         <v>0</v>
       </c>
       <c r="C16" s="24">
         <f>入力!$B$11</f>
-        <v>943852</v>
+        <v>960000</v>
       </c>
       <c r="D16" s="24">
         <v>0</v>
@@ -2283,18 +2289,18 @@
       </c>
       <c r="F16" s="24">
         <f>入力!$B$11</f>
-        <v>943852</v>
+        <v>960000</v>
       </c>
       <c r="G16" s="24">
         <v>0</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B17" s="24">
         <v>0</v>
@@ -2317,44 +2323,44 @@
         <v>1896000</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="26" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B18" s="27">
         <f t="shared" ref="B18:G18" si="2">B15-B16-B17</f>
-        <v>1169628</v>
+        <v>1180000</v>
       </c>
       <c r="C18" s="27">
         <f t="shared" si="2"/>
-        <v>225776</v>
+        <v>220000</v>
       </c>
       <c r="D18" s="27">
         <f t="shared" si="2"/>
-        <v>-726372</v>
+        <v>-716000</v>
       </c>
       <c r="E18" s="27">
         <f t="shared" si="2"/>
-        <v>1786648</v>
+        <v>1795000</v>
       </c>
       <c r="F18" s="27">
         <f t="shared" si="2"/>
-        <v>842796</v>
+        <v>835000</v>
       </c>
       <c r="G18" s="27">
         <f t="shared" si="2"/>
-        <v>-109352</v>
+        <v>-101000</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B19" s="24">
         <f>入力!$B$13</f>
@@ -2383,118 +2389,118 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="26" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B20" s="27">
         <f t="shared" ref="B20:G20" si="3">B18-B19</f>
-        <v>869628</v>
+        <v>880000</v>
       </c>
       <c r="C20" s="27">
         <f t="shared" si="3"/>
-        <v>-74224</v>
+        <v>-80000</v>
       </c>
       <c r="D20" s="27">
         <f t="shared" si="3"/>
-        <v>-1026372</v>
+        <v>-1016000</v>
       </c>
       <c r="E20" s="27">
         <f t="shared" si="3"/>
-        <v>1486648</v>
+        <v>1495000</v>
       </c>
       <c r="F20" s="27">
         <f t="shared" si="3"/>
-        <v>542796</v>
+        <v>535000</v>
       </c>
       <c r="G20" s="27">
         <f t="shared" si="3"/>
-        <v>-409352</v>
+        <v>-401000</v>
       </c>
       <c r="H20" s="26"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B21" s="24">
         <f>(入力!$B$7*12+入力!$B$8*12+入力!$B$10+B16+B17)/入力!$B$21</f>
-        <v>57377811.25294625</v>
+        <v>57338218.477981836</v>
       </c>
       <c r="C21" s="24">
         <f>(入力!$B$7*12+入力!$B$8*12+入力!$B$10+C16+C17)/入力!$B$21</f>
-        <v>60846964.598259076</v>
+        <v>60866724.230473027</v>
       </c>
       <c r="D21" s="24">
         <f>(入力!$B$7*12+入力!$B$8*12+入力!$B$10+D16+D17)/入力!$B$21</f>
-        <v>64346610.114116348</v>
+        <v>64307017.339151941</v>
       </c>
       <c r="E21" s="24">
         <f>(入力!$B$7*12+入力!$B$8*12+入力!$B$10+E16+E17)/入力!$B$21</f>
-        <v>57377811.25294625</v>
+        <v>57338218.477981836</v>
       </c>
       <c r="F21" s="24">
         <f>(入力!$B$7*12+入力!$B$8*12+入力!$B$10+F16+F17)/入力!$B$21</f>
-        <v>60846964.598259076</v>
+        <v>60866724.230473027</v>
       </c>
       <c r="G21" s="24">
         <f>(入力!$B$7*12+入力!$B$8*12+入力!$B$10+G16+G17)/入力!$B$21</f>
-        <v>64346610.114116348</v>
+        <v>64307017.339151941</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B22" s="25">
         <f>B21/入力!$B$19</f>
-        <v>0.91075890877692456</v>
+        <v>0.9101304520314577</v>
       </c>
       <c r="C22" s="25">
         <f>C21/入力!$B$19</f>
-        <v>0.96582483489300119</v>
+        <v>0.96613847984877821</v>
       </c>
       <c r="D22" s="25">
         <f>D21/入力!$B$19</f>
-        <v>1.0213747637161326</v>
+        <v>1.0207463069706657</v>
       </c>
       <c r="E22" s="25">
         <f>E21/入力!$B$19</f>
-        <v>0.91075890877692456</v>
+        <v>0.9101304520314577</v>
       </c>
       <c r="F22" s="25">
         <f>F21/入力!$B$19</f>
-        <v>0.96582483489300119</v>
+        <v>0.96613847984877821</v>
       </c>
       <c r="G22" s="25">
         <f>G21/入力!$B$19</f>
-        <v>1.0213747637161326</v>
+        <v>1.0207463069706657</v>
       </c>
       <c r="H22" s="19" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="21" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="30" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -2504,19 +2510,19 @@
       </c>
       <c r="B27" s="24">
         <f>C27+入力!$B$11</f>
-        <v>-184412</v>
+        <v>-170000</v>
       </c>
       <c r="C27" s="24">
         <f>達成度別!E4</f>
-        <v>-1128264</v>
+        <v>-1130000</v>
       </c>
       <c r="D27" s="24">
         <f>C27+入力!$B$11-入力!$B$12*12</f>
-        <v>-2080412</v>
+        <v>-2066000</v>
       </c>
       <c r="E27" s="24">
         <f t="shared" ref="E27:E32" si="4">B27-C27</f>
-        <v>943852</v>
+        <v>960000</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
@@ -2526,19 +2532,19 @@
       </c>
       <c r="B28" s="24">
         <f>C28+入力!$B$11</f>
-        <v>672608</v>
+        <v>685000</v>
       </c>
       <c r="C28" s="24">
         <f>達成度別!E5</f>
-        <v>-271244</v>
+        <v>-275000</v>
       </c>
       <c r="D28" s="24">
         <f>C28+入力!$B$11-入力!$B$12*12</f>
-        <v>-1223392</v>
+        <v>-1211000</v>
       </c>
       <c r="E28" s="24">
         <f t="shared" si="4"/>
-        <v>943852</v>
+        <v>960000</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
@@ -2548,19 +2554,19 @@
       </c>
       <c r="B29" s="27">
         <f>C29+入力!$B$11</f>
-        <v>1169628</v>
+        <v>1180000</v>
       </c>
       <c r="C29" s="27">
         <f>達成度別!E6</f>
-        <v>225776</v>
+        <v>220000</v>
       </c>
       <c r="D29" s="27">
         <f>C29+入力!$B$11-入力!$B$12*12</f>
-        <v>-726372</v>
+        <v>-716000</v>
       </c>
       <c r="E29" s="27">
         <f t="shared" si="4"/>
-        <v>943852</v>
+        <v>960000</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
@@ -2570,19 +2576,19 @@
       </c>
       <c r="B30" s="24">
         <f>C30+入力!$B$11</f>
-        <v>1683840</v>
+        <v>1695000</v>
       </c>
       <c r="C30" s="24">
         <f>達成度別!E7</f>
-        <v>739988</v>
+        <v>735000</v>
       </c>
       <c r="D30" s="24">
         <f>C30+入力!$B$11-入力!$B$12*12</f>
-        <v>-212160</v>
+        <v>-201000</v>
       </c>
       <c r="E30" s="24">
         <f t="shared" si="4"/>
-        <v>943852</v>
+        <v>960000</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
@@ -2592,19 +2598,19 @@
       </c>
       <c r="B31" s="24">
         <f>C31+入力!$B$11</f>
-        <v>1786648</v>
+        <v>1795000</v>
       </c>
       <c r="C31" s="24">
         <f>達成度別!E8</f>
-        <v>842796</v>
+        <v>835000</v>
       </c>
       <c r="D31" s="24">
         <f>C31+入力!$B$11-入力!$B$12*12</f>
-        <v>-109352</v>
+        <v>-101000</v>
       </c>
       <c r="E31" s="24">
         <f t="shared" si="4"/>
-        <v>943852</v>
+        <v>960000</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
@@ -2614,24 +2620,24 @@
       </c>
       <c r="B32" s="24">
         <f>C32+入力!$B$11</f>
-        <v>2643668.0000000037</v>
+        <v>2650000.0000000037</v>
       </c>
       <c r="C32" s="24">
         <f>達成度別!E9</f>
-        <v>1699816.0000000037</v>
+        <v>1690000.0000000037</v>
       </c>
       <c r="D32" s="24">
         <f>C32+入力!$B$11-入力!$B$12*12</f>
-        <v>747668.00000000373</v>
+        <v>754000.00000000373</v>
       </c>
       <c r="E32" s="24">
         <f t="shared" si="4"/>
-        <v>943852</v>
+        <v>960000</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="21" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="30" x14ac:dyDescent="0.3">
@@ -2639,16 +2645,16 @@
         <v>4</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -2662,15 +2668,15 @@
       </c>
       <c r="C37" s="24">
         <f>D37+入力!$B$11/12</f>
-        <v>102342.33333333333</v>
+        <v>100000</v>
       </c>
       <c r="D37" s="24">
         <f>'月別（スマレジ版）'!H6</f>
-        <v>23688</v>
+        <v>20000</v>
       </c>
       <c r="E37" s="24">
         <f>D37+入力!$B$11/12-入力!$B$12</f>
-        <v>-55657.666666666672</v>
+        <v>-58000</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -2684,15 +2690,15 @@
       </c>
       <c r="C38" s="24">
         <f>D38+入力!$B$11/12</f>
-        <v>102342.33333333333</v>
+        <v>100000</v>
       </c>
       <c r="D38" s="24">
         <f>'月別（スマレジ版）'!H7</f>
-        <v>23688</v>
+        <v>20000</v>
       </c>
       <c r="E38" s="24">
         <f>D38+入力!$B$11/12-入力!$B$12</f>
-        <v>-55657.666666666672</v>
+        <v>-58000</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -2706,15 +2712,15 @@
       </c>
       <c r="C39" s="24">
         <f>D39+入力!$B$11/12</f>
-        <v>188502.33333333331</v>
+        <v>190000</v>
       </c>
       <c r="D39" s="24">
         <f>'月別（スマレジ版）'!H8</f>
-        <v>109848</v>
+        <v>110000</v>
       </c>
       <c r="E39" s="24">
         <f>D39+入力!$B$11/12-入力!$B$12</f>
-        <v>30502.333333333314</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -2728,15 +2734,15 @@
       </c>
       <c r="C40" s="24">
         <f>D40+入力!$B$11/12</f>
-        <v>188502.33333333331</v>
+        <v>190000</v>
       </c>
       <c r="D40" s="24">
         <f>'月別（スマレジ版）'!H9</f>
-        <v>109848</v>
+        <v>110000</v>
       </c>
       <c r="E40" s="24">
         <f>D40+入力!$B$11/12-入力!$B$12</f>
-        <v>30502.333333333314</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -2750,15 +2756,15 @@
       </c>
       <c r="C41" s="24">
         <f>D41+入力!$B$11/12</f>
-        <v>584702.33333333337</v>
+        <v>590000</v>
       </c>
       <c r="D41" s="24">
         <f>'月別（スマレジ版）'!H10</f>
-        <v>506048</v>
+        <v>510000</v>
       </c>
       <c r="E41" s="24">
         <f>D41+入力!$B$11/12-入力!$B$12</f>
-        <v>426702.33333333337</v>
+        <v>432000</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -2772,15 +2778,15 @@
       </c>
       <c r="C42" s="24">
         <f>D42+入力!$B$11/12</f>
-        <v>303902.33333333331</v>
+        <v>300000</v>
       </c>
       <c r="D42" s="24">
         <f>'月別（スマレジ版）'!H11</f>
-        <v>225248</v>
+        <v>220000</v>
       </c>
       <c r="E42" s="24">
         <f>D42+入力!$B$11/12-入力!$B$12</f>
-        <v>145902.33333333331</v>
+        <v>142000</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -2794,15 +2800,15 @@
       </c>
       <c r="C43" s="24">
         <f>D43+入力!$B$11/12</f>
-        <v>102342.33333333333</v>
+        <v>100000</v>
       </c>
       <c r="D43" s="24">
         <f>'月別（スマレジ版）'!H12</f>
-        <v>23688</v>
+        <v>20000</v>
       </c>
       <c r="E43" s="24">
         <f>D43+入力!$B$11/12-入力!$B$12</f>
-        <v>-55657.666666666672</v>
+        <v>-58000</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -2816,15 +2822,15 @@
       </c>
       <c r="C44" s="24">
         <f>D44+入力!$B$11/12</f>
-        <v>188502.33333333331</v>
+        <v>190000</v>
       </c>
       <c r="D44" s="24">
         <f>'月別（スマレジ版）'!H13</f>
-        <v>109848</v>
+        <v>110000</v>
       </c>
       <c r="E44" s="24">
         <f>D44+入力!$B$11/12-入力!$B$12</f>
-        <v>30502.333333333314</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -2838,15 +2844,15 @@
       </c>
       <c r="C45" s="24">
         <f>D45+入力!$B$11/12</f>
-        <v>102342.33333333333</v>
+        <v>100000</v>
       </c>
       <c r="D45" s="24">
         <f>'月別（スマレジ版）'!H14</f>
-        <v>23688</v>
+        <v>20000</v>
       </c>
       <c r="E45" s="24">
         <f>D45+入力!$B$11/12-入力!$B$12</f>
-        <v>-55657.666666666672</v>
+        <v>-58000</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -2860,15 +2866,15 @@
       </c>
       <c r="C46" s="24">
         <f>D46+入力!$B$11/12</f>
-        <v>102342.33333333333</v>
+        <v>100000</v>
       </c>
       <c r="D46" s="24">
         <f>'月別（スマレジ版）'!H15</f>
-        <v>23688</v>
+        <v>20000</v>
       </c>
       <c r="E46" s="24">
         <f>D46+入力!$B$11/12-入力!$B$12</f>
-        <v>-55657.666666666672</v>
+        <v>-58000</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -2882,15 +2888,15 @@
       </c>
       <c r="C47" s="24">
         <f>D47+入力!$B$11/12</f>
-        <v>188502.33333333331</v>
+        <v>190000</v>
       </c>
       <c r="D47" s="24">
         <f>'月別（スマレジ版）'!H16</f>
-        <v>109848</v>
+        <v>110000</v>
       </c>
       <c r="E47" s="24">
         <f>D47+入力!$B$11/12-入力!$B$12</f>
-        <v>30502.333333333314</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -2904,15 +2910,15 @@
       </c>
       <c r="C48" s="24">
         <f>D48+入力!$B$11/12</f>
-        <v>102342.33333333333</v>
+        <v>100000</v>
       </c>
       <c r="D48" s="24">
         <f>'月別（スマレジ版）'!H17</f>
-        <v>23688</v>
+        <v>20000</v>
       </c>
       <c r="E48" s="24">
         <f>D48+入力!$B$11/12-入力!$B$12</f>
-        <v>-55657.666666666672</v>
+        <v>-58000</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -2925,20 +2931,20 @@
       </c>
       <c r="C49" s="27">
         <f>SUM(C37:C48)</f>
-        <v>2256667.9999999995</v>
+        <v>2250000</v>
       </c>
       <c r="D49" s="27">
         <f>SUM(D37:D48)</f>
-        <v>1312816</v>
+        <v>1290000</v>
       </c>
       <c r="E49" s="27">
         <f>SUM(E37:E48)</f>
-        <v>360667.99999999983</v>
+        <v>354000</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="30" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C50" s="31">
         <f>COUNTIF(C37:C48,"&lt;0")</f>
@@ -3482,7 +3488,7 @@
     </row>
     <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C19" s="8">
         <f>C18-入力!B5</f>
@@ -3609,7 +3615,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
@@ -3636,7 +3642,7 @@
         <v>21500000</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.3">
@@ -3667,94 +3673,94 @@
         <v>46</v>
       </c>
       <c r="B8" s="14">
-        <v>209792</v>
+        <v>210000</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>47</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" s="13">
         <v>6.9199999999999998E-2</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>49</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B10" s="14">
-        <v>3493268</v>
+        <v>3480000</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>51</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B11" s="14">
-        <v>943852</v>
+        <v>960000</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>53</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B12" s="14">
         <v>158000</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B13" s="14">
         <v>300000</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B14" s="14">
         <f>'報奨金（例B）'!D8</f>
         <v>30000</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B15" s="14">
         <f>'報奨金（例B）'!E8</f>
         <v>50000</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B16" s="15">
         <v>1.05</v>
@@ -3763,51 +3769,51 @@
     </row>
     <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B19" s="12">
         <v>63000000</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B20" s="8">
         <f>B7*12+B8*12+B10+B11</f>
-        <v>16554624</v>
+        <v>16560000</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B21" s="16">
         <f>B6-B9</f>
         <v>0.27206984126984129</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B22" s="8">
         <f>B20/B21</f>
-        <v>60846964.598259076</v>
+        <v>60866724.230473027</v>
       </c>
       <c r="C22" s="2"/>
     </row>
@@ -3829,7 +3835,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="31.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -3837,18 +3843,18 @@
         <v>38</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B4" s="16">
         <v>1</v>
@@ -3861,7 +3867,7 @@
     </row>
     <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B5" s="8">
         <f>入力!$B$19*B4</f>
@@ -3872,12 +3878,12 @@
         <v>66150000</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B6" s="8">
         <f>入力!$B$5*B4</f>
@@ -3891,7 +3897,7 @@
     </row>
     <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B7" s="8">
         <f>入力!$B$7*12</f>
@@ -3902,12 +3908,12 @@
         <v>9600000</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B8" s="8">
         <f>入力!$B$14*12</f>
@@ -3918,84 +3924,84 @@
         <v>600000</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B9" s="8">
-        <f>入力!$B$8*12+B5*入力!$B$9</f>
-        <v>6877104</v>
+        <f>入力!$B$8*12+ROUND(B5*入力!$B$9,-4)</f>
+        <v>6880000</v>
       </c>
       <c r="C9" s="8">
-        <f>入力!$B$8*12+C5*入力!$B$9</f>
-        <v>7095084</v>
+        <f>入力!$B$8*12+ROUND(C5*入力!$B$9,-4)</f>
+        <v>7100000</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>83</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B10" s="8">
         <f>入力!$B$10</f>
-        <v>3493268</v>
+        <v>3480000</v>
       </c>
       <c r="C10" s="8">
         <f>入力!$B$10</f>
-        <v>3493268</v>
+        <v>3480000</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B11" s="8">
         <f>入力!$B$11</f>
-        <v>943852</v>
+        <v>960000</v>
       </c>
       <c r="C11" s="8">
         <f>入力!$B$11</f>
-        <v>943852</v>
+        <v>960000</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B12" s="8">
         <f>SUM(B7:B11)</f>
-        <v>21274224</v>
+        <v>21280000</v>
       </c>
       <c r="C12" s="8">
         <f>SUM(C7:C11)</f>
-        <v>21732204</v>
+        <v>21740000</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B13" s="7">
         <f>B6-B12</f>
-        <v>225776</v>
+        <v>220000</v>
       </c>
       <c r="C13" s="7">
         <f>C6-C12</f>
-        <v>842796</v>
+        <v>835000</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B14" s="8">
         <f>入力!$B$13</f>
@@ -4009,32 +4015,32 @@
     </row>
     <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B15" s="7">
         <f>B13-B14</f>
-        <v>-74224</v>
+        <v>-80000</v>
       </c>
       <c r="C15" s="7">
         <f>C13-C14</f>
-        <v>542796</v>
+        <v>535000</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B16" s="8">
         <f>B13+B11-入力!$B$12*12</f>
-        <v>-726372</v>
+        <v>-716000</v>
       </c>
       <c r="C16" s="8">
         <f>C13+C11-入力!$B$12*12</f>
-        <v>-109352</v>
+        <v>-101000</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -4056,27 +4062,27 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.3">
@@ -4096,12 +4102,12 @@
         <v>0</v>
       </c>
       <c r="E4" s="10">
-        <f>C4-B4*入力!$B$9-入力!$B$20-D4</f>
-        <v>-1128264</v>
+        <f>C4-ROUND(B4*入力!$B$9,-4)-入力!$B$20-D4</f>
+        <v>-1130000</v>
       </c>
       <c r="F4" s="8">
         <f>E4-入力!$B$13</f>
-        <v>-1428264</v>
+        <v>-1430000</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.3">
@@ -4121,12 +4127,12 @@
         <v>0</v>
       </c>
       <c r="E5" s="10">
-        <f>C5-B5*入力!$B$9-入力!$B$20-D5</f>
-        <v>-271244</v>
+        <f>C5-ROUND(B5*入力!$B$9,-4)-入力!$B$20-D5</f>
+        <v>-275000</v>
       </c>
       <c r="F5" s="8">
         <f>E5-入力!$B$13</f>
-        <v>-571244</v>
+        <v>-575000</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.3">
@@ -4146,12 +4152,12 @@
         <v>360000</v>
       </c>
       <c r="E6" s="10">
-        <f>C6-B6*入力!$B$9-入力!$B$20-D6</f>
-        <v>225776</v>
+        <f>C6-ROUND(B6*入力!$B$9,-4)-入力!$B$20-D6</f>
+        <v>220000</v>
       </c>
       <c r="F6" s="8">
         <f>E6-入力!$B$13</f>
-        <v>-74224</v>
+        <v>-80000</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.3">
@@ -4171,12 +4177,12 @@
         <v>360000</v>
       </c>
       <c r="E7" s="10">
-        <f>C7-B7*入力!$B$9-入力!$B$20-D7</f>
-        <v>739988</v>
+        <f>C7-ROUND(B7*入力!$B$9,-4)-入力!$B$20-D7</f>
+        <v>735000</v>
       </c>
       <c r="F7" s="8">
         <f>E7-入力!$B$13</f>
-        <v>439988</v>
+        <v>435000</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.3">
@@ -4196,12 +4202,12 @@
         <v>600000</v>
       </c>
       <c r="E8" s="10">
-        <f>C8-B8*入力!$B$9-入力!$B$20-D8</f>
-        <v>842796</v>
+        <f>C8-ROUND(B8*入力!$B$9,-4)-入力!$B$20-D8</f>
+        <v>835000</v>
       </c>
       <c r="F8" s="8">
         <f>E8-入力!$B$13</f>
-        <v>542796</v>
+        <v>535000</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.3">
@@ -4221,17 +4227,17 @@
         <v>600000</v>
       </c>
       <c r="E9" s="10">
-        <f>C9-B9*入力!$B$9-入力!$B$20-D9</f>
-        <v>1699816.0000000037</v>
+        <f>C9-ROUND(B9*入力!$B$9,-4)-入力!$B$20-D9</f>
+        <v>1690000.0000000037</v>
       </c>
       <c r="F9" s="8">
         <f>E9-入力!$B$13</f>
-        <v>1399816.0000000037</v>
+        <v>1390000.0000000037</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E11" s="8">
         <f>入力!B19*0.01*入力!B21</f>
@@ -4258,24 +4264,24 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.3">
@@ -4291,12 +4297,12 @@
         <v>0</v>
       </c>
       <c r="D4" s="10">
-        <f>B4-入力!$B$19*入力!$B$9-入力!$B$20-C4</f>
-        <v>-1384224</v>
+        <f>B4-ROUND(入力!$B$19*入力!$B$9,-4)-入力!$B$20-C4</f>
+        <v>-1390000</v>
       </c>
       <c r="E4" s="8">
         <f>D4-入力!$B$13</f>
-        <v>-1684224</v>
+        <v>-1690000</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.3">
@@ -4312,12 +4318,12 @@
         <v>0</v>
       </c>
       <c r="D5" s="10">
-        <f>B5-入力!$B$19*入力!$B$9-入力!$B$20-C5</f>
-        <v>-754224</v>
+        <f>B5-ROUND(入力!$B$19*入力!$B$9,-4)-入力!$B$20-C5</f>
+        <v>-760000</v>
       </c>
       <c r="E5" s="8">
         <f>D5-入力!$B$13</f>
-        <v>-1054224</v>
+        <v>-1060000</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.3">
@@ -4333,12 +4339,12 @@
         <v>0</v>
       </c>
       <c r="D6" s="10">
-        <f>B6-入力!$B$19*入力!$B$9-入力!$B$20-C6</f>
-        <v>-124224</v>
+        <f>B6-ROUND(入力!$B$19*入力!$B$9,-4)-入力!$B$20-C6</f>
+        <v>-130000</v>
       </c>
       <c r="E6" s="8">
         <f>D6-入力!$B$13</f>
-        <v>-424224</v>
+        <v>-430000</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.3">
@@ -4355,12 +4361,12 @@
         <v>360000</v>
       </c>
       <c r="D7" s="10">
-        <f>B7-入力!$B$19*入力!$B$9-入力!$B$20-C7</f>
-        <v>225776</v>
+        <f>B7-ROUND(入力!$B$19*入力!$B$9,-4)-入力!$B$20-C7</f>
+        <v>220000</v>
       </c>
       <c r="E7" s="8">
         <f>D7-入力!$B$13</f>
-        <v>-74224</v>
+        <v>-80000</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.3">
@@ -4376,12 +4382,12 @@
         <v>360000</v>
       </c>
       <c r="D8" s="10">
-        <f>B8-入力!$B$19*入力!$B$9-入力!$B$20-C8</f>
-        <v>775776</v>
+        <f>B8-ROUND(入力!$B$19*入力!$B$9,-4)-入力!$B$20-C8</f>
+        <v>770000</v>
       </c>
       <c r="E8" s="8">
         <f>D8-入力!$B$13</f>
-        <v>475776</v>
+        <v>470000</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.3">
@@ -4397,17 +4403,17 @@
         <v>600000</v>
       </c>
       <c r="D9" s="10">
-        <f>B9-入力!$B$19*入力!$B$9-入力!$B$20-C9</f>
-        <v>1165776</v>
+        <f>B9-ROUND(入力!$B$19*入力!$B$9,-4)-入力!$B$20-C9</f>
+        <v>1160000</v>
       </c>
       <c r="E9" s="8">
         <f>D9-入力!$B$13</f>
-        <v>865776</v>
+        <v>860000</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D11" s="8">
         <f>入力!B19*0.01</f>
@@ -4433,17 +4439,17 @@
   <sheetData>
     <row r="1" spans="1:12" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="31.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -4451,37 +4457,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="K5" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>108</v>
-      </c>
       <c r="L5" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" x14ac:dyDescent="0.3">
@@ -4510,12 +4516,12 @@
         <v>1250000</v>
       </c>
       <c r="H6" s="8">
-        <f>F6-D6*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>-458672</v>
+        <f>F6-ROUND(D6*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>-460000</v>
       </c>
       <c r="I6" s="8">
         <f>SUM($H$6:H6)</f>
-        <v>-458672</v>
+        <v>-460000</v>
       </c>
       <c r="J6" s="12"/>
       <c r="K6" s="11" t="str">
@@ -4553,12 +4559,12 @@
         <v>1500000</v>
       </c>
       <c r="H7" s="8">
-        <f>F7-D7*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>-257112</v>
+        <f>F7-ROUND(D7*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>-260000</v>
       </c>
       <c r="I7" s="8">
         <f>SUM($H$6:H7)</f>
-        <v>-715784</v>
+        <v>-720000</v>
       </c>
       <c r="J7" s="12"/>
       <c r="K7" s="11" t="str">
@@ -4596,12 +4602,12 @@
         <v>2100000</v>
       </c>
       <c r="H8" s="8">
-        <f>F8-D8*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>189088</v>
+        <f>F8-ROUND(D8*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>190000</v>
       </c>
       <c r="I8" s="8">
         <f>SUM($H$6:H8)</f>
-        <v>-526696</v>
+        <v>-530000</v>
       </c>
       <c r="J8" s="12"/>
       <c r="K8" s="11" t="str">
@@ -4639,12 +4645,12 @@
         <v>2150000</v>
       </c>
       <c r="H9" s="8">
-        <f>F9-D9*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>225248</v>
+        <f>F9-ROUND(D9*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>220000</v>
       </c>
       <c r="I9" s="8">
         <f>SUM($H$6:H9)</f>
-        <v>-301448</v>
+        <v>-310000</v>
       </c>
       <c r="J9" s="12"/>
       <c r="K9" s="11" t="str">
@@ -4682,12 +4688,12 @@
         <v>2900000</v>
       </c>
       <c r="H10" s="8">
-        <f>F10-D10*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>786848</v>
+        <f>F10-ROUND(D10*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>790000</v>
       </c>
       <c r="I10" s="8">
         <f>SUM($H$6:H10)</f>
-        <v>485400</v>
+        <v>480000</v>
       </c>
       <c r="J10" s="12"/>
       <c r="K10" s="11" t="str">
@@ -4725,12 +4731,12 @@
         <v>2050000</v>
       </c>
       <c r="H11" s="8">
-        <f>F11-D11*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>146008</v>
+        <f>F11-ROUND(D11*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>150000</v>
       </c>
       <c r="I11" s="8">
         <f>SUM($H$6:H11)</f>
-        <v>631408</v>
+        <v>630000</v>
       </c>
       <c r="J11" s="12"/>
       <c r="K11" s="11" t="str">
@@ -4768,12 +4774,12 @@
         <v>1150000</v>
       </c>
       <c r="H12" s="8">
-        <f>F12-D12*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>-537912</v>
+        <f>F12-ROUND(D12*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>-540000</v>
       </c>
       <c r="I12" s="8">
         <f>SUM($H$6:H12)</f>
-        <v>93496</v>
+        <v>90000</v>
       </c>
       <c r="J12" s="12"/>
       <c r="K12" s="11" t="str">
@@ -4811,12 +4817,12 @@
         <v>1850000</v>
       </c>
       <c r="H13" s="8">
-        <f>F13-D13*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>-19392</v>
+        <f>F13-ROUND(D13*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>-20000</v>
       </c>
       <c r="I13" s="8">
         <f>SUM($H$6:H13)</f>
-        <v>74104</v>
+        <v>70000</v>
       </c>
       <c r="J13" s="12"/>
       <c r="K13" s="11" t="str">
@@ -4854,12 +4860,12 @@
         <v>1500000</v>
       </c>
       <c r="H14" s="8">
-        <f>F14-D14*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>-250192</v>
+        <f>F14-ROUND(D14*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>-250000</v>
       </c>
       <c r="I14" s="8">
         <f>SUM($H$6:H14)</f>
-        <v>-176088</v>
+        <v>-180000</v>
       </c>
       <c r="J14" s="12"/>
       <c r="K14" s="11" t="str">
@@ -4897,12 +4903,12 @@
         <v>2050000</v>
       </c>
       <c r="H15" s="8">
-        <f>F15-D15*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>152928</v>
+        <f>F15-ROUND(D15*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>150000</v>
       </c>
       <c r="I15" s="8">
         <f>SUM($H$6:H15)</f>
-        <v>-23160</v>
+        <v>-30000</v>
       </c>
       <c r="J15" s="12"/>
       <c r="K15" s="11" t="str">
@@ -4940,12 +4946,12 @@
         <v>2050000</v>
       </c>
       <c r="H16" s="8">
-        <f>F16-D16*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>146008</v>
+        <f>F16-ROUND(D16*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>150000</v>
       </c>
       <c r="I16" s="8">
         <f>SUM($H$6:H16)</f>
-        <v>122848</v>
+        <v>120000</v>
       </c>
       <c r="J16" s="12"/>
       <c r="K16" s="11" t="str">
@@ -4983,12 +4989,12 @@
         <v>2000000</v>
       </c>
       <c r="H17" s="8">
-        <f>F17-D17*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>102928</v>
+        <f>F17-ROUND(D17*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>100000</v>
       </c>
       <c r="I17" s="8">
         <f>SUM($H$6:H17)</f>
-        <v>225776</v>
+        <v>220000</v>
       </c>
       <c r="J17" s="12"/>
       <c r="K17" s="11" t="str">
@@ -5026,7 +5032,7 @@
       </c>
       <c r="H18" s="10">
         <f>SUM(H6:H17)</f>
-        <v>225776</v>
+        <v>220000</v>
       </c>
       <c r="J18" s="10">
         <f>SUM(J6:J17)</f>
@@ -5052,7 +5058,7 @@
     </row>
     <row r="20" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -5075,17 +5081,17 @@
   <sheetData>
     <row r="1" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -5093,40 +5099,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="K5" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="L5" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>108</v>
-      </c>
       <c r="M5" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" x14ac:dyDescent="0.3">
@@ -5155,12 +5161,12 @@
         <v>1900000</v>
       </c>
       <c r="H6" s="8">
-        <f>F6-D6*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>23688</v>
+        <f>F6-ROUND(D6*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>20000</v>
       </c>
       <c r="I6" s="8">
         <f>SUM($H$6:H6)</f>
-        <v>23688</v>
+        <v>20000</v>
       </c>
       <c r="J6" s="8">
         <f>F6-月別目標と営業利益!F6</f>
@@ -5202,12 +5208,12 @@
         <v>1900000</v>
       </c>
       <c r="H7" s="8">
-        <f>F7-D7*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>23688</v>
+        <f>F7-ROUND(D7*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>20000</v>
       </c>
       <c r="I7" s="8">
         <f>SUM($H$6:H7)</f>
-        <v>47376</v>
+        <v>40000</v>
       </c>
       <c r="J7" s="8">
         <f>F7-月別目標と営業利益!F7</f>
@@ -5249,12 +5255,12 @@
         <v>2000000</v>
       </c>
       <c r="H8" s="8">
-        <f>F8-D8*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>109848</v>
+        <f>F8-ROUND(D8*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>110000</v>
       </c>
       <c r="I8" s="8">
         <f>SUM($H$6:H8)</f>
-        <v>157224</v>
+        <v>150000</v>
       </c>
       <c r="J8" s="8">
         <f>F8-月別目標と営業利益!F8</f>
@@ -5296,12 +5302,12 @@
         <v>2000000</v>
       </c>
       <c r="H9" s="8">
-        <f>F9-D9*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>109848</v>
+        <f>F9-ROUND(D9*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>110000</v>
       </c>
       <c r="I9" s="8">
         <f>SUM($H$6:H9)</f>
-        <v>267072</v>
+        <v>260000</v>
       </c>
       <c r="J9" s="8">
         <f>F9-月別目標と営業利益!F9</f>
@@ -5343,12 +5349,12 @@
         <v>2500000</v>
       </c>
       <c r="H10" s="8">
-        <f>F10-D10*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>506048</v>
+        <f>F10-ROUND(D10*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>510000</v>
       </c>
       <c r="I10" s="8">
         <f>SUM($H$6:H10)</f>
-        <v>773120</v>
+        <v>770000</v>
       </c>
       <c r="J10" s="8">
         <f>F10-月別目標と営業利益!F10</f>
@@ -5390,12 +5396,12 @@
         <v>2150000</v>
       </c>
       <c r="H11" s="8">
-        <f>F11-D11*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>225248</v>
+        <f>F11-ROUND(D11*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>220000</v>
       </c>
       <c r="I11" s="8">
         <f>SUM($H$6:H11)</f>
-        <v>998368</v>
+        <v>990000</v>
       </c>
       <c r="J11" s="8">
         <f>F11-月別目標と営業利益!F11</f>
@@ -5437,12 +5443,12 @@
         <v>1900000</v>
       </c>
       <c r="H12" s="8">
-        <f>F12-D12*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>23688</v>
+        <f>F12-ROUND(D12*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>20000</v>
       </c>
       <c r="I12" s="8">
         <f>SUM($H$6:H12)</f>
-        <v>1022056</v>
+        <v>1010000</v>
       </c>
       <c r="J12" s="8">
         <f>F12-月別目標と営業利益!F12</f>
@@ -5484,12 +5490,12 @@
         <v>2000000</v>
       </c>
       <c r="H13" s="8">
-        <f>F13-D13*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>109848</v>
+        <f>F13-ROUND(D13*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>110000</v>
       </c>
       <c r="I13" s="8">
         <f>SUM($H$6:H13)</f>
-        <v>1131904</v>
+        <v>1120000</v>
       </c>
       <c r="J13" s="8">
         <f>F13-月別目標と営業利益!F13</f>
@@ -5531,12 +5537,12 @@
         <v>1900000</v>
       </c>
       <c r="H14" s="8">
-        <f>F14-D14*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>23688</v>
+        <f>F14-ROUND(D14*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>20000</v>
       </c>
       <c r="I14" s="8">
         <f>SUM($H$6:H14)</f>
-        <v>1155592</v>
+        <v>1140000</v>
       </c>
       <c r="J14" s="8">
         <f>F14-月別目標と営業利益!F14</f>
@@ -5578,12 +5584,12 @@
         <v>1900000</v>
       </c>
       <c r="H15" s="8">
-        <f>F15-D15*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>23688</v>
+        <f>F15-ROUND(D15*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>20000</v>
       </c>
       <c r="I15" s="8">
         <f>SUM($H$6:H15)</f>
-        <v>1179280</v>
+        <v>1160000</v>
       </c>
       <c r="J15" s="8">
         <f>F15-月別目標と営業利益!F15</f>
@@ -5625,12 +5631,12 @@
         <v>2000000</v>
       </c>
       <c r="H16" s="8">
-        <f>F16-D16*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>109848</v>
+        <f>F16-ROUND(D16*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>110000</v>
       </c>
       <c r="I16" s="8">
         <f>SUM($H$6:H16)</f>
-        <v>1289128</v>
+        <v>1270000</v>
       </c>
       <c r="J16" s="8">
         <f>F16-月別目標と営業利益!F16</f>
@@ -5672,12 +5678,12 @@
         <v>1900000</v>
       </c>
       <c r="H17" s="8">
-        <f>F17-D17*入力!$B$9-入力!$B$20/12-入力!$B$14</f>
-        <v>23688</v>
+        <f>F17-ROUND(D17*入力!$B$9,-4)-入力!$B$20/12-入力!$B$14</f>
+        <v>20000</v>
       </c>
       <c r="I17" s="8">
         <f>SUM($H$6:H17)</f>
-        <v>1312816</v>
+        <v>1290000</v>
       </c>
       <c r="J17" s="8">
         <f>F17-月別目標と営業利益!F17</f>
@@ -5719,7 +5725,7 @@
       </c>
       <c r="H18" s="10">
         <f>SUM(H6:H17)</f>
-        <v>1312816</v>
+        <v>1290000</v>
       </c>
       <c r="K18" s="10">
         <f>SUM(K6:K17)</f>
@@ -5732,7 +5738,7 @@
     </row>
     <row r="19" spans="1:13" ht="15" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D19" s="8">
         <f>D18-入力!B19</f>
@@ -5745,7 +5751,7 @@
     </row>
     <row r="20" spans="1:13" ht="15" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -5767,12 +5773,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -5783,18 +5789,18 @@
         <v>29</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B5" s="4">
         <v>1</v>
@@ -5812,7 +5818,7 @@
     </row>
     <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B6" s="4">
         <v>1</v>
@@ -5830,7 +5836,7 @@
     </row>
     <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B7" s="4">
         <v>2</v>
@@ -5848,7 +5854,7 @@
     </row>
     <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B8" s="9">
         <f>SUM(B5:B7)</f>
@@ -5865,7 +5871,7 @@
     </row>
     <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D9" s="10">
         <f>D8*12</f>
@@ -5878,12 +5884,12 @@
     </row>
     <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" x14ac:dyDescent="0.3">

--- a/excel/Weekends_予算と報奨金案_粗利2150万円.xlsx
+++ b/excel/Weekends_予算と報奨金案_粗利2150万円.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yataka-02\AppData\Local\Temp\claude\C--Users-yataka-02-Desktop-Claude\76fa42a7-01fc-42d8-86c7-11cf90447c56\scratchpad\margin-calculator\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E180A3-A5EA-4934-AF8F-43848D48AB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B38EB86-47D5-4FA9-A27E-140AFADECE3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -208,15 +208,9 @@
     <t>報奨金 第1段階（店舗計・月）</t>
   </si>
   <si>
-    <t>粗利が月の目標の100%以上。1人あたりの額は「報奨金（例B）」シートで入力</t>
-  </si>
-  <si>
     <t>報奨金 第2段階（店舗計・月）</t>
   </si>
   <si>
-    <t>粗利が月の目標の105%以上。同上</t>
-  </si>
-  <si>
     <t>第2段階のライン</t>
   </si>
   <si>
@@ -320,9 +314,6 @@
   </si>
   <si>
     <t>粗利率1ポイントあたりの営業利益の変化</t>
-  </si>
-  <si>
-    <t>月の目標は前年（2025/8〜2026/7）の売上構成比で配分。固定費は12等分。黄色の実績粗利（スマレジ・税抜）を入れると段階と報奨金が出る。</t>
   </si>
   <si>
     <t>黄色の「売上目標」は10万円単位（年計6,300万円）、「粗利目標100%」は5万円単位（年計2,150万円）に丸めた目標。105%は5万円単位。</t>
@@ -518,26 +509,10 @@
     <phoneticPr fontId="9"/>
   </si>
   <si>
-    <t>年間予算（決算上の目標）。月の目標の合計は2,285万円で、予算より135万円多い（2026-10-07 ②案）</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>月の目標＝店長がスマレジに登録した予算（年6,000万円・税抜）×粗利率。ただし赤字になる月（8・9・2・4・5・7月）は、販管費を賄える粗利180万円・売上530万円に引き上げた。</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t>黄色の目標は手入力。月の目標の合計（売上6,680万円・粗利2,285万円）は年間予算（6,300万円・2,150万円）より多く、その差が予算達成の余裕になる（2026-10-07 ②案）。</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
     <t>年間予算との差（上乗せ分）</t>
     <phoneticPr fontId="9"/>
   </si>
   <si>
-    <t>（月の目標の合計が年間予算をどれだけ上回るか。プラスなら、月の目標がいくつか未達でも年間予算に届く余裕がある）</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
     <t>売上歩合制。前年12か月の回帰の切片209,792円を月21万円に丸め（2026-10-07）</t>
     <phoneticPr fontId="9"/>
   </si>
@@ -559,6 +534,34 @@
   </si>
   <si>
     <t>共通部の実費＝発展会計の共通部（主に租税公課、予算は月8万円・年96万円、前年実績943,852円を丸め）。「なし」は店舗だけの損益、「あり」は現在の計画、「本部費込み」は共通部の実費の代わりに管理会計の本部費（月15.8万円）を負担した場合（参考）。金額はすべて税抜・円。</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>年間予算（決算上の目標）。報奨金の目標の合計は2,285万円で、予算より135万円多い（2026-10-07 ②案）</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>粗利が報奨金の目標の100%以上。1人あたりの額は「報奨金（例B）」シートで入力</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>粗利が報奨金の目標の105%以上。同上</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>報奨金の目標は前年（2025/8〜2026/7）の売上構成比で配分。固定費は12等分。黄色の実績粗利（スマレジ・税抜）を入れると段階と報奨金が出る。</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>報奨金の目標＝店長がスマレジに登録した予算（年6,000万円・税抜）×粗利率。ただし赤字になる月（8・9・2・4・5・7月）は、販管費を賄える粗利180万円・売上530万円に引き上げた。</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>黄色の目標は手入力。報奨金の目標の合計（売上6,680万円・粗利2,285万円）は年間予算（6,300万円・2,150万円）より多く、その差が予算達成の余裕になる（2026-10-07 ②案）。</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>（報奨金の目標の合計が年間予算をどれだけ上回るか。プラスなら、報奨金の目標がいくつか未達でも年間予算に届く余裕がある）</t>
     <phoneticPr fontId="9"/>
   </si>
 </sst>
@@ -1944,22 +1947,22 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="21" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1967,30 +1970,30 @@
         <v>38</v>
       </c>
       <c r="B6" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="F6" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="G6" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="E6" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>143</v>
-      </c>
       <c r="H6" s="22" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B7" s="23">
         <f>1</f>
@@ -2019,7 +2022,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B8" s="24">
         <f>入力!$B$19*B7</f>
@@ -2046,12 +2049,12 @@
         <v>66150000</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B9" s="24">
         <f>入力!$B$5*B7</f>
@@ -2078,12 +2081,12 @@
         <v>22575000</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B10" s="24">
         <f>入力!$B$7*12</f>
@@ -2110,12 +2113,12 @@
         <v>9600000</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B11" s="24">
         <f>IF(B7&gt;=入力!$B$16,入力!$B$15,IF(B7&gt;=1,入力!$B$14,0))*12</f>
@@ -2142,12 +2145,12 @@
         <v>600000</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B12" s="24">
         <f>入力!$B$8*12+ROUND(B8*入力!$B$9,-4)</f>
@@ -2174,12 +2177,12 @@
         <v>7100000</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B13" s="24">
         <f>入力!$B$10</f>
@@ -2208,7 +2211,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="26" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B14" s="27">
         <f t="shared" ref="B14:G14" si="0">SUM(B10:B13)</f>
@@ -2235,12 +2238,12 @@
         <v>20780000</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="26" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B15" s="27">
         <f t="shared" ref="B15:G15" si="1">B9-B14</f>
@@ -2267,12 +2270,12 @@
         <v>1795000</v>
       </c>
       <c r="H15" s="26" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B16" s="24">
         <v>0</v>
@@ -2295,12 +2298,12 @@
         <v>0</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B17" s="24">
         <v>0</v>
@@ -2323,12 +2326,12 @@
         <v>1896000</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B18" s="27">
         <f t="shared" ref="B18:G18" si="2">B15-B16-B17</f>
@@ -2355,12 +2358,12 @@
         <v>-101000</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B19" s="24">
         <f>入力!$B$13</f>
@@ -2389,7 +2392,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B20" s="27">
         <f t="shared" ref="B20:G20" si="3">B18-B19</f>
@@ -2419,7 +2422,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B21" s="24">
         <f>(入力!$B$7*12+入力!$B$8*12+入力!$B$10+B16+B17)/入力!$B$21</f>
@@ -2446,12 +2449,12 @@
         <v>64307017.339151941</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B22" s="25">
         <f>B21/入力!$B$19</f>
@@ -2478,29 +2481,29 @@
         <v>1.0207463069706657</v>
       </c>
       <c r="H22" s="19" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="21" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="30" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B26" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="E26" s="22" t="s">
         <v>145</v>
-      </c>
-      <c r="C26" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="D26" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -2637,7 +2640,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="21" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="30" x14ac:dyDescent="0.3">
@@ -2645,16 +2648,16 @@
         <v>4</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -2944,7 +2947,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="30" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C50" s="31">
         <f>COUNTIF(C37:C48,"&lt;0")</f>
@@ -3488,7 +3491,7 @@
     </row>
     <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C19" s="8">
         <f>C18-入力!B5</f>
@@ -3615,7 +3618,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
@@ -3642,7 +3645,7 @@
         <v>21500000</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.3">
@@ -3676,7 +3679,7 @@
         <v>210000</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.3">
@@ -3687,7 +3690,7 @@
         <v>6.9199999999999998E-2</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.3">
@@ -3698,7 +3701,7 @@
         <v>3480000</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.3">
@@ -3709,7 +3712,7 @@
         <v>960000</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.3">
@@ -3743,24 +3746,24 @@
         <v>30000</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>55</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B15" s="14">
         <f>'報奨金（例B）'!E8</f>
         <v>50000</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>57</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B16" s="15">
         <v>1.05</v>
@@ -3769,47 +3772,47 @@
     </row>
     <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B19" s="12">
         <v>63000000</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B20" s="8">
         <f>B7*12+B8*12+B10+B11</f>
         <v>16560000</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B21" s="16">
         <f>B6-B9</f>
         <v>0.27206984126984129</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B22" s="8">
         <f>B20/B21</f>
@@ -3835,7 +3838,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="31.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -3843,18 +3846,18 @@
         <v>38</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B4" s="16">
         <v>1</v>
@@ -3867,7 +3870,7 @@
     </row>
     <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B5" s="8">
         <f>入力!$B$19*B4</f>
@@ -3878,12 +3881,12 @@
         <v>66150000</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B6" s="8">
         <f>入力!$B$5*B4</f>
@@ -3897,7 +3900,7 @@
     </row>
     <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B7" s="8">
         <f>入力!$B$7*12</f>
@@ -3908,12 +3911,12 @@
         <v>9600000</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B8" s="8">
         <f>入力!$B$14*12</f>
@@ -3924,12 +3927,12 @@
         <v>600000</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B9" s="8">
         <f>入力!$B$8*12+ROUND(B5*入力!$B$9,-4)</f>
@@ -3940,12 +3943,12 @@
         <v>7100000</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B10" s="8">
         <f>入力!$B$10</f>
@@ -3959,7 +3962,7 @@
     </row>
     <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B11" s="8">
         <f>入力!$B$11</f>
@@ -3973,7 +3976,7 @@
     </row>
     <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B12" s="8">
         <f>SUM(B7:B11)</f>
@@ -3987,7 +3990,7 @@
     </row>
     <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B13" s="7">
         <f>B6-B12</f>
@@ -4001,7 +4004,7 @@
     </row>
     <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B14" s="8">
         <f>入力!$B$13</f>
@@ -4015,7 +4018,7 @@
     </row>
     <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B15" s="7">
         <f>B13-B14</f>
@@ -4029,7 +4032,7 @@
     </row>
     <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B16" s="8">
         <f>B13+B11-入力!$B$12*12</f>
@@ -4040,7 +4043,7 @@
         <v>-101000</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -4062,27 +4065,27 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>73</v>
-      </c>
       <c r="D3" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>82</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.3">
@@ -4237,7 +4240,7 @@
     </row>
     <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E11" s="8">
         <f>入力!B19*0.01*入力!B21</f>
@@ -4264,24 +4267,24 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>82</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.3">
@@ -4413,7 +4416,7 @@
     </row>
     <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D11" s="8">
         <f>入力!B19*0.01</f>
@@ -4439,17 +4442,17 @@
   <sheetData>
     <row r="1" spans="1:12" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>93</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="31.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -4457,37 +4460,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="K5" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>103</v>
-      </c>
       <c r="L5" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" x14ac:dyDescent="0.3">
@@ -5058,7 +5061,7 @@
     </row>
     <row r="20" spans="1:12" ht="15" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -5081,17 +5084,17 @@
   <sheetData>
     <row r="1" spans="1:13" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -5099,40 +5102,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="J5" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="K5" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="L5" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>103</v>
-      </c>
       <c r="M5" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" x14ac:dyDescent="0.3">
@@ -5738,7 +5741,7 @@
     </row>
     <row r="19" spans="1:13" ht="15" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D19" s="8">
         <f>D18-入力!B19</f>
@@ -5751,7 +5754,7 @@
     </row>
     <row r="20" spans="1:13" ht="15" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -5773,12 +5776,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.600000000000001" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -5789,18 +5792,18 @@
         <v>29</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B5" s="4">
         <v>1</v>
@@ -5818,7 +5821,7 @@
     </row>
     <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B6" s="4">
         <v>1</v>
@@ -5836,7 +5839,7 @@
     </row>
     <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B7" s="4">
         <v>2</v>
@@ -5854,7 +5857,7 @@
     </row>
     <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B8" s="9">
         <f>SUM(B5:B7)</f>
@@ -5871,7 +5874,7 @@
     </row>
     <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D9" s="10">
         <f>D8*12</f>
@@ -5884,12 +5887,12 @@
     </row>
     <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" x14ac:dyDescent="0.3">
